--- a/waste-calculator/waste_calculator_template.xlsx
+++ b/waste-calculator/waste_calculator_template.xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet name="使い方" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="入力" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="比較表" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="かんたん入力" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="詳細入力" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -140,8 +140,8 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B22"/>
+  <dimension ref="B2:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -531,70 +531,66 @@
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>① 入力シート</t>
+          <t>① どちらのシートを使うか</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>青字のセルのみ入力してください（黒字は自動計算の数式です）。</t>
+          <t>「かんたん入力」：種別・数量・頻度だけで月間袋数をサッと出したいとき。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>・ラボ名：案件（ラボ）ごとに同じ表記で統一してください（比較表で名前を突き合わせます）</t>
+          <t>「詳細入力」：単位・袋サイズ・単価まで含めて月間容量や概算料金も試算したいとき。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>・種別：可燃ごみ／生ごみ／不燃ごみ／瓶／缶／ペットボトル／段ボール／その他 からセルのドロップダウンで選択できます</t>
+          <t>どちらも青字のセルのみ入力してください（黒字は自動計算の数式です）。</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>・頻度パターン：</t>
-        </is>
-      </c>
+      <c r="B9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="B10" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">　「日」＝1回（1日）あたりの数量 × 週の収集日数　（例：1〜2袋/日、週5回）</t>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>② 入力のしかた</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">　「週」＝週あたりの数量をそのまま入力　（例：週に1〜2袋、瓶・缶・ペットボトルなど）</t>
+          <t>・ラボ名（案件名）：案件ごとに分かる名前を入力（複数案件を1シートに並べてOK）</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>・週の収集日数：頻度パターンが「日」の場合のみ入力してください</t>
+          <t>・種別：可燃ごみ／生ごみ／不燃ごみ／瓶／缶／ペットボトル／段ボール／その他 からドロップダウンで選択</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>・袋サイズ(L)：容量を計算したい場合のみ入力（段ボール等「枚」単位の項目は空欄でOK）</t>
+          <t>・頻度(週◯回)：収集の頻度。例:「1日1〜2袋、週5回」→数量1〜2・頻度5、「週に1〜2袋」→数量1〜2・頻度1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>・単価(円)：概算料金を出したい場合のみ入力（未入力の項目は料金計算から除外されます）</t>
+          <t>・（詳細入力のみ）袋サイズ(L)：容量を計算したい場合のみ入力。単価(円)：概算料金を出したい場合のみ入力</t>
         </is>
       </c>
     </row>
@@ -604,45 +600,21 @@
     <row r="16">
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>② 比較表シート</t>
+          <t>③ 前提</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>入力シートに登録したラボ名を1行ずつ入力すると、種別ごとの月間量・合計容量・概算料金が自動集計されます。</t>
+          <t>1ヶ月あたりの週数は各シートのC1セルで設定（既定値 4.35週 ＝ 365日 ÷ 12ヶ月 ÷ 7日）。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>ラボ名は入力シートの表記と完全に一致させてください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="4" t="inlineStr"/>
-    </row>
-    <row r="20">
-      <c r="B20" s="3" t="inlineStr">
-        <is>
-          <t>③ 前提</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="4" t="inlineStr">
-        <is>
-          <t>1ヶ月あたりの週数は「入力」シート C1 セルで設定しています（既定値 4.35 週 ＝ 365日 ÷ 12ヶ月 ÷ 7日）。</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="4" t="inlineStr">
-        <is>
-          <t>数量が明記されていない項目（例：「不燃物 週2日」のみで数量記載なし）は 1回1袋 と仮定しています。実数が分かり次第、入力シートの数量を修正してください。</t>
+          <t>数量が明記されていない項目（例:「不燃物 週2日」のみで数量記載なし）は 1回1袋 と仮定しています。実数が分かり次第、数量欄を修正してください。</t>
         </is>
       </c>
     </row>
@@ -657,10 +629,636 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>1ヶ月あたりの週数</t>
+        </is>
+      </c>
+      <c r="C1" s="6" t="n">
+        <v>4.35</v>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>※365日÷12ヶ月÷7日で算出した平均週数。必要に応じて変更してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
+      <c r="A3" s="8" t="inlineStr">
+        <is>
+          <t>ラボ名（案件名）</t>
+        </is>
+      </c>
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>種別</t>
+        </is>
+      </c>
+      <c r="C3" s="8" t="inlineStr">
+        <is>
+          <t>数量min(1回あたり)</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>数量max(1回あたり)</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>頻度(週◯回)</t>
+        </is>
+      </c>
+      <c r="F3" s="8" t="inlineStr">
+        <is>
+          <t>月間量(平均)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="inlineStr">
+        <is>
+          <t>新宿区新規ラボ（laidback cafeの例）</t>
+        </is>
+      </c>
+      <c r="B4" s="9" t="inlineStr">
+        <is>
+          <t>可燃ごみ</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D4" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="F4" s="10">
+        <f>IF(C4="","",(C4+D4)/2*E4*$C$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>新宿区新規ラボ（laidback cafeの例）</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="inlineStr">
+        <is>
+          <t>生ごみ</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="F5" s="10">
+        <f>IF(C5="","",(C5+D5)/2*E5*$C$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>新宿区新規ラボ（laidback cafeの例）</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>瓶</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="10">
+        <f>IF(C6="","",(C6+D6)/2*E6*$C$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>新宿区新規ラボ（laidback cafeの例）</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>缶</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" s="10">
+        <f>IF(C7="","",(C7+D7)/2*E7*$C$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>新宿区新規ラボ（laidback cafeの例）</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>ペットボトル</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" s="10">
+        <f>IF(C8="","",(C8+D8)/2*E8*$C$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>新宿区新規ラボ（laidback cafeの例）</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>段ボール</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="10">
+        <f>IF(C9="","",(C9+D9)/2*E9*$C$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>中野区の現ラボの例</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>可燃ごみ</t>
+        </is>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="F10" s="10">
+        <f>IF(C10="","",(C10+D10)/2*E10*$C$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>中野区の現ラボの例</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>不燃ごみ</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="F11" s="10">
+        <f>IF(C11="","",(C11+D11)/2*E11*$C$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="11" t="n"/>
+      <c r="B12" s="11" t="n"/>
+      <c r="C12" s="11" t="n"/>
+      <c r="D12" s="11" t="n"/>
+      <c r="E12" s="11" t="n"/>
+      <c r="F12" s="10">
+        <f>IF(C12="","",(C12+D12)/2*E12*$C$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="n"/>
+      <c r="B13" s="11" t="n"/>
+      <c r="C13" s="11" t="n"/>
+      <c r="D13" s="11" t="n"/>
+      <c r="E13" s="11" t="n"/>
+      <c r="F13" s="10">
+        <f>IF(C13="","",(C13+D13)/2*E13*$C$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="n"/>
+      <c r="B14" s="11" t="n"/>
+      <c r="C14" s="11" t="n"/>
+      <c r="D14" s="11" t="n"/>
+      <c r="E14" s="11" t="n"/>
+      <c r="F14" s="10">
+        <f>IF(C14="","",(C14+D14)/2*E14*$C$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="11" t="n"/>
+      <c r="B15" s="11" t="n"/>
+      <c r="C15" s="11" t="n"/>
+      <c r="D15" s="11" t="n"/>
+      <c r="E15" s="11" t="n"/>
+      <c r="F15" s="10">
+        <f>IF(C15="","",(C15+D15)/2*E15*$C$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="11" t="n"/>
+      <c r="B16" s="11" t="n"/>
+      <c r="C16" s="11" t="n"/>
+      <c r="D16" s="11" t="n"/>
+      <c r="E16" s="11" t="n"/>
+      <c r="F16" s="10">
+        <f>IF(C16="","",(C16+D16)/2*E16*$C$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="11" t="n"/>
+      <c r="B17" s="11" t="n"/>
+      <c r="C17" s="11" t="n"/>
+      <c r="D17" s="11" t="n"/>
+      <c r="E17" s="11" t="n"/>
+      <c r="F17" s="10">
+        <f>IF(C17="","",(C17+D17)/2*E17*$C$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="11" t="n"/>
+      <c r="B18" s="11" t="n"/>
+      <c r="C18" s="11" t="n"/>
+      <c r="D18" s="11" t="n"/>
+      <c r="E18" s="11" t="n"/>
+      <c r="F18" s="10">
+        <f>IF(C18="","",(C18+D18)/2*E18*$C$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="11" t="n"/>
+      <c r="B19" s="11" t="n"/>
+      <c r="C19" s="11" t="n"/>
+      <c r="D19" s="11" t="n"/>
+      <c r="E19" s="11" t="n"/>
+      <c r="F19" s="10">
+        <f>IF(C19="","",(C19+D19)/2*E19*$C$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="n"/>
+      <c r="B20" s="11" t="n"/>
+      <c r="C20" s="11" t="n"/>
+      <c r="D20" s="11" t="n"/>
+      <c r="E20" s="11" t="n"/>
+      <c r="F20" s="10">
+        <f>IF(C20="","",(C20+D20)/2*E20*$C$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="11" t="n"/>
+      <c r="B21" s="11" t="n"/>
+      <c r="C21" s="11" t="n"/>
+      <c r="D21" s="11" t="n"/>
+      <c r="E21" s="11" t="n"/>
+      <c r="F21" s="10">
+        <f>IF(C21="","",(C21+D21)/2*E21*$C$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="n"/>
+      <c r="B22" s="11" t="n"/>
+      <c r="C22" s="11" t="n"/>
+      <c r="D22" s="11" t="n"/>
+      <c r="E22" s="11" t="n"/>
+      <c r="F22" s="10">
+        <f>IF(C22="","",(C22+D22)/2*E22*$C$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="n"/>
+      <c r="B23" s="11" t="n"/>
+      <c r="C23" s="11" t="n"/>
+      <c r="D23" s="11" t="n"/>
+      <c r="E23" s="11" t="n"/>
+      <c r="F23" s="10">
+        <f>IF(C23="","",(C23+D23)/2*E23*$C$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="n"/>
+      <c r="B24" s="11" t="n"/>
+      <c r="C24" s="11" t="n"/>
+      <c r="D24" s="11" t="n"/>
+      <c r="E24" s="11" t="n"/>
+      <c r="F24" s="10">
+        <f>IF(C24="","",(C24+D24)/2*E24*$C$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="n"/>
+      <c r="B25" s="11" t="n"/>
+      <c r="C25" s="11" t="n"/>
+      <c r="D25" s="11" t="n"/>
+      <c r="E25" s="11" t="n"/>
+      <c r="F25" s="10">
+        <f>IF(C25="","",(C25+D25)/2*E25*$C$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="11" t="n"/>
+      <c r="B26" s="11" t="n"/>
+      <c r="C26" s="11" t="n"/>
+      <c r="D26" s="11" t="n"/>
+      <c r="E26" s="11" t="n"/>
+      <c r="F26" s="10">
+        <f>IF(C26="","",(C26+D26)/2*E26*$C$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="11" t="n"/>
+      <c r="B27" s="11" t="n"/>
+      <c r="C27" s="11" t="n"/>
+      <c r="D27" s="11" t="n"/>
+      <c r="E27" s="11" t="n"/>
+      <c r="F27" s="10">
+        <f>IF(C27="","",(C27+D27)/2*E27*$C$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="n"/>
+      <c r="B28" s="11" t="n"/>
+      <c r="C28" s="11" t="n"/>
+      <c r="D28" s="11" t="n"/>
+      <c r="E28" s="11" t="n"/>
+      <c r="F28" s="10">
+        <f>IF(C28="","",(C28+D28)/2*E28*$C$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="11" t="n"/>
+      <c r="B29" s="11" t="n"/>
+      <c r="C29" s="11" t="n"/>
+      <c r="D29" s="11" t="n"/>
+      <c r="E29" s="11" t="n"/>
+      <c r="F29" s="10">
+        <f>IF(C29="","",(C29+D29)/2*E29*$C$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="n"/>
+      <c r="B30" s="11" t="n"/>
+      <c r="C30" s="11" t="n"/>
+      <c r="D30" s="11" t="n"/>
+      <c r="E30" s="11" t="n"/>
+      <c r="F30" s="10">
+        <f>IF(C30="","",(C30+D30)/2*E30*$C$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="11" t="n"/>
+      <c r="B31" s="11" t="n"/>
+      <c r="C31" s="11" t="n"/>
+      <c r="D31" s="11" t="n"/>
+      <c r="E31" s="11" t="n"/>
+      <c r="F31" s="10">
+        <f>IF(C31="","",(C31+D31)/2*E31*$C$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="n"/>
+      <c r="B32" s="11" t="n"/>
+      <c r="C32" s="11" t="n"/>
+      <c r="D32" s="11" t="n"/>
+      <c r="E32" s="11" t="n"/>
+      <c r="F32" s="10">
+        <f>IF(C32="","",(C32+D32)/2*E32*$C$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="11" t="n"/>
+      <c r="B33" s="11" t="n"/>
+      <c r="C33" s="11" t="n"/>
+      <c r="D33" s="11" t="n"/>
+      <c r="E33" s="11" t="n"/>
+      <c r="F33" s="10">
+        <f>IF(C33="","",(C33+D33)/2*E33*$C$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="11" t="n"/>
+      <c r="B34" s="11" t="n"/>
+      <c r="C34" s="11" t="n"/>
+      <c r="D34" s="11" t="n"/>
+      <c r="E34" s="11" t="n"/>
+      <c r="F34" s="10">
+        <f>IF(C34="","",(C34+D34)/2*E34*$C$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="n"/>
+      <c r="B35" s="11" t="n"/>
+      <c r="C35" s="11" t="n"/>
+      <c r="D35" s="11" t="n"/>
+      <c r="E35" s="11" t="n"/>
+      <c r="F35" s="10">
+        <f>IF(C35="","",(C35+D35)/2*E35*$C$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="n"/>
+      <c r="B36" s="11" t="n"/>
+      <c r="C36" s="11" t="n"/>
+      <c r="D36" s="11" t="n"/>
+      <c r="E36" s="11" t="n"/>
+      <c r="F36" s="10">
+        <f>IF(C36="","",(C36+D36)/2*E36*$C$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="n"/>
+      <c r="B37" s="11" t="n"/>
+      <c r="C37" s="11" t="n"/>
+      <c r="D37" s="11" t="n"/>
+      <c r="E37" s="11" t="n"/>
+      <c r="F37" s="10">
+        <f>IF(C37="","",(C37+D37)/2*E37*$C$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="n"/>
+      <c r="B38" s="11" t="n"/>
+      <c r="C38" s="11" t="n"/>
+      <c r="D38" s="11" t="n"/>
+      <c r="E38" s="11" t="n"/>
+      <c r="F38" s="10">
+        <f>IF(C38="","",(C38+D38)/2*E38*$C$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="11" t="n"/>
+      <c r="B39" s="11" t="n"/>
+      <c r="C39" s="11" t="n"/>
+      <c r="D39" s="11" t="n"/>
+      <c r="E39" s="11" t="n"/>
+      <c r="F39" s="10">
+        <f>IF(C39="","",(C39+D39)/2*E39*$C$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="n"/>
+      <c r="B40" s="11" t="n"/>
+      <c r="C40" s="11" t="n"/>
+      <c r="D40" s="11" t="n"/>
+      <c r="E40" s="11" t="n"/>
+      <c r="F40" s="10">
+        <f>IF(C40="","",(C40+D40)/2*E40*$C$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="n"/>
+      <c r="B41" s="11" t="n"/>
+      <c r="C41" s="11" t="n"/>
+      <c r="D41" s="11" t="n"/>
+      <c r="E41" s="11" t="n"/>
+      <c r="F41" s="10">
+        <f>IF(C41="","",(C41+D41)/2*E41*$C$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="11" t="n"/>
+      <c r="B42" s="11" t="n"/>
+      <c r="C42" s="11" t="n"/>
+      <c r="D42" s="11" t="n"/>
+      <c r="E42" s="11" t="n"/>
+      <c r="F42" s="10">
+        <f>IF(C42="","",(C42+D42)/2*E42*$C$1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="11" t="n"/>
+      <c r="B43" s="11" t="n"/>
+      <c r="C43" s="11" t="n"/>
+      <c r="D43" s="11" t="n"/>
+      <c r="E43" s="11" t="n"/>
+      <c r="F43" s="10">
+        <f>IF(C43="","",(C43+D43)/2*E43*$C$1)</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="B4:B43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+      <formula1>"可燃ごみ,生ごみ,不燃ごみ,瓶,缶,ペットボトル,段ボール,その他"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:L43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
@@ -692,7 +1290,7 @@
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>ラボ名</t>
+          <t>ラボ名（案件名）</t>
         </is>
       </c>
       <c r="B3" s="8" t="inlineStr">
@@ -754,7 +1352,7 @@
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>サンプルラボA（新宿区新規ラボ想定）</t>
+          <t>新宿区新規ラボ（laidback cafeの例）</t>
         </is>
       </c>
       <c r="B4" s="9" t="inlineStr">
@@ -793,7 +1391,7 @@
         <f>IF(OR(J4="",H4=""),"",J4*H4)</f>
         <v/>
       </c>
-      <c r="L4" s="11">
+      <c r="L4" s="12">
         <f>IF(OR(J4="",I4=""),"",J4*I4)</f>
         <v/>
       </c>
@@ -801,7 +1399,7 @@
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>サンプルラボA（新宿区新規ラボ想定）</t>
+          <t>新宿区新規ラボ（laidback cafeの例）</t>
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr">
@@ -840,7 +1438,7 @@
         <f>IF(OR(J5="",H5=""),"",J5*H5)</f>
         <v/>
       </c>
-      <c r="L5" s="11">
+      <c r="L5" s="12">
         <f>IF(OR(J5="",I5=""),"",J5*I5)</f>
         <v/>
       </c>
@@ -848,7 +1446,7 @@
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>サンプルラボA（新宿区新規ラボ想定）</t>
+          <t>新宿区新規ラボ（laidback cafeの例）</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
@@ -885,7 +1483,7 @@
         <f>IF(OR(J6="",H6=""),"",J6*H6)</f>
         <v/>
       </c>
-      <c r="L6" s="11">
+      <c r="L6" s="12">
         <f>IF(OR(J6="",I6=""),"",J6*I6)</f>
         <v/>
       </c>
@@ -893,7 +1491,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>サンプルラボA（新宿区新規ラボ想定）</t>
+          <t>新宿区新規ラボ（laidback cafeの例）</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
@@ -930,7 +1528,7 @@
         <f>IF(OR(J7="",H7=""),"",J7*H7)</f>
         <v/>
       </c>
-      <c r="L7" s="11">
+      <c r="L7" s="12">
         <f>IF(OR(J7="",I7=""),"",J7*I7)</f>
         <v/>
       </c>
@@ -938,7 +1536,7 @@
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>サンプルラボA（新宿区新規ラボ想定）</t>
+          <t>新宿区新規ラボ（laidback cafeの例）</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
@@ -975,7 +1573,7 @@
         <f>IF(OR(J8="",H8=""),"",J8*H8)</f>
         <v/>
       </c>
-      <c r="L8" s="11">
+      <c r="L8" s="12">
         <f>IF(OR(J8="",I8=""),"",J8*I8)</f>
         <v/>
       </c>
@@ -983,7 +1581,7 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>サンプルラボA（新宿区新規ラボ想定）</t>
+          <t>新宿区新規ラボ（laidback cafeの例）</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
@@ -1018,7 +1616,7 @@
         <f>IF(OR(J9="",H9=""),"",J9*H9)</f>
         <v/>
       </c>
-      <c r="L9" s="11">
+      <c r="L9" s="12">
         <f>IF(OR(J9="",I9=""),"",J9*I9)</f>
         <v/>
       </c>
@@ -1026,7 +1624,7 @@
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>サンプルラボB（中野区の現ラボ想定）</t>
+          <t>中野区の現ラボの例</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
@@ -1067,7 +1665,7 @@
         <f>IF(OR(J10="",H10=""),"",J10*H10)</f>
         <v/>
       </c>
-      <c r="L10" s="11">
+      <c r="L10" s="12">
         <f>IF(OR(J10="",I10=""),"",J10*I10)</f>
         <v/>
       </c>
@@ -1075,7 +1673,7 @@
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>サンプルラボB（中野区の現ラボ想定）</t>
+          <t>中野区の現ラボの例</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
@@ -1116,21 +1714,21 @@
         <f>IF(OR(J11="",H11=""),"",J11*H11)</f>
         <v/>
       </c>
-      <c r="L11" s="11">
+      <c r="L11" s="12">
         <f>IF(OR(J11="",I11=""),"",J11*I11)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="n"/>
-      <c r="B12" s="12" t="n"/>
-      <c r="C12" s="12" t="n"/>
-      <c r="D12" s="12" t="n"/>
-      <c r="E12" s="12" t="n"/>
-      <c r="F12" s="12" t="n"/>
-      <c r="G12" s="12" t="n"/>
-      <c r="H12" s="12" t="n"/>
-      <c r="I12" s="12" t="n"/>
+      <c r="A12" s="11" t="n"/>
+      <c r="B12" s="11" t="n"/>
+      <c r="C12" s="11" t="n"/>
+      <c r="D12" s="11" t="n"/>
+      <c r="E12" s="11" t="n"/>
+      <c r="F12" s="11" t="n"/>
+      <c r="G12" s="11" t="n"/>
+      <c r="H12" s="11" t="n"/>
+      <c r="I12" s="11" t="n"/>
       <c r="J12" s="10">
         <f>IF(E12="","",IF(D12="日",(E12+F12)/2*G12,(E12+F12)/2)*$C$1)</f>
         <v/>
@@ -1139,21 +1737,21 @@
         <f>IF(OR(J12="",H12=""),"",J12*H12)</f>
         <v/>
       </c>
-      <c r="L12" s="11">
+      <c r="L12" s="12">
         <f>IF(OR(J12="",I12=""),"",J12*I12)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="n"/>
-      <c r="B13" s="12" t="n"/>
-      <c r="C13" s="12" t="n"/>
-      <c r="D13" s="12" t="n"/>
-      <c r="E13" s="12" t="n"/>
-      <c r="F13" s="12" t="n"/>
-      <c r="G13" s="12" t="n"/>
-      <c r="H13" s="12" t="n"/>
-      <c r="I13" s="12" t="n"/>
+      <c r="A13" s="11" t="n"/>
+      <c r="B13" s="11" t="n"/>
+      <c r="C13" s="11" t="n"/>
+      <c r="D13" s="11" t="n"/>
+      <c r="E13" s="11" t="n"/>
+      <c r="F13" s="11" t="n"/>
+      <c r="G13" s="11" t="n"/>
+      <c r="H13" s="11" t="n"/>
+      <c r="I13" s="11" t="n"/>
       <c r="J13" s="10">
         <f>IF(E13="","",IF(D13="日",(E13+F13)/2*G13,(E13+F13)/2)*$C$1)</f>
         <v/>
@@ -1162,21 +1760,21 @@
         <f>IF(OR(J13="",H13=""),"",J13*H13)</f>
         <v/>
       </c>
-      <c r="L13" s="11">
+      <c r="L13" s="12">
         <f>IF(OR(J13="",I13=""),"",J13*I13)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="n"/>
-      <c r="B14" s="12" t="n"/>
-      <c r="C14" s="12" t="n"/>
-      <c r="D14" s="12" t="n"/>
-      <c r="E14" s="12" t="n"/>
-      <c r="F14" s="12" t="n"/>
-      <c r="G14" s="12" t="n"/>
-      <c r="H14" s="12" t="n"/>
-      <c r="I14" s="12" t="n"/>
+      <c r="A14" s="11" t="n"/>
+      <c r="B14" s="11" t="n"/>
+      <c r="C14" s="11" t="n"/>
+      <c r="D14" s="11" t="n"/>
+      <c r="E14" s="11" t="n"/>
+      <c r="F14" s="11" t="n"/>
+      <c r="G14" s="11" t="n"/>
+      <c r="H14" s="11" t="n"/>
+      <c r="I14" s="11" t="n"/>
       <c r="J14" s="10">
         <f>IF(E14="","",IF(D14="日",(E14+F14)/2*G14,(E14+F14)/2)*$C$1)</f>
         <v/>
@@ -1185,21 +1783,21 @@
         <f>IF(OR(J14="",H14=""),"",J14*H14)</f>
         <v/>
       </c>
-      <c r="L14" s="11">
+      <c r="L14" s="12">
         <f>IF(OR(J14="",I14=""),"",J14*I14)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="n"/>
-      <c r="B15" s="12" t="n"/>
-      <c r="C15" s="12" t="n"/>
-      <c r="D15" s="12" t="n"/>
-      <c r="E15" s="12" t="n"/>
-      <c r="F15" s="12" t="n"/>
-      <c r="G15" s="12" t="n"/>
-      <c r="H15" s="12" t="n"/>
-      <c r="I15" s="12" t="n"/>
+      <c r="A15" s="11" t="n"/>
+      <c r="B15" s="11" t="n"/>
+      <c r="C15" s="11" t="n"/>
+      <c r="D15" s="11" t="n"/>
+      <c r="E15" s="11" t="n"/>
+      <c r="F15" s="11" t="n"/>
+      <c r="G15" s="11" t="n"/>
+      <c r="H15" s="11" t="n"/>
+      <c r="I15" s="11" t="n"/>
       <c r="J15" s="10">
         <f>IF(E15="","",IF(D15="日",(E15+F15)/2*G15,(E15+F15)/2)*$C$1)</f>
         <v/>
@@ -1208,21 +1806,21 @@
         <f>IF(OR(J15="",H15=""),"",J15*H15)</f>
         <v/>
       </c>
-      <c r="L15" s="11">
+      <c r="L15" s="12">
         <f>IF(OR(J15="",I15=""),"",J15*I15)</f>
         <v/>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="n"/>
-      <c r="B16" s="12" t="n"/>
-      <c r="C16" s="12" t="n"/>
-      <c r="D16" s="12" t="n"/>
-      <c r="E16" s="12" t="n"/>
-      <c r="F16" s="12" t="n"/>
-      <c r="G16" s="12" t="n"/>
-      <c r="H16" s="12" t="n"/>
-      <c r="I16" s="12" t="n"/>
+      <c r="A16" s="11" t="n"/>
+      <c r="B16" s="11" t="n"/>
+      <c r="C16" s="11" t="n"/>
+      <c r="D16" s="11" t="n"/>
+      <c r="E16" s="11" t="n"/>
+      <c r="F16" s="11" t="n"/>
+      <c r="G16" s="11" t="n"/>
+      <c r="H16" s="11" t="n"/>
+      <c r="I16" s="11" t="n"/>
       <c r="J16" s="10">
         <f>IF(E16="","",IF(D16="日",(E16+F16)/2*G16,(E16+F16)/2)*$C$1)</f>
         <v/>
@@ -1231,21 +1829,21 @@
         <f>IF(OR(J16="",H16=""),"",J16*H16)</f>
         <v/>
       </c>
-      <c r="L16" s="11">
+      <c r="L16" s="12">
         <f>IF(OR(J16="",I16=""),"",J16*I16)</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="12" t="n"/>
-      <c r="B17" s="12" t="n"/>
-      <c r="C17" s="12" t="n"/>
-      <c r="D17" s="12" t="n"/>
-      <c r="E17" s="12" t="n"/>
-      <c r="F17" s="12" t="n"/>
-      <c r="G17" s="12" t="n"/>
-      <c r="H17" s="12" t="n"/>
-      <c r="I17" s="12" t="n"/>
+      <c r="A17" s="11" t="n"/>
+      <c r="B17" s="11" t="n"/>
+      <c r="C17" s="11" t="n"/>
+      <c r="D17" s="11" t="n"/>
+      <c r="E17" s="11" t="n"/>
+      <c r="F17" s="11" t="n"/>
+      <c r="G17" s="11" t="n"/>
+      <c r="H17" s="11" t="n"/>
+      <c r="I17" s="11" t="n"/>
       <c r="J17" s="10">
         <f>IF(E17="","",IF(D17="日",(E17+F17)/2*G17,(E17+F17)/2)*$C$1)</f>
         <v/>
@@ -1254,21 +1852,21 @@
         <f>IF(OR(J17="",H17=""),"",J17*H17)</f>
         <v/>
       </c>
-      <c r="L17" s="11">
+      <c r="L17" s="12">
         <f>IF(OR(J17="",I17=""),"",J17*I17)</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="n"/>
-      <c r="B18" s="12" t="n"/>
-      <c r="C18" s="12" t="n"/>
-      <c r="D18" s="12" t="n"/>
-      <c r="E18" s="12" t="n"/>
-      <c r="F18" s="12" t="n"/>
-      <c r="G18" s="12" t="n"/>
-      <c r="H18" s="12" t="n"/>
-      <c r="I18" s="12" t="n"/>
+      <c r="A18" s="11" t="n"/>
+      <c r="B18" s="11" t="n"/>
+      <c r="C18" s="11" t="n"/>
+      <c r="D18" s="11" t="n"/>
+      <c r="E18" s="11" t="n"/>
+      <c r="F18" s="11" t="n"/>
+      <c r="G18" s="11" t="n"/>
+      <c r="H18" s="11" t="n"/>
+      <c r="I18" s="11" t="n"/>
       <c r="J18" s="10">
         <f>IF(E18="","",IF(D18="日",(E18+F18)/2*G18,(E18+F18)/2)*$C$1)</f>
         <v/>
@@ -1277,21 +1875,21 @@
         <f>IF(OR(J18="",H18=""),"",J18*H18)</f>
         <v/>
       </c>
-      <c r="L18" s="11">
+      <c r="L18" s="12">
         <f>IF(OR(J18="",I18=""),"",J18*I18)</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="12" t="n"/>
-      <c r="B19" s="12" t="n"/>
-      <c r="C19" s="12" t="n"/>
-      <c r="D19" s="12" t="n"/>
-      <c r="E19" s="12" t="n"/>
-      <c r="F19" s="12" t="n"/>
-      <c r="G19" s="12" t="n"/>
-      <c r="H19" s="12" t="n"/>
-      <c r="I19" s="12" t="n"/>
+      <c r="A19" s="11" t="n"/>
+      <c r="B19" s="11" t="n"/>
+      <c r="C19" s="11" t="n"/>
+      <c r="D19" s="11" t="n"/>
+      <c r="E19" s="11" t="n"/>
+      <c r="F19" s="11" t="n"/>
+      <c r="G19" s="11" t="n"/>
+      <c r="H19" s="11" t="n"/>
+      <c r="I19" s="11" t="n"/>
       <c r="J19" s="10">
         <f>IF(E19="","",IF(D19="日",(E19+F19)/2*G19,(E19+F19)/2)*$C$1)</f>
         <v/>
@@ -1300,21 +1898,21 @@
         <f>IF(OR(J19="",H19=""),"",J19*H19)</f>
         <v/>
       </c>
-      <c r="L19" s="11">
+      <c r="L19" s="12">
         <f>IF(OR(J19="",I19=""),"",J19*I19)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="n"/>
-      <c r="B20" s="12" t="n"/>
-      <c r="C20" s="12" t="n"/>
-      <c r="D20" s="12" t="n"/>
-      <c r="E20" s="12" t="n"/>
-      <c r="F20" s="12" t="n"/>
-      <c r="G20" s="12" t="n"/>
-      <c r="H20" s="12" t="n"/>
-      <c r="I20" s="12" t="n"/>
+      <c r="A20" s="11" t="n"/>
+      <c r="B20" s="11" t="n"/>
+      <c r="C20" s="11" t="n"/>
+      <c r="D20" s="11" t="n"/>
+      <c r="E20" s="11" t="n"/>
+      <c r="F20" s="11" t="n"/>
+      <c r="G20" s="11" t="n"/>
+      <c r="H20" s="11" t="n"/>
+      <c r="I20" s="11" t="n"/>
       <c r="J20" s="10">
         <f>IF(E20="","",IF(D20="日",(E20+F20)/2*G20,(E20+F20)/2)*$C$1)</f>
         <v/>
@@ -1323,21 +1921,21 @@
         <f>IF(OR(J20="",H20=""),"",J20*H20)</f>
         <v/>
       </c>
-      <c r="L20" s="11">
+      <c r="L20" s="12">
         <f>IF(OR(J20="",I20=""),"",J20*I20)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="12" t="n"/>
-      <c r="B21" s="12" t="n"/>
-      <c r="C21" s="12" t="n"/>
-      <c r="D21" s="12" t="n"/>
-      <c r="E21" s="12" t="n"/>
-      <c r="F21" s="12" t="n"/>
-      <c r="G21" s="12" t="n"/>
-      <c r="H21" s="12" t="n"/>
-      <c r="I21" s="12" t="n"/>
+      <c r="A21" s="11" t="n"/>
+      <c r="B21" s="11" t="n"/>
+      <c r="C21" s="11" t="n"/>
+      <c r="D21" s="11" t="n"/>
+      <c r="E21" s="11" t="n"/>
+      <c r="F21" s="11" t="n"/>
+      <c r="G21" s="11" t="n"/>
+      <c r="H21" s="11" t="n"/>
+      <c r="I21" s="11" t="n"/>
       <c r="J21" s="10">
         <f>IF(E21="","",IF(D21="日",(E21+F21)/2*G21,(E21+F21)/2)*$C$1)</f>
         <v/>
@@ -1346,21 +1944,21 @@
         <f>IF(OR(J21="",H21=""),"",J21*H21)</f>
         <v/>
       </c>
-      <c r="L21" s="11">
+      <c r="L21" s="12">
         <f>IF(OR(J21="",I21=""),"",J21*I21)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="12" t="n"/>
-      <c r="B22" s="12" t="n"/>
-      <c r="C22" s="12" t="n"/>
-      <c r="D22" s="12" t="n"/>
-      <c r="E22" s="12" t="n"/>
-      <c r="F22" s="12" t="n"/>
-      <c r="G22" s="12" t="n"/>
-      <c r="H22" s="12" t="n"/>
-      <c r="I22" s="12" t="n"/>
+      <c r="A22" s="11" t="n"/>
+      <c r="B22" s="11" t="n"/>
+      <c r="C22" s="11" t="n"/>
+      <c r="D22" s="11" t="n"/>
+      <c r="E22" s="11" t="n"/>
+      <c r="F22" s="11" t="n"/>
+      <c r="G22" s="11" t="n"/>
+      <c r="H22" s="11" t="n"/>
+      <c r="I22" s="11" t="n"/>
       <c r="J22" s="10">
         <f>IF(E22="","",IF(D22="日",(E22+F22)/2*G22,(E22+F22)/2)*$C$1)</f>
         <v/>
@@ -1369,21 +1967,21 @@
         <f>IF(OR(J22="",H22=""),"",J22*H22)</f>
         <v/>
       </c>
-      <c r="L22" s="11">
+      <c r="L22" s="12">
         <f>IF(OR(J22="",I22=""),"",J22*I22)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="12" t="n"/>
-      <c r="B23" s="12" t="n"/>
-      <c r="C23" s="12" t="n"/>
-      <c r="D23" s="12" t="n"/>
-      <c r="E23" s="12" t="n"/>
-      <c r="F23" s="12" t="n"/>
-      <c r="G23" s="12" t="n"/>
-      <c r="H23" s="12" t="n"/>
-      <c r="I23" s="12" t="n"/>
+      <c r="A23" s="11" t="n"/>
+      <c r="B23" s="11" t="n"/>
+      <c r="C23" s="11" t="n"/>
+      <c r="D23" s="11" t="n"/>
+      <c r="E23" s="11" t="n"/>
+      <c r="F23" s="11" t="n"/>
+      <c r="G23" s="11" t="n"/>
+      <c r="H23" s="11" t="n"/>
+      <c r="I23" s="11" t="n"/>
       <c r="J23" s="10">
         <f>IF(E23="","",IF(D23="日",(E23+F23)/2*G23,(E23+F23)/2)*$C$1)</f>
         <v/>
@@ -1392,21 +1990,21 @@
         <f>IF(OR(J23="",H23=""),"",J23*H23)</f>
         <v/>
       </c>
-      <c r="L23" s="11">
+      <c r="L23" s="12">
         <f>IF(OR(J23="",I23=""),"",J23*I23)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="n"/>
-      <c r="B24" s="12" t="n"/>
-      <c r="C24" s="12" t="n"/>
-      <c r="D24" s="12" t="n"/>
-      <c r="E24" s="12" t="n"/>
-      <c r="F24" s="12" t="n"/>
-      <c r="G24" s="12" t="n"/>
-      <c r="H24" s="12" t="n"/>
-      <c r="I24" s="12" t="n"/>
+      <c r="A24" s="11" t="n"/>
+      <c r="B24" s="11" t="n"/>
+      <c r="C24" s="11" t="n"/>
+      <c r="D24" s="11" t="n"/>
+      <c r="E24" s="11" t="n"/>
+      <c r="F24" s="11" t="n"/>
+      <c r="G24" s="11" t="n"/>
+      <c r="H24" s="11" t="n"/>
+      <c r="I24" s="11" t="n"/>
       <c r="J24" s="10">
         <f>IF(E24="","",IF(D24="日",(E24+F24)/2*G24,(E24+F24)/2)*$C$1)</f>
         <v/>
@@ -1415,21 +2013,21 @@
         <f>IF(OR(J24="",H24=""),"",J24*H24)</f>
         <v/>
       </c>
-      <c r="L24" s="11">
+      <c r="L24" s="12">
         <f>IF(OR(J24="",I24=""),"",J24*I24)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="n"/>
-      <c r="B25" s="12" t="n"/>
-      <c r="C25" s="12" t="n"/>
-      <c r="D25" s="12" t="n"/>
-      <c r="E25" s="12" t="n"/>
-      <c r="F25" s="12" t="n"/>
-      <c r="G25" s="12" t="n"/>
-      <c r="H25" s="12" t="n"/>
-      <c r="I25" s="12" t="n"/>
+      <c r="A25" s="11" t="n"/>
+      <c r="B25" s="11" t="n"/>
+      <c r="C25" s="11" t="n"/>
+      <c r="D25" s="11" t="n"/>
+      <c r="E25" s="11" t="n"/>
+      <c r="F25" s="11" t="n"/>
+      <c r="G25" s="11" t="n"/>
+      <c r="H25" s="11" t="n"/>
+      <c r="I25" s="11" t="n"/>
       <c r="J25" s="10">
         <f>IF(E25="","",IF(D25="日",(E25+F25)/2*G25,(E25+F25)/2)*$C$1)</f>
         <v/>
@@ -1438,21 +2036,21 @@
         <f>IF(OR(J25="",H25=""),"",J25*H25)</f>
         <v/>
       </c>
-      <c r="L25" s="11">
+      <c r="L25" s="12">
         <f>IF(OR(J25="",I25=""),"",J25*I25)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="12" t="n"/>
-      <c r="B26" s="12" t="n"/>
-      <c r="C26" s="12" t="n"/>
-      <c r="D26" s="12" t="n"/>
-      <c r="E26" s="12" t="n"/>
-      <c r="F26" s="12" t="n"/>
-      <c r="G26" s="12" t="n"/>
-      <c r="H26" s="12" t="n"/>
-      <c r="I26" s="12" t="n"/>
+      <c r="A26" s="11" t="n"/>
+      <c r="B26" s="11" t="n"/>
+      <c r="C26" s="11" t="n"/>
+      <c r="D26" s="11" t="n"/>
+      <c r="E26" s="11" t="n"/>
+      <c r="F26" s="11" t="n"/>
+      <c r="G26" s="11" t="n"/>
+      <c r="H26" s="11" t="n"/>
+      <c r="I26" s="11" t="n"/>
       <c r="J26" s="10">
         <f>IF(E26="","",IF(D26="日",(E26+F26)/2*G26,(E26+F26)/2)*$C$1)</f>
         <v/>
@@ -1461,21 +2059,21 @@
         <f>IF(OR(J26="",H26=""),"",J26*H26)</f>
         <v/>
       </c>
-      <c r="L26" s="11">
+      <c r="L26" s="12">
         <f>IF(OR(J26="",I26=""),"",J26*I26)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="12" t="n"/>
-      <c r="B27" s="12" t="n"/>
-      <c r="C27" s="12" t="n"/>
-      <c r="D27" s="12" t="n"/>
-      <c r="E27" s="12" t="n"/>
-      <c r="F27" s="12" t="n"/>
-      <c r="G27" s="12" t="n"/>
-      <c r="H27" s="12" t="n"/>
-      <c r="I27" s="12" t="n"/>
+      <c r="A27" s="11" t="n"/>
+      <c r="B27" s="11" t="n"/>
+      <c r="C27" s="11" t="n"/>
+      <c r="D27" s="11" t="n"/>
+      <c r="E27" s="11" t="n"/>
+      <c r="F27" s="11" t="n"/>
+      <c r="G27" s="11" t="n"/>
+      <c r="H27" s="11" t="n"/>
+      <c r="I27" s="11" t="n"/>
       <c r="J27" s="10">
         <f>IF(E27="","",IF(D27="日",(E27+F27)/2*G27,(E27+F27)/2)*$C$1)</f>
         <v/>
@@ -1484,21 +2082,21 @@
         <f>IF(OR(J27="",H27=""),"",J27*H27)</f>
         <v/>
       </c>
-      <c r="L27" s="11">
+      <c r="L27" s="12">
         <f>IF(OR(J27="",I27=""),"",J27*I27)</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="12" t="n"/>
-      <c r="B28" s="12" t="n"/>
-      <c r="C28" s="12" t="n"/>
-      <c r="D28" s="12" t="n"/>
-      <c r="E28" s="12" t="n"/>
-      <c r="F28" s="12" t="n"/>
-      <c r="G28" s="12" t="n"/>
-      <c r="H28" s="12" t="n"/>
-      <c r="I28" s="12" t="n"/>
+      <c r="A28" s="11" t="n"/>
+      <c r="B28" s="11" t="n"/>
+      <c r="C28" s="11" t="n"/>
+      <c r="D28" s="11" t="n"/>
+      <c r="E28" s="11" t="n"/>
+      <c r="F28" s="11" t="n"/>
+      <c r="G28" s="11" t="n"/>
+      <c r="H28" s="11" t="n"/>
+      <c r="I28" s="11" t="n"/>
       <c r="J28" s="10">
         <f>IF(E28="","",IF(D28="日",(E28+F28)/2*G28,(E28+F28)/2)*$C$1)</f>
         <v/>
@@ -1507,21 +2105,21 @@
         <f>IF(OR(J28="",H28=""),"",J28*H28)</f>
         <v/>
       </c>
-      <c r="L28" s="11">
+      <c r="L28" s="12">
         <f>IF(OR(J28="",I28=""),"",J28*I28)</f>
         <v/>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="12" t="n"/>
-      <c r="B29" s="12" t="n"/>
-      <c r="C29" s="12" t="n"/>
-      <c r="D29" s="12" t="n"/>
-      <c r="E29" s="12" t="n"/>
-      <c r="F29" s="12" t="n"/>
-      <c r="G29" s="12" t="n"/>
-      <c r="H29" s="12" t="n"/>
-      <c r="I29" s="12" t="n"/>
+      <c r="A29" s="11" t="n"/>
+      <c r="B29" s="11" t="n"/>
+      <c r="C29" s="11" t="n"/>
+      <c r="D29" s="11" t="n"/>
+      <c r="E29" s="11" t="n"/>
+      <c r="F29" s="11" t="n"/>
+      <c r="G29" s="11" t="n"/>
+      <c r="H29" s="11" t="n"/>
+      <c r="I29" s="11" t="n"/>
       <c r="J29" s="10">
         <f>IF(E29="","",IF(D29="日",(E29+F29)/2*G29,(E29+F29)/2)*$C$1)</f>
         <v/>
@@ -1530,21 +2128,21 @@
         <f>IF(OR(J29="",H29=""),"",J29*H29)</f>
         <v/>
       </c>
-      <c r="L29" s="11">
+      <c r="L29" s="12">
         <f>IF(OR(J29="",I29=""),"",J29*I29)</f>
         <v/>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="12" t="n"/>
-      <c r="B30" s="12" t="n"/>
-      <c r="C30" s="12" t="n"/>
-      <c r="D30" s="12" t="n"/>
-      <c r="E30" s="12" t="n"/>
-      <c r="F30" s="12" t="n"/>
-      <c r="G30" s="12" t="n"/>
-      <c r="H30" s="12" t="n"/>
-      <c r="I30" s="12" t="n"/>
+      <c r="A30" s="11" t="n"/>
+      <c r="B30" s="11" t="n"/>
+      <c r="C30" s="11" t="n"/>
+      <c r="D30" s="11" t="n"/>
+      <c r="E30" s="11" t="n"/>
+      <c r="F30" s="11" t="n"/>
+      <c r="G30" s="11" t="n"/>
+      <c r="H30" s="11" t="n"/>
+      <c r="I30" s="11" t="n"/>
       <c r="J30" s="10">
         <f>IF(E30="","",IF(D30="日",(E30+F30)/2*G30,(E30+F30)/2)*$C$1)</f>
         <v/>
@@ -1553,21 +2151,21 @@
         <f>IF(OR(J30="",H30=""),"",J30*H30)</f>
         <v/>
       </c>
-      <c r="L30" s="11">
+      <c r="L30" s="12">
         <f>IF(OR(J30="",I30=""),"",J30*I30)</f>
         <v/>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="12" t="n"/>
-      <c r="B31" s="12" t="n"/>
-      <c r="C31" s="12" t="n"/>
-      <c r="D31" s="12" t="n"/>
-      <c r="E31" s="12" t="n"/>
-      <c r="F31" s="12" t="n"/>
-      <c r="G31" s="12" t="n"/>
-      <c r="H31" s="12" t="n"/>
-      <c r="I31" s="12" t="n"/>
+      <c r="A31" s="11" t="n"/>
+      <c r="B31" s="11" t="n"/>
+      <c r="C31" s="11" t="n"/>
+      <c r="D31" s="11" t="n"/>
+      <c r="E31" s="11" t="n"/>
+      <c r="F31" s="11" t="n"/>
+      <c r="G31" s="11" t="n"/>
+      <c r="H31" s="11" t="n"/>
+      <c r="I31" s="11" t="n"/>
       <c r="J31" s="10">
         <f>IF(E31="","",IF(D31="日",(E31+F31)/2*G31,(E31+F31)/2)*$C$1)</f>
         <v/>
@@ -1576,21 +2174,21 @@
         <f>IF(OR(J31="",H31=""),"",J31*H31)</f>
         <v/>
       </c>
-      <c r="L31" s="11">
+      <c r="L31" s="12">
         <f>IF(OR(J31="",I31=""),"",J31*I31)</f>
         <v/>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="12" t="n"/>
-      <c r="B32" s="12" t="n"/>
-      <c r="C32" s="12" t="n"/>
-      <c r="D32" s="12" t="n"/>
-      <c r="E32" s="12" t="n"/>
-      <c r="F32" s="12" t="n"/>
-      <c r="G32" s="12" t="n"/>
-      <c r="H32" s="12" t="n"/>
-      <c r="I32" s="12" t="n"/>
+      <c r="A32" s="11" t="n"/>
+      <c r="B32" s="11" t="n"/>
+      <c r="C32" s="11" t="n"/>
+      <c r="D32" s="11" t="n"/>
+      <c r="E32" s="11" t="n"/>
+      <c r="F32" s="11" t="n"/>
+      <c r="G32" s="11" t="n"/>
+      <c r="H32" s="11" t="n"/>
+      <c r="I32" s="11" t="n"/>
       <c r="J32" s="10">
         <f>IF(E32="","",IF(D32="日",(E32+F32)/2*G32,(E32+F32)/2)*$C$1)</f>
         <v/>
@@ -1599,21 +2197,21 @@
         <f>IF(OR(J32="",H32=""),"",J32*H32)</f>
         <v/>
       </c>
-      <c r="L32" s="11">
+      <c r="L32" s="12">
         <f>IF(OR(J32="",I32=""),"",J32*I32)</f>
         <v/>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="12" t="n"/>
-      <c r="B33" s="12" t="n"/>
-      <c r="C33" s="12" t="n"/>
-      <c r="D33" s="12" t="n"/>
-      <c r="E33" s="12" t="n"/>
-      <c r="F33" s="12" t="n"/>
-      <c r="G33" s="12" t="n"/>
-      <c r="H33" s="12" t="n"/>
-      <c r="I33" s="12" t="n"/>
+      <c r="A33" s="11" t="n"/>
+      <c r="B33" s="11" t="n"/>
+      <c r="C33" s="11" t="n"/>
+      <c r="D33" s="11" t="n"/>
+      <c r="E33" s="11" t="n"/>
+      <c r="F33" s="11" t="n"/>
+      <c r="G33" s="11" t="n"/>
+      <c r="H33" s="11" t="n"/>
+      <c r="I33" s="11" t="n"/>
       <c r="J33" s="10">
         <f>IF(E33="","",IF(D33="日",(E33+F33)/2*G33,(E33+F33)/2)*$C$1)</f>
         <v/>
@@ -1622,21 +2220,21 @@
         <f>IF(OR(J33="",H33=""),"",J33*H33)</f>
         <v/>
       </c>
-      <c r="L33" s="11">
+      <c r="L33" s="12">
         <f>IF(OR(J33="",I33=""),"",J33*I33)</f>
         <v/>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="12" t="n"/>
-      <c r="B34" s="12" t="n"/>
-      <c r="C34" s="12" t="n"/>
-      <c r="D34" s="12" t="n"/>
-      <c r="E34" s="12" t="n"/>
-      <c r="F34" s="12" t="n"/>
-      <c r="G34" s="12" t="n"/>
-      <c r="H34" s="12" t="n"/>
-      <c r="I34" s="12" t="n"/>
+      <c r="A34" s="11" t="n"/>
+      <c r="B34" s="11" t="n"/>
+      <c r="C34" s="11" t="n"/>
+      <c r="D34" s="11" t="n"/>
+      <c r="E34" s="11" t="n"/>
+      <c r="F34" s="11" t="n"/>
+      <c r="G34" s="11" t="n"/>
+      <c r="H34" s="11" t="n"/>
+      <c r="I34" s="11" t="n"/>
       <c r="J34" s="10">
         <f>IF(E34="","",IF(D34="日",(E34+F34)/2*G34,(E34+F34)/2)*$C$1)</f>
         <v/>
@@ -1645,21 +2243,21 @@
         <f>IF(OR(J34="",H34=""),"",J34*H34)</f>
         <v/>
       </c>
-      <c r="L34" s="11">
+      <c r="L34" s="12">
         <f>IF(OR(J34="",I34=""),"",J34*I34)</f>
         <v/>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="12" t="n"/>
-      <c r="B35" s="12" t="n"/>
-      <c r="C35" s="12" t="n"/>
-      <c r="D35" s="12" t="n"/>
-      <c r="E35" s="12" t="n"/>
-      <c r="F35" s="12" t="n"/>
-      <c r="G35" s="12" t="n"/>
-      <c r="H35" s="12" t="n"/>
-      <c r="I35" s="12" t="n"/>
+      <c r="A35" s="11" t="n"/>
+      <c r="B35" s="11" t="n"/>
+      <c r="C35" s="11" t="n"/>
+      <c r="D35" s="11" t="n"/>
+      <c r="E35" s="11" t="n"/>
+      <c r="F35" s="11" t="n"/>
+      <c r="G35" s="11" t="n"/>
+      <c r="H35" s="11" t="n"/>
+      <c r="I35" s="11" t="n"/>
       <c r="J35" s="10">
         <f>IF(E35="","",IF(D35="日",(E35+F35)/2*G35,(E35+F35)/2)*$C$1)</f>
         <v/>
@@ -1668,21 +2266,21 @@
         <f>IF(OR(J35="",H35=""),"",J35*H35)</f>
         <v/>
       </c>
-      <c r="L35" s="11">
+      <c r="L35" s="12">
         <f>IF(OR(J35="",I35=""),"",J35*I35)</f>
         <v/>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="12" t="n"/>
-      <c r="B36" s="12" t="n"/>
-      <c r="C36" s="12" t="n"/>
-      <c r="D36" s="12" t="n"/>
-      <c r="E36" s="12" t="n"/>
-      <c r="F36" s="12" t="n"/>
-      <c r="G36" s="12" t="n"/>
-      <c r="H36" s="12" t="n"/>
-      <c r="I36" s="12" t="n"/>
+      <c r="A36" s="11" t="n"/>
+      <c r="B36" s="11" t="n"/>
+      <c r="C36" s="11" t="n"/>
+      <c r="D36" s="11" t="n"/>
+      <c r="E36" s="11" t="n"/>
+      <c r="F36" s="11" t="n"/>
+      <c r="G36" s="11" t="n"/>
+      <c r="H36" s="11" t="n"/>
+      <c r="I36" s="11" t="n"/>
       <c r="J36" s="10">
         <f>IF(E36="","",IF(D36="日",(E36+F36)/2*G36,(E36+F36)/2)*$C$1)</f>
         <v/>
@@ -1691,21 +2289,21 @@
         <f>IF(OR(J36="",H36=""),"",J36*H36)</f>
         <v/>
       </c>
-      <c r="L36" s="11">
+      <c r="L36" s="12">
         <f>IF(OR(J36="",I36=""),"",J36*I36)</f>
         <v/>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="12" t="n"/>
-      <c r="B37" s="12" t="n"/>
-      <c r="C37" s="12" t="n"/>
-      <c r="D37" s="12" t="n"/>
-      <c r="E37" s="12" t="n"/>
-      <c r="F37" s="12" t="n"/>
-      <c r="G37" s="12" t="n"/>
-      <c r="H37" s="12" t="n"/>
-      <c r="I37" s="12" t="n"/>
+      <c r="A37" s="11" t="n"/>
+      <c r="B37" s="11" t="n"/>
+      <c r="C37" s="11" t="n"/>
+      <c r="D37" s="11" t="n"/>
+      <c r="E37" s="11" t="n"/>
+      <c r="F37" s="11" t="n"/>
+      <c r="G37" s="11" t="n"/>
+      <c r="H37" s="11" t="n"/>
+      <c r="I37" s="11" t="n"/>
       <c r="J37" s="10">
         <f>IF(E37="","",IF(D37="日",(E37+F37)/2*G37,(E37+F37)/2)*$C$1)</f>
         <v/>
@@ -1714,21 +2312,21 @@
         <f>IF(OR(J37="",H37=""),"",J37*H37)</f>
         <v/>
       </c>
-      <c r="L37" s="11">
+      <c r="L37" s="12">
         <f>IF(OR(J37="",I37=""),"",J37*I37)</f>
         <v/>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="12" t="n"/>
-      <c r="B38" s="12" t="n"/>
-      <c r="C38" s="12" t="n"/>
-      <c r="D38" s="12" t="n"/>
-      <c r="E38" s="12" t="n"/>
-      <c r="F38" s="12" t="n"/>
-      <c r="G38" s="12" t="n"/>
-      <c r="H38" s="12" t="n"/>
-      <c r="I38" s="12" t="n"/>
+      <c r="A38" s="11" t="n"/>
+      <c r="B38" s="11" t="n"/>
+      <c r="C38" s="11" t="n"/>
+      <c r="D38" s="11" t="n"/>
+      <c r="E38" s="11" t="n"/>
+      <c r="F38" s="11" t="n"/>
+      <c r="G38" s="11" t="n"/>
+      <c r="H38" s="11" t="n"/>
+      <c r="I38" s="11" t="n"/>
       <c r="J38" s="10">
         <f>IF(E38="","",IF(D38="日",(E38+F38)/2*G38,(E38+F38)/2)*$C$1)</f>
         <v/>
@@ -1737,21 +2335,21 @@
         <f>IF(OR(J38="",H38=""),"",J38*H38)</f>
         <v/>
       </c>
-      <c r="L38" s="11">
+      <c r="L38" s="12">
         <f>IF(OR(J38="",I38=""),"",J38*I38)</f>
         <v/>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="12" t="n"/>
-      <c r="B39" s="12" t="n"/>
-      <c r="C39" s="12" t="n"/>
-      <c r="D39" s="12" t="n"/>
-      <c r="E39" s="12" t="n"/>
-      <c r="F39" s="12" t="n"/>
-      <c r="G39" s="12" t="n"/>
-      <c r="H39" s="12" t="n"/>
-      <c r="I39" s="12" t="n"/>
+      <c r="A39" s="11" t="n"/>
+      <c r="B39" s="11" t="n"/>
+      <c r="C39" s="11" t="n"/>
+      <c r="D39" s="11" t="n"/>
+      <c r="E39" s="11" t="n"/>
+      <c r="F39" s="11" t="n"/>
+      <c r="G39" s="11" t="n"/>
+      <c r="H39" s="11" t="n"/>
+      <c r="I39" s="11" t="n"/>
       <c r="J39" s="10">
         <f>IF(E39="","",IF(D39="日",(E39+F39)/2*G39,(E39+F39)/2)*$C$1)</f>
         <v/>
@@ -1760,21 +2358,21 @@
         <f>IF(OR(J39="",H39=""),"",J39*H39)</f>
         <v/>
       </c>
-      <c r="L39" s="11">
+      <c r="L39" s="12">
         <f>IF(OR(J39="",I39=""),"",J39*I39)</f>
         <v/>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="12" t="n"/>
-      <c r="B40" s="12" t="n"/>
-      <c r="C40" s="12" t="n"/>
-      <c r="D40" s="12" t="n"/>
-      <c r="E40" s="12" t="n"/>
-      <c r="F40" s="12" t="n"/>
-      <c r="G40" s="12" t="n"/>
-      <c r="H40" s="12" t="n"/>
-      <c r="I40" s="12" t="n"/>
+      <c r="A40" s="11" t="n"/>
+      <c r="B40" s="11" t="n"/>
+      <c r="C40" s="11" t="n"/>
+      <c r="D40" s="11" t="n"/>
+      <c r="E40" s="11" t="n"/>
+      <c r="F40" s="11" t="n"/>
+      <c r="G40" s="11" t="n"/>
+      <c r="H40" s="11" t="n"/>
+      <c r="I40" s="11" t="n"/>
       <c r="J40" s="10">
         <f>IF(E40="","",IF(D40="日",(E40+F40)/2*G40,(E40+F40)/2)*$C$1)</f>
         <v/>
@@ -1783,21 +2381,21 @@
         <f>IF(OR(J40="",H40=""),"",J40*H40)</f>
         <v/>
       </c>
-      <c r="L40" s="11">
+      <c r="L40" s="12">
         <f>IF(OR(J40="",I40=""),"",J40*I40)</f>
         <v/>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="12" t="n"/>
-      <c r="B41" s="12" t="n"/>
-      <c r="C41" s="12" t="n"/>
-      <c r="D41" s="12" t="n"/>
-      <c r="E41" s="12" t="n"/>
-      <c r="F41" s="12" t="n"/>
-      <c r="G41" s="12" t="n"/>
-      <c r="H41" s="12" t="n"/>
-      <c r="I41" s="12" t="n"/>
+      <c r="A41" s="11" t="n"/>
+      <c r="B41" s="11" t="n"/>
+      <c r="C41" s="11" t="n"/>
+      <c r="D41" s="11" t="n"/>
+      <c r="E41" s="11" t="n"/>
+      <c r="F41" s="11" t="n"/>
+      <c r="G41" s="11" t="n"/>
+      <c r="H41" s="11" t="n"/>
+      <c r="I41" s="11" t="n"/>
       <c r="J41" s="10">
         <f>IF(E41="","",IF(D41="日",(E41+F41)/2*G41,(E41+F41)/2)*$C$1)</f>
         <v/>
@@ -1806,21 +2404,21 @@
         <f>IF(OR(J41="",H41=""),"",J41*H41)</f>
         <v/>
       </c>
-      <c r="L41" s="11">
+      <c r="L41" s="12">
         <f>IF(OR(J41="",I41=""),"",J41*I41)</f>
         <v/>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="12" t="n"/>
-      <c r="B42" s="12" t="n"/>
-      <c r="C42" s="12" t="n"/>
-      <c r="D42" s="12" t="n"/>
-      <c r="E42" s="12" t="n"/>
-      <c r="F42" s="12" t="n"/>
-      <c r="G42" s="12" t="n"/>
-      <c r="H42" s="12" t="n"/>
-      <c r="I42" s="12" t="n"/>
+      <c r="A42" s="11" t="n"/>
+      <c r="B42" s="11" t="n"/>
+      <c r="C42" s="11" t="n"/>
+      <c r="D42" s="11" t="n"/>
+      <c r="E42" s="11" t="n"/>
+      <c r="F42" s="11" t="n"/>
+      <c r="G42" s="11" t="n"/>
+      <c r="H42" s="11" t="n"/>
+      <c r="I42" s="11" t="n"/>
       <c r="J42" s="10">
         <f>IF(E42="","",IF(D42="日",(E42+F42)/2*G42,(E42+F42)/2)*$C$1)</f>
         <v/>
@@ -1829,21 +2427,21 @@
         <f>IF(OR(J42="",H42=""),"",J42*H42)</f>
         <v/>
       </c>
-      <c r="L42" s="11">
+      <c r="L42" s="12">
         <f>IF(OR(J42="",I42=""),"",J42*I42)</f>
         <v/>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="12" t="n"/>
-      <c r="B43" s="12" t="n"/>
-      <c r="C43" s="12" t="n"/>
-      <c r="D43" s="12" t="n"/>
-      <c r="E43" s="12" t="n"/>
-      <c r="F43" s="12" t="n"/>
-      <c r="G43" s="12" t="n"/>
-      <c r="H43" s="12" t="n"/>
-      <c r="I43" s="12" t="n"/>
+      <c r="A43" s="11" t="n"/>
+      <c r="B43" s="11" t="n"/>
+      <c r="C43" s="11" t="n"/>
+      <c r="D43" s="11" t="n"/>
+      <c r="E43" s="11" t="n"/>
+      <c r="F43" s="11" t="n"/>
+      <c r="G43" s="11" t="n"/>
+      <c r="H43" s="11" t="n"/>
+      <c r="I43" s="11" t="n"/>
       <c r="J43" s="10">
         <f>IF(E43="","",IF(D43="日",(E43+F43)/2*G43,(E43+F43)/2)*$C$1)</f>
         <v/>
@@ -1852,7 +2450,7 @@
         <f>IF(OR(J43="",H43=""),"",J43*H43)</f>
         <v/>
       </c>
-      <c r="L43" s="11">
+      <c r="L43" s="12">
         <f>IF(OR(J43="",I43=""),"",J43*I43)</f>
         <v/>
       </c>
@@ -1871,762 +2469,4 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:K21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>収集ラボ間の比較表</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>「入力」シートに登録したラボ名を、下表のA列に入力シートと同じ表記で入力してください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
-        <is>
-          <t>ラボ名</t>
-        </is>
-      </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>可燃ごみ</t>
-        </is>
-      </c>
-      <c r="C4" s="8" t="inlineStr">
-        <is>
-          <t>生ごみ</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>不燃ごみ</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>瓶</t>
-        </is>
-      </c>
-      <c r="F4" s="8" t="inlineStr">
-        <is>
-          <t>缶</t>
-        </is>
-      </c>
-      <c r="G4" s="8" t="inlineStr">
-        <is>
-          <t>ペットボトル</t>
-        </is>
-      </c>
-      <c r="H4" s="8" t="inlineStr">
-        <is>
-          <t>段ボール</t>
-        </is>
-      </c>
-      <c r="I4" s="8" t="inlineStr">
-        <is>
-          <t>合計個数</t>
-        </is>
-      </c>
-      <c r="J4" s="8" t="inlineStr">
-        <is>
-          <t>合計容量(L)</t>
-        </is>
-      </c>
-      <c r="K4" s="8" t="inlineStr">
-        <is>
-          <t>概算料金合計(円)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>サンプルラボA（新宿区新規ラボ想定）</t>
-        </is>
-      </c>
-      <c r="B5" s="10">
-        <f>IF($A5="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A5,入力!$B$4:$B$43,B$4))</f>
-        <v/>
-      </c>
-      <c r="C5" s="10">
-        <f>IF($A5="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A5,入力!$B$4:$B$43,C$4))</f>
-        <v/>
-      </c>
-      <c r="D5" s="10">
-        <f>IF($A5="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A5,入力!$B$4:$B$43,D$4))</f>
-        <v/>
-      </c>
-      <c r="E5" s="10">
-        <f>IF($A5="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A5,入力!$B$4:$B$43,E$4))</f>
-        <v/>
-      </c>
-      <c r="F5" s="10">
-        <f>IF($A5="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A5,入力!$B$4:$B$43,F$4))</f>
-        <v/>
-      </c>
-      <c r="G5" s="10">
-        <f>IF($A5="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A5,入力!$B$4:$B$43,G$4))</f>
-        <v/>
-      </c>
-      <c r="H5" s="10">
-        <f>IF($A5="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A5,入力!$B$4:$B$43,H$4))</f>
-        <v/>
-      </c>
-      <c r="I5" s="11">
-        <f>IF($A5="","",SUMIF(入力!$A$4:$A$43,$A5,入力!$J$4:$J$43))</f>
-        <v/>
-      </c>
-      <c r="J5" s="11">
-        <f>IF($A5="","",SUMIF(入力!$A$4:$A$43,$A5,入力!$K$4:$K$43))</f>
-        <v/>
-      </c>
-      <c r="K5" s="11">
-        <f>IF($A5="","",SUMIF(入力!$A$4:$A$43,$A5,入力!$L$4:$L$43))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>サンプルラボB（中野区の現ラボ想定）</t>
-        </is>
-      </c>
-      <c r="B6" s="10">
-        <f>IF($A6="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A6,入力!$B$4:$B$43,B$4))</f>
-        <v/>
-      </c>
-      <c r="C6" s="10">
-        <f>IF($A6="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A6,入力!$B$4:$B$43,C$4))</f>
-        <v/>
-      </c>
-      <c r="D6" s="10">
-        <f>IF($A6="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A6,入力!$B$4:$B$43,D$4))</f>
-        <v/>
-      </c>
-      <c r="E6" s="10">
-        <f>IF($A6="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A6,入力!$B$4:$B$43,E$4))</f>
-        <v/>
-      </c>
-      <c r="F6" s="10">
-        <f>IF($A6="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A6,入力!$B$4:$B$43,F$4))</f>
-        <v/>
-      </c>
-      <c r="G6" s="10">
-        <f>IF($A6="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A6,入力!$B$4:$B$43,G$4))</f>
-        <v/>
-      </c>
-      <c r="H6" s="10">
-        <f>IF($A6="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A6,入力!$B$4:$B$43,H$4))</f>
-        <v/>
-      </c>
-      <c r="I6" s="11">
-        <f>IF($A6="","",SUMIF(入力!$A$4:$A$43,$A6,入力!$J$4:$J$43))</f>
-        <v/>
-      </c>
-      <c r="J6" s="11">
-        <f>IF($A6="","",SUMIF(入力!$A$4:$A$43,$A6,入力!$K$4:$K$43))</f>
-        <v/>
-      </c>
-      <c r="K6" s="11">
-        <f>IF($A6="","",SUMIF(入力!$A$4:$A$43,$A6,入力!$L$4:$L$43))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="12" t="n"/>
-      <c r="B7" s="10">
-        <f>IF($A7="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A7,入力!$B$4:$B$43,B$4))</f>
-        <v/>
-      </c>
-      <c r="C7" s="10">
-        <f>IF($A7="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A7,入力!$B$4:$B$43,C$4))</f>
-        <v/>
-      </c>
-      <c r="D7" s="10">
-        <f>IF($A7="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A7,入力!$B$4:$B$43,D$4))</f>
-        <v/>
-      </c>
-      <c r="E7" s="10">
-        <f>IF($A7="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A7,入力!$B$4:$B$43,E$4))</f>
-        <v/>
-      </c>
-      <c r="F7" s="10">
-        <f>IF($A7="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A7,入力!$B$4:$B$43,F$4))</f>
-        <v/>
-      </c>
-      <c r="G7" s="10">
-        <f>IF($A7="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A7,入力!$B$4:$B$43,G$4))</f>
-        <v/>
-      </c>
-      <c r="H7" s="10">
-        <f>IF($A7="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A7,入力!$B$4:$B$43,H$4))</f>
-        <v/>
-      </c>
-      <c r="I7" s="11">
-        <f>IF($A7="","",SUMIF(入力!$A$4:$A$43,$A7,入力!$J$4:$J$43))</f>
-        <v/>
-      </c>
-      <c r="J7" s="11">
-        <f>IF($A7="","",SUMIF(入力!$A$4:$A$43,$A7,入力!$K$4:$K$43))</f>
-        <v/>
-      </c>
-      <c r="K7" s="11">
-        <f>IF($A7="","",SUMIF(入力!$A$4:$A$43,$A7,入力!$L$4:$L$43))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="n"/>
-      <c r="B8" s="10">
-        <f>IF($A8="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A8,入力!$B$4:$B$43,B$4))</f>
-        <v/>
-      </c>
-      <c r="C8" s="10">
-        <f>IF($A8="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A8,入力!$B$4:$B$43,C$4))</f>
-        <v/>
-      </c>
-      <c r="D8" s="10">
-        <f>IF($A8="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A8,入力!$B$4:$B$43,D$4))</f>
-        <v/>
-      </c>
-      <c r="E8" s="10">
-        <f>IF($A8="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A8,入力!$B$4:$B$43,E$4))</f>
-        <v/>
-      </c>
-      <c r="F8" s="10">
-        <f>IF($A8="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A8,入力!$B$4:$B$43,F$4))</f>
-        <v/>
-      </c>
-      <c r="G8" s="10">
-        <f>IF($A8="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A8,入力!$B$4:$B$43,G$4))</f>
-        <v/>
-      </c>
-      <c r="H8" s="10">
-        <f>IF($A8="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A8,入力!$B$4:$B$43,H$4))</f>
-        <v/>
-      </c>
-      <c r="I8" s="11">
-        <f>IF($A8="","",SUMIF(入力!$A$4:$A$43,$A8,入力!$J$4:$J$43))</f>
-        <v/>
-      </c>
-      <c r="J8" s="11">
-        <f>IF($A8="","",SUMIF(入力!$A$4:$A$43,$A8,入力!$K$4:$K$43))</f>
-        <v/>
-      </c>
-      <c r="K8" s="11">
-        <f>IF($A8="","",SUMIF(入力!$A$4:$A$43,$A8,入力!$L$4:$L$43))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="12" t="n"/>
-      <c r="B9" s="10">
-        <f>IF($A9="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A9,入力!$B$4:$B$43,B$4))</f>
-        <v/>
-      </c>
-      <c r="C9" s="10">
-        <f>IF($A9="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A9,入力!$B$4:$B$43,C$4))</f>
-        <v/>
-      </c>
-      <c r="D9" s="10">
-        <f>IF($A9="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A9,入力!$B$4:$B$43,D$4))</f>
-        <v/>
-      </c>
-      <c r="E9" s="10">
-        <f>IF($A9="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A9,入力!$B$4:$B$43,E$4))</f>
-        <v/>
-      </c>
-      <c r="F9" s="10">
-        <f>IF($A9="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A9,入力!$B$4:$B$43,F$4))</f>
-        <v/>
-      </c>
-      <c r="G9" s="10">
-        <f>IF($A9="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A9,入力!$B$4:$B$43,G$4))</f>
-        <v/>
-      </c>
-      <c r="H9" s="10">
-        <f>IF($A9="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A9,入力!$B$4:$B$43,H$4))</f>
-        <v/>
-      </c>
-      <c r="I9" s="11">
-        <f>IF($A9="","",SUMIF(入力!$A$4:$A$43,$A9,入力!$J$4:$J$43))</f>
-        <v/>
-      </c>
-      <c r="J9" s="11">
-        <f>IF($A9="","",SUMIF(入力!$A$4:$A$43,$A9,入力!$K$4:$K$43))</f>
-        <v/>
-      </c>
-      <c r="K9" s="11">
-        <f>IF($A9="","",SUMIF(入力!$A$4:$A$43,$A9,入力!$L$4:$L$43))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="12" t="n"/>
-      <c r="B10" s="10">
-        <f>IF($A10="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A10,入力!$B$4:$B$43,B$4))</f>
-        <v/>
-      </c>
-      <c r="C10" s="10">
-        <f>IF($A10="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A10,入力!$B$4:$B$43,C$4))</f>
-        <v/>
-      </c>
-      <c r="D10" s="10">
-        <f>IF($A10="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A10,入力!$B$4:$B$43,D$4))</f>
-        <v/>
-      </c>
-      <c r="E10" s="10">
-        <f>IF($A10="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A10,入力!$B$4:$B$43,E$4))</f>
-        <v/>
-      </c>
-      <c r="F10" s="10">
-        <f>IF($A10="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A10,入力!$B$4:$B$43,F$4))</f>
-        <v/>
-      </c>
-      <c r="G10" s="10">
-        <f>IF($A10="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A10,入力!$B$4:$B$43,G$4))</f>
-        <v/>
-      </c>
-      <c r="H10" s="10">
-        <f>IF($A10="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A10,入力!$B$4:$B$43,H$4))</f>
-        <v/>
-      </c>
-      <c r="I10" s="11">
-        <f>IF($A10="","",SUMIF(入力!$A$4:$A$43,$A10,入力!$J$4:$J$43))</f>
-        <v/>
-      </c>
-      <c r="J10" s="11">
-        <f>IF($A10="","",SUMIF(入力!$A$4:$A$43,$A10,入力!$K$4:$K$43))</f>
-        <v/>
-      </c>
-      <c r="K10" s="11">
-        <f>IF($A10="","",SUMIF(入力!$A$4:$A$43,$A10,入力!$L$4:$L$43))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="12" t="n"/>
-      <c r="B11" s="10">
-        <f>IF($A11="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A11,入力!$B$4:$B$43,B$4))</f>
-        <v/>
-      </c>
-      <c r="C11" s="10">
-        <f>IF($A11="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A11,入力!$B$4:$B$43,C$4))</f>
-        <v/>
-      </c>
-      <c r="D11" s="10">
-        <f>IF($A11="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A11,入力!$B$4:$B$43,D$4))</f>
-        <v/>
-      </c>
-      <c r="E11" s="10">
-        <f>IF($A11="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A11,入力!$B$4:$B$43,E$4))</f>
-        <v/>
-      </c>
-      <c r="F11" s="10">
-        <f>IF($A11="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A11,入力!$B$4:$B$43,F$4))</f>
-        <v/>
-      </c>
-      <c r="G11" s="10">
-        <f>IF($A11="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A11,入力!$B$4:$B$43,G$4))</f>
-        <v/>
-      </c>
-      <c r="H11" s="10">
-        <f>IF($A11="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A11,入力!$B$4:$B$43,H$4))</f>
-        <v/>
-      </c>
-      <c r="I11" s="11">
-        <f>IF($A11="","",SUMIF(入力!$A$4:$A$43,$A11,入力!$J$4:$J$43))</f>
-        <v/>
-      </c>
-      <c r="J11" s="11">
-        <f>IF($A11="","",SUMIF(入力!$A$4:$A$43,$A11,入力!$K$4:$K$43))</f>
-        <v/>
-      </c>
-      <c r="K11" s="11">
-        <f>IF($A11="","",SUMIF(入力!$A$4:$A$43,$A11,入力!$L$4:$L$43))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="12" t="n"/>
-      <c r="B12" s="10">
-        <f>IF($A12="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A12,入力!$B$4:$B$43,B$4))</f>
-        <v/>
-      </c>
-      <c r="C12" s="10">
-        <f>IF($A12="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A12,入力!$B$4:$B$43,C$4))</f>
-        <v/>
-      </c>
-      <c r="D12" s="10">
-        <f>IF($A12="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A12,入力!$B$4:$B$43,D$4))</f>
-        <v/>
-      </c>
-      <c r="E12" s="10">
-        <f>IF($A12="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A12,入力!$B$4:$B$43,E$4))</f>
-        <v/>
-      </c>
-      <c r="F12" s="10">
-        <f>IF($A12="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A12,入力!$B$4:$B$43,F$4))</f>
-        <v/>
-      </c>
-      <c r="G12" s="10">
-        <f>IF($A12="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A12,入力!$B$4:$B$43,G$4))</f>
-        <v/>
-      </c>
-      <c r="H12" s="10">
-        <f>IF($A12="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A12,入力!$B$4:$B$43,H$4))</f>
-        <v/>
-      </c>
-      <c r="I12" s="11">
-        <f>IF($A12="","",SUMIF(入力!$A$4:$A$43,$A12,入力!$J$4:$J$43))</f>
-        <v/>
-      </c>
-      <c r="J12" s="11">
-        <f>IF($A12="","",SUMIF(入力!$A$4:$A$43,$A12,入力!$K$4:$K$43))</f>
-        <v/>
-      </c>
-      <c r="K12" s="11">
-        <f>IF($A12="","",SUMIF(入力!$A$4:$A$43,$A12,入力!$L$4:$L$43))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="12" t="n"/>
-      <c r="B13" s="10">
-        <f>IF($A13="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A13,入力!$B$4:$B$43,B$4))</f>
-        <v/>
-      </c>
-      <c r="C13" s="10">
-        <f>IF($A13="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A13,入力!$B$4:$B$43,C$4))</f>
-        <v/>
-      </c>
-      <c r="D13" s="10">
-        <f>IF($A13="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A13,入力!$B$4:$B$43,D$4))</f>
-        <v/>
-      </c>
-      <c r="E13" s="10">
-        <f>IF($A13="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A13,入力!$B$4:$B$43,E$4))</f>
-        <v/>
-      </c>
-      <c r="F13" s="10">
-        <f>IF($A13="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A13,入力!$B$4:$B$43,F$4))</f>
-        <v/>
-      </c>
-      <c r="G13" s="10">
-        <f>IF($A13="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A13,入力!$B$4:$B$43,G$4))</f>
-        <v/>
-      </c>
-      <c r="H13" s="10">
-        <f>IF($A13="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A13,入力!$B$4:$B$43,H$4))</f>
-        <v/>
-      </c>
-      <c r="I13" s="11">
-        <f>IF($A13="","",SUMIF(入力!$A$4:$A$43,$A13,入力!$J$4:$J$43))</f>
-        <v/>
-      </c>
-      <c r="J13" s="11">
-        <f>IF($A13="","",SUMIF(入力!$A$4:$A$43,$A13,入力!$K$4:$K$43))</f>
-        <v/>
-      </c>
-      <c r="K13" s="11">
-        <f>IF($A13="","",SUMIF(入力!$A$4:$A$43,$A13,入力!$L$4:$L$43))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="12" t="n"/>
-      <c r="B14" s="10">
-        <f>IF($A14="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A14,入力!$B$4:$B$43,B$4))</f>
-        <v/>
-      </c>
-      <c r="C14" s="10">
-        <f>IF($A14="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A14,入力!$B$4:$B$43,C$4))</f>
-        <v/>
-      </c>
-      <c r="D14" s="10">
-        <f>IF($A14="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A14,入力!$B$4:$B$43,D$4))</f>
-        <v/>
-      </c>
-      <c r="E14" s="10">
-        <f>IF($A14="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A14,入力!$B$4:$B$43,E$4))</f>
-        <v/>
-      </c>
-      <c r="F14" s="10">
-        <f>IF($A14="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A14,入力!$B$4:$B$43,F$4))</f>
-        <v/>
-      </c>
-      <c r="G14" s="10">
-        <f>IF($A14="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A14,入力!$B$4:$B$43,G$4))</f>
-        <v/>
-      </c>
-      <c r="H14" s="10">
-        <f>IF($A14="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A14,入力!$B$4:$B$43,H$4))</f>
-        <v/>
-      </c>
-      <c r="I14" s="11">
-        <f>IF($A14="","",SUMIF(入力!$A$4:$A$43,$A14,入力!$J$4:$J$43))</f>
-        <v/>
-      </c>
-      <c r="J14" s="11">
-        <f>IF($A14="","",SUMIF(入力!$A$4:$A$43,$A14,入力!$K$4:$K$43))</f>
-        <v/>
-      </c>
-      <c r="K14" s="11">
-        <f>IF($A14="","",SUMIF(入力!$A$4:$A$43,$A14,入力!$L$4:$L$43))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="12" t="n"/>
-      <c r="B15" s="10">
-        <f>IF($A15="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A15,入力!$B$4:$B$43,B$4))</f>
-        <v/>
-      </c>
-      <c r="C15" s="10">
-        <f>IF($A15="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A15,入力!$B$4:$B$43,C$4))</f>
-        <v/>
-      </c>
-      <c r="D15" s="10">
-        <f>IF($A15="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A15,入力!$B$4:$B$43,D$4))</f>
-        <v/>
-      </c>
-      <c r="E15" s="10">
-        <f>IF($A15="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A15,入力!$B$4:$B$43,E$4))</f>
-        <v/>
-      </c>
-      <c r="F15" s="10">
-        <f>IF($A15="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A15,入力!$B$4:$B$43,F$4))</f>
-        <v/>
-      </c>
-      <c r="G15" s="10">
-        <f>IF($A15="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A15,入力!$B$4:$B$43,G$4))</f>
-        <v/>
-      </c>
-      <c r="H15" s="10">
-        <f>IF($A15="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A15,入力!$B$4:$B$43,H$4))</f>
-        <v/>
-      </c>
-      <c r="I15" s="11">
-        <f>IF($A15="","",SUMIF(入力!$A$4:$A$43,$A15,入力!$J$4:$J$43))</f>
-        <v/>
-      </c>
-      <c r="J15" s="11">
-        <f>IF($A15="","",SUMIF(入力!$A$4:$A$43,$A15,入力!$K$4:$K$43))</f>
-        <v/>
-      </c>
-      <c r="K15" s="11">
-        <f>IF($A15="","",SUMIF(入力!$A$4:$A$43,$A15,入力!$L$4:$L$43))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="12" t="n"/>
-      <c r="B16" s="10">
-        <f>IF($A16="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A16,入力!$B$4:$B$43,B$4))</f>
-        <v/>
-      </c>
-      <c r="C16" s="10">
-        <f>IF($A16="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A16,入力!$B$4:$B$43,C$4))</f>
-        <v/>
-      </c>
-      <c r="D16" s="10">
-        <f>IF($A16="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A16,入力!$B$4:$B$43,D$4))</f>
-        <v/>
-      </c>
-      <c r="E16" s="10">
-        <f>IF($A16="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A16,入力!$B$4:$B$43,E$4))</f>
-        <v/>
-      </c>
-      <c r="F16" s="10">
-        <f>IF($A16="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A16,入力!$B$4:$B$43,F$4))</f>
-        <v/>
-      </c>
-      <c r="G16" s="10">
-        <f>IF($A16="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A16,入力!$B$4:$B$43,G$4))</f>
-        <v/>
-      </c>
-      <c r="H16" s="10">
-        <f>IF($A16="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A16,入力!$B$4:$B$43,H$4))</f>
-        <v/>
-      </c>
-      <c r="I16" s="11">
-        <f>IF($A16="","",SUMIF(入力!$A$4:$A$43,$A16,入力!$J$4:$J$43))</f>
-        <v/>
-      </c>
-      <c r="J16" s="11">
-        <f>IF($A16="","",SUMIF(入力!$A$4:$A$43,$A16,入力!$K$4:$K$43))</f>
-        <v/>
-      </c>
-      <c r="K16" s="11">
-        <f>IF($A16="","",SUMIF(入力!$A$4:$A$43,$A16,入力!$L$4:$L$43))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="12" t="n"/>
-      <c r="B17" s="10">
-        <f>IF($A17="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A17,入力!$B$4:$B$43,B$4))</f>
-        <v/>
-      </c>
-      <c r="C17" s="10">
-        <f>IF($A17="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A17,入力!$B$4:$B$43,C$4))</f>
-        <v/>
-      </c>
-      <c r="D17" s="10">
-        <f>IF($A17="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A17,入力!$B$4:$B$43,D$4))</f>
-        <v/>
-      </c>
-      <c r="E17" s="10">
-        <f>IF($A17="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A17,入力!$B$4:$B$43,E$4))</f>
-        <v/>
-      </c>
-      <c r="F17" s="10">
-        <f>IF($A17="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A17,入力!$B$4:$B$43,F$4))</f>
-        <v/>
-      </c>
-      <c r="G17" s="10">
-        <f>IF($A17="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A17,入力!$B$4:$B$43,G$4))</f>
-        <v/>
-      </c>
-      <c r="H17" s="10">
-        <f>IF($A17="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A17,入力!$B$4:$B$43,H$4))</f>
-        <v/>
-      </c>
-      <c r="I17" s="11">
-        <f>IF($A17="","",SUMIF(入力!$A$4:$A$43,$A17,入力!$J$4:$J$43))</f>
-        <v/>
-      </c>
-      <c r="J17" s="11">
-        <f>IF($A17="","",SUMIF(入力!$A$4:$A$43,$A17,入力!$K$4:$K$43))</f>
-        <v/>
-      </c>
-      <c r="K17" s="11">
-        <f>IF($A17="","",SUMIF(入力!$A$4:$A$43,$A17,入力!$L$4:$L$43))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="12" t="n"/>
-      <c r="B18" s="10">
-        <f>IF($A18="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A18,入力!$B$4:$B$43,B$4))</f>
-        <v/>
-      </c>
-      <c r="C18" s="10">
-        <f>IF($A18="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A18,入力!$B$4:$B$43,C$4))</f>
-        <v/>
-      </c>
-      <c r="D18" s="10">
-        <f>IF($A18="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A18,入力!$B$4:$B$43,D$4))</f>
-        <v/>
-      </c>
-      <c r="E18" s="10">
-        <f>IF($A18="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A18,入力!$B$4:$B$43,E$4))</f>
-        <v/>
-      </c>
-      <c r="F18" s="10">
-        <f>IF($A18="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A18,入力!$B$4:$B$43,F$4))</f>
-        <v/>
-      </c>
-      <c r="G18" s="10">
-        <f>IF($A18="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A18,入力!$B$4:$B$43,G$4))</f>
-        <v/>
-      </c>
-      <c r="H18" s="10">
-        <f>IF($A18="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A18,入力!$B$4:$B$43,H$4))</f>
-        <v/>
-      </c>
-      <c r="I18" s="11">
-        <f>IF($A18="","",SUMIF(入力!$A$4:$A$43,$A18,入力!$J$4:$J$43))</f>
-        <v/>
-      </c>
-      <c r="J18" s="11">
-        <f>IF($A18="","",SUMIF(入力!$A$4:$A$43,$A18,入力!$K$4:$K$43))</f>
-        <v/>
-      </c>
-      <c r="K18" s="11">
-        <f>IF($A18="","",SUMIF(入力!$A$4:$A$43,$A18,入力!$L$4:$L$43))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="12" t="n"/>
-      <c r="B19" s="10">
-        <f>IF($A19="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A19,入力!$B$4:$B$43,B$4))</f>
-        <v/>
-      </c>
-      <c r="C19" s="10">
-        <f>IF($A19="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A19,入力!$B$4:$B$43,C$4))</f>
-        <v/>
-      </c>
-      <c r="D19" s="10">
-        <f>IF($A19="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A19,入力!$B$4:$B$43,D$4))</f>
-        <v/>
-      </c>
-      <c r="E19" s="10">
-        <f>IF($A19="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A19,入力!$B$4:$B$43,E$4))</f>
-        <v/>
-      </c>
-      <c r="F19" s="10">
-        <f>IF($A19="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A19,入力!$B$4:$B$43,F$4))</f>
-        <v/>
-      </c>
-      <c r="G19" s="10">
-        <f>IF($A19="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A19,入力!$B$4:$B$43,G$4))</f>
-        <v/>
-      </c>
-      <c r="H19" s="10">
-        <f>IF($A19="","",SUMIFS(入力!$J$4:$J$43,入力!$A$4:$A$43,$A19,入力!$B$4:$B$43,H$4))</f>
-        <v/>
-      </c>
-      <c r="I19" s="11">
-        <f>IF($A19="","",SUMIF(入力!$A$4:$A$43,$A19,入力!$J$4:$J$43))</f>
-        <v/>
-      </c>
-      <c r="J19" s="11">
-        <f>IF($A19="","",SUMIF(入力!$A$4:$A$43,$A19,入力!$K$4:$K$43))</f>
-        <v/>
-      </c>
-      <c r="K19" s="11">
-        <f>IF($A19="","",SUMIF(入力!$A$4:$A$43,$A19,入力!$L$4:$L$43))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>※「その他」で登録した独自種別は比較表の集計対象外です（入力シートの月間量・容量・料金列を直接ご確認ください）。</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/waste-calculator/waste_calculator_template.xlsx
+++ b/waste-calculator/waste_calculator_template.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B18"/>
+  <dimension ref="B2:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -545,7 +545,7 @@
     <row r="7">
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>「詳細入力」：単位・袋サイズ・単価まで含めて月間容量や概算料金も試算したいとき。</t>
+          <t>「詳細入力」：単位・袋サイズ・重量・単価まで含めて月間容量や概算料金も試算したいとき。</t>
         </is>
       </c>
     </row>
@@ -590,31 +590,45 @@
     <row r="14">
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>・（詳細入力のみ）袋サイズ(L)：容量を計算したい場合のみ入力。単価(円)：概算料金を出したい場合のみ入力</t>
+          <t>・（詳細入力のみ）重量(kg/個)：料金計算のもとになる重量。45L≈5kg・70L≈8kgの実測値をもとにした目安を仮入力していますが、必要に応じて修正してください（段ボールは1枚≈0.3kgが目安）。</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="4" t="inlineStr"/>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>・（詳細入力のみ）単価(円/kg)：1kgあたりの料金。可燃40円・不燃100円・段ボール35円を仮入力済み（実際の契約単価に合わせて修正してください）</t>
+        </is>
+      </c>
     </row>
     <row r="16">
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B16" s="4" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>③ 前提</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>1ヶ月あたりの週数は各シートのC1セルで設定（既定値 4.35週 ＝ 365日 ÷ 12ヶ月 ÷ 7日）。</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="B18" s="4" t="inlineStr">
         <is>
+          <t>1ヶ月あたりの週数は各シートのC1セルで設定（既定値 4.35週 ＝ 365日 ÷ 12ヶ月 ÷ 7日）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="4" t="inlineStr">
+        <is>
           <t>数量が明記されていない項目（例:「不燃物 週2日」のみで数量記載なし）は 1回1袋 と仮定しています。実数が分かり次第、数量欄を修正してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>概算料金＝月間量×重量(kg/個)×単価(円/kg)で計算しています。重量が未入力の項目は料金計算から除外されます。</t>
         </is>
       </c>
     </row>
@@ -1255,7 +1269,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L43"/>
+  <dimension ref="A1:N43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1266,10 +1280,12 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
-    <col width="10" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1330,20 +1346,30 @@
       </c>
       <c r="I3" s="8" t="inlineStr">
         <is>
-          <t>単価(円)</t>
+          <t>重量(kg/個)</t>
         </is>
       </c>
       <c r="J3" s="8" t="inlineStr">
         <is>
+          <t>単価(円/kg)</t>
+        </is>
+      </c>
+      <c r="K3" s="8" t="inlineStr">
+        <is>
           <t>月間量(平均)</t>
         </is>
       </c>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="L3" s="8" t="inlineStr">
         <is>
           <t>月間容量(L)</t>
         </is>
       </c>
-      <c r="L3" s="8" t="inlineStr">
+      <c r="M3" s="8" t="inlineStr">
+        <is>
+          <t>月間重量(kg)</t>
+        </is>
+      </c>
+      <c r="N3" s="8" t="inlineStr">
         <is>
           <t>月間概算料金(円)</t>
         </is>
@@ -1382,17 +1408,26 @@
       <c r="H4" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="I4" s="9" t="inlineStr"/>
-      <c r="J4" s="10">
+      <c r="I4" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="J4" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="K4" s="10">
         <f>IF(E4="","",IF(D4="日",(E4+F4)/2*G4,(E4+F4)/2)*$C$1)</f>
         <v/>
       </c>
-      <c r="K4" s="10">
-        <f>IF(OR(J4="",H4=""),"",J4*H4)</f>
-        <v/>
-      </c>
-      <c r="L4" s="12">
-        <f>IF(OR(J4="",I4=""),"",J4*I4)</f>
+      <c r="L4" s="10">
+        <f>IF(OR(K4="",H4=""),"",K4*H4)</f>
+        <v/>
+      </c>
+      <c r="M4" s="10">
+        <f>IF(OR(K4="",I4=""),"",K4*I4)</f>
+        <v/>
+      </c>
+      <c r="N4" s="12">
+        <f>IF(OR(M4="",J4=""),"",M4*J4)</f>
         <v/>
       </c>
     </row>
@@ -1429,17 +1464,24 @@
       <c r="H5" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="I5" s="9" t="inlineStr"/>
-      <c r="J5" s="10">
+      <c r="I5" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="J5" s="9" t="inlineStr"/>
+      <c r="K5" s="10">
         <f>IF(E5="","",IF(D5="日",(E5+F5)/2*G5,(E5+F5)/2)*$C$1)</f>
         <v/>
       </c>
-      <c r="K5" s="10">
-        <f>IF(OR(J5="",H5=""),"",J5*H5)</f>
-        <v/>
-      </c>
-      <c r="L5" s="12">
-        <f>IF(OR(J5="",I5=""),"",J5*I5)</f>
+      <c r="L5" s="10">
+        <f>IF(OR(K5="",H5=""),"",K5*H5)</f>
+        <v/>
+      </c>
+      <c r="M5" s="10">
+        <f>IF(OR(K5="",I5=""),"",K5*I5)</f>
+        <v/>
+      </c>
+      <c r="N5" s="12">
+        <f>IF(OR(M5="",J5=""),"",M5*J5)</f>
         <v/>
       </c>
     </row>
@@ -1474,17 +1516,24 @@
       <c r="H6" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="I6" s="9" t="inlineStr"/>
-      <c r="J6" s="10">
+      <c r="I6" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="J6" s="9" t="inlineStr"/>
+      <c r="K6" s="10">
         <f>IF(E6="","",IF(D6="日",(E6+F6)/2*G6,(E6+F6)/2)*$C$1)</f>
         <v/>
       </c>
-      <c r="K6" s="10">
-        <f>IF(OR(J6="",H6=""),"",J6*H6)</f>
-        <v/>
-      </c>
-      <c r="L6" s="12">
-        <f>IF(OR(J6="",I6=""),"",J6*I6)</f>
+      <c r="L6" s="10">
+        <f>IF(OR(K6="",H6=""),"",K6*H6)</f>
+        <v/>
+      </c>
+      <c r="M6" s="10">
+        <f>IF(OR(K6="",I6=""),"",K6*I6)</f>
+        <v/>
+      </c>
+      <c r="N6" s="12">
+        <f>IF(OR(M6="",J6=""),"",M6*J6)</f>
         <v/>
       </c>
     </row>
@@ -1519,17 +1568,24 @@
       <c r="H7" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="I7" s="9" t="inlineStr"/>
-      <c r="J7" s="10">
+      <c r="I7" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="J7" s="9" t="inlineStr"/>
+      <c r="K7" s="10">
         <f>IF(E7="","",IF(D7="日",(E7+F7)/2*G7,(E7+F7)/2)*$C$1)</f>
         <v/>
       </c>
-      <c r="K7" s="10">
-        <f>IF(OR(J7="",H7=""),"",J7*H7)</f>
-        <v/>
-      </c>
-      <c r="L7" s="12">
-        <f>IF(OR(J7="",I7=""),"",J7*I7)</f>
+      <c r="L7" s="10">
+        <f>IF(OR(K7="",H7=""),"",K7*H7)</f>
+        <v/>
+      </c>
+      <c r="M7" s="10">
+        <f>IF(OR(K7="",I7=""),"",K7*I7)</f>
+        <v/>
+      </c>
+      <c r="N7" s="12">
+        <f>IF(OR(M7="",J7=""),"",M7*J7)</f>
         <v/>
       </c>
     </row>
@@ -1564,17 +1620,24 @@
       <c r="H8" s="9" t="n">
         <v>45</v>
       </c>
-      <c r="I8" s="9" t="inlineStr"/>
-      <c r="J8" s="10">
+      <c r="I8" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="J8" s="9" t="inlineStr"/>
+      <c r="K8" s="10">
         <f>IF(E8="","",IF(D8="日",(E8+F8)/2*G8,(E8+F8)/2)*$C$1)</f>
         <v/>
       </c>
-      <c r="K8" s="10">
-        <f>IF(OR(J8="",H8=""),"",J8*H8)</f>
-        <v/>
-      </c>
-      <c r="L8" s="12">
-        <f>IF(OR(J8="",I8=""),"",J8*I8)</f>
+      <c r="L8" s="10">
+        <f>IF(OR(K8="",H8=""),"",K8*H8)</f>
+        <v/>
+      </c>
+      <c r="M8" s="10">
+        <f>IF(OR(K8="",I8=""),"",K8*I8)</f>
+        <v/>
+      </c>
+      <c r="N8" s="12">
+        <f>IF(OR(M8="",J8=""),"",M8*J8)</f>
         <v/>
       </c>
     </row>
@@ -1607,17 +1670,26 @@
       </c>
       <c r="G9" s="9" t="inlineStr"/>
       <c r="H9" s="9" t="inlineStr"/>
-      <c r="I9" s="9" t="inlineStr"/>
-      <c r="J9" s="10">
+      <c r="I9" s="9" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J9" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="K9" s="10">
         <f>IF(E9="","",IF(D9="日",(E9+F9)/2*G9,(E9+F9)/2)*$C$1)</f>
         <v/>
       </c>
-      <c r="K9" s="10">
-        <f>IF(OR(J9="",H9=""),"",J9*H9)</f>
-        <v/>
-      </c>
-      <c r="L9" s="12">
-        <f>IF(OR(J9="",I9=""),"",J9*I9)</f>
+      <c r="L9" s="10">
+        <f>IF(OR(K9="",H9=""),"",K9*H9)</f>
+        <v/>
+      </c>
+      <c r="M9" s="10">
+        <f>IF(OR(K9="",I9=""),"",K9*I9)</f>
+        <v/>
+      </c>
+      <c r="N9" s="12">
+        <f>IF(OR(M9="",J9=""),"",M9*J9)</f>
         <v/>
       </c>
     </row>
@@ -1655,18 +1727,25 @@
         <v>45</v>
       </c>
       <c r="I10" s="9" t="n">
-        <v>120</v>
-      </c>
-      <c r="J10" s="10">
+        <v>5</v>
+      </c>
+      <c r="J10" s="9" t="n">
+        <v>40</v>
+      </c>
+      <c r="K10" s="10">
         <f>IF(E10="","",IF(D10="日",(E10+F10)/2*G10,(E10+F10)/2)*$C$1)</f>
         <v/>
       </c>
-      <c r="K10" s="10">
-        <f>IF(OR(J10="",H10=""),"",J10*H10)</f>
-        <v/>
-      </c>
-      <c r="L10" s="12">
-        <f>IF(OR(J10="",I10=""),"",J10*I10)</f>
+      <c r="L10" s="10">
+        <f>IF(OR(K10="",H10=""),"",K10*H10)</f>
+        <v/>
+      </c>
+      <c r="M10" s="10">
+        <f>IF(OR(K10="",I10=""),"",K10*I10)</f>
+        <v/>
+      </c>
+      <c r="N10" s="12">
+        <f>IF(OR(M10="",J10=""),"",M10*J10)</f>
         <v/>
       </c>
     </row>
@@ -1704,18 +1783,25 @@
         <v>45</v>
       </c>
       <c r="I11" s="9" t="n">
-        <v>120</v>
-      </c>
-      <c r="J11" s="10">
+        <v>5</v>
+      </c>
+      <c r="J11" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="K11" s="10">
         <f>IF(E11="","",IF(D11="日",(E11+F11)/2*G11,(E11+F11)/2)*$C$1)</f>
         <v/>
       </c>
-      <c r="K11" s="10">
-        <f>IF(OR(J11="",H11=""),"",J11*H11)</f>
-        <v/>
-      </c>
-      <c r="L11" s="12">
-        <f>IF(OR(J11="",I11=""),"",J11*I11)</f>
+      <c r="L11" s="10">
+        <f>IF(OR(K11="",H11=""),"",K11*H11)</f>
+        <v/>
+      </c>
+      <c r="M11" s="10">
+        <f>IF(OR(K11="",I11=""),"",K11*I11)</f>
+        <v/>
+      </c>
+      <c r="N11" s="12">
+        <f>IF(OR(M11="",J11=""),"",M11*J11)</f>
         <v/>
       </c>
     </row>
@@ -1729,16 +1815,21 @@
       <c r="G12" s="11" t="n"/>
       <c r="H12" s="11" t="n"/>
       <c r="I12" s="11" t="n"/>
-      <c r="J12" s="10">
+      <c r="J12" s="11" t="n"/>
+      <c r="K12" s="10">
         <f>IF(E12="","",IF(D12="日",(E12+F12)/2*G12,(E12+F12)/2)*$C$1)</f>
         <v/>
       </c>
-      <c r="K12" s="10">
-        <f>IF(OR(J12="",H12=""),"",J12*H12)</f>
-        <v/>
-      </c>
-      <c r="L12" s="12">
-        <f>IF(OR(J12="",I12=""),"",J12*I12)</f>
+      <c r="L12" s="10">
+        <f>IF(OR(K12="",H12=""),"",K12*H12)</f>
+        <v/>
+      </c>
+      <c r="M12" s="10">
+        <f>IF(OR(K12="",I12=""),"",K12*I12)</f>
+        <v/>
+      </c>
+      <c r="N12" s="12">
+        <f>IF(OR(M12="",J12=""),"",M12*J12)</f>
         <v/>
       </c>
     </row>
@@ -1752,16 +1843,21 @@
       <c r="G13" s="11" t="n"/>
       <c r="H13" s="11" t="n"/>
       <c r="I13" s="11" t="n"/>
-      <c r="J13" s="10">
+      <c r="J13" s="11" t="n"/>
+      <c r="K13" s="10">
         <f>IF(E13="","",IF(D13="日",(E13+F13)/2*G13,(E13+F13)/2)*$C$1)</f>
         <v/>
       </c>
-      <c r="K13" s="10">
-        <f>IF(OR(J13="",H13=""),"",J13*H13)</f>
-        <v/>
-      </c>
-      <c r="L13" s="12">
-        <f>IF(OR(J13="",I13=""),"",J13*I13)</f>
+      <c r="L13" s="10">
+        <f>IF(OR(K13="",H13=""),"",K13*H13)</f>
+        <v/>
+      </c>
+      <c r="M13" s="10">
+        <f>IF(OR(K13="",I13=""),"",K13*I13)</f>
+        <v/>
+      </c>
+      <c r="N13" s="12">
+        <f>IF(OR(M13="",J13=""),"",M13*J13)</f>
         <v/>
       </c>
     </row>
@@ -1775,16 +1871,21 @@
       <c r="G14" s="11" t="n"/>
       <c r="H14" s="11" t="n"/>
       <c r="I14" s="11" t="n"/>
-      <c r="J14" s="10">
+      <c r="J14" s="11" t="n"/>
+      <c r="K14" s="10">
         <f>IF(E14="","",IF(D14="日",(E14+F14)/2*G14,(E14+F14)/2)*$C$1)</f>
         <v/>
       </c>
-      <c r="K14" s="10">
-        <f>IF(OR(J14="",H14=""),"",J14*H14)</f>
-        <v/>
-      </c>
-      <c r="L14" s="12">
-        <f>IF(OR(J14="",I14=""),"",J14*I14)</f>
+      <c r="L14" s="10">
+        <f>IF(OR(K14="",H14=""),"",K14*H14)</f>
+        <v/>
+      </c>
+      <c r="M14" s="10">
+        <f>IF(OR(K14="",I14=""),"",K14*I14)</f>
+        <v/>
+      </c>
+      <c r="N14" s="12">
+        <f>IF(OR(M14="",J14=""),"",M14*J14)</f>
         <v/>
       </c>
     </row>
@@ -1798,16 +1899,21 @@
       <c r="G15" s="11" t="n"/>
       <c r="H15" s="11" t="n"/>
       <c r="I15" s="11" t="n"/>
-      <c r="J15" s="10">
+      <c r="J15" s="11" t="n"/>
+      <c r="K15" s="10">
         <f>IF(E15="","",IF(D15="日",(E15+F15)/2*G15,(E15+F15)/2)*$C$1)</f>
         <v/>
       </c>
-      <c r="K15" s="10">
-        <f>IF(OR(J15="",H15=""),"",J15*H15)</f>
-        <v/>
-      </c>
-      <c r="L15" s="12">
-        <f>IF(OR(J15="",I15=""),"",J15*I15)</f>
+      <c r="L15" s="10">
+        <f>IF(OR(K15="",H15=""),"",K15*H15)</f>
+        <v/>
+      </c>
+      <c r="M15" s="10">
+        <f>IF(OR(K15="",I15=""),"",K15*I15)</f>
+        <v/>
+      </c>
+      <c r="N15" s="12">
+        <f>IF(OR(M15="",J15=""),"",M15*J15)</f>
         <v/>
       </c>
     </row>
@@ -1821,16 +1927,21 @@
       <c r="G16" s="11" t="n"/>
       <c r="H16" s="11" t="n"/>
       <c r="I16" s="11" t="n"/>
-      <c r="J16" s="10">
+      <c r="J16" s="11" t="n"/>
+      <c r="K16" s="10">
         <f>IF(E16="","",IF(D16="日",(E16+F16)/2*G16,(E16+F16)/2)*$C$1)</f>
         <v/>
       </c>
-      <c r="K16" s="10">
-        <f>IF(OR(J16="",H16=""),"",J16*H16)</f>
-        <v/>
-      </c>
-      <c r="L16" s="12">
-        <f>IF(OR(J16="",I16=""),"",J16*I16)</f>
+      <c r="L16" s="10">
+        <f>IF(OR(K16="",H16=""),"",K16*H16)</f>
+        <v/>
+      </c>
+      <c r="M16" s="10">
+        <f>IF(OR(K16="",I16=""),"",K16*I16)</f>
+        <v/>
+      </c>
+      <c r="N16" s="12">
+        <f>IF(OR(M16="",J16=""),"",M16*J16)</f>
         <v/>
       </c>
     </row>
@@ -1844,16 +1955,21 @@
       <c r="G17" s="11" t="n"/>
       <c r="H17" s="11" t="n"/>
       <c r="I17" s="11" t="n"/>
-      <c r="J17" s="10">
+      <c r="J17" s="11" t="n"/>
+      <c r="K17" s="10">
         <f>IF(E17="","",IF(D17="日",(E17+F17)/2*G17,(E17+F17)/2)*$C$1)</f>
         <v/>
       </c>
-      <c r="K17" s="10">
-        <f>IF(OR(J17="",H17=""),"",J17*H17)</f>
-        <v/>
-      </c>
-      <c r="L17" s="12">
-        <f>IF(OR(J17="",I17=""),"",J17*I17)</f>
+      <c r="L17" s="10">
+        <f>IF(OR(K17="",H17=""),"",K17*H17)</f>
+        <v/>
+      </c>
+      <c r="M17" s="10">
+        <f>IF(OR(K17="",I17=""),"",K17*I17)</f>
+        <v/>
+      </c>
+      <c r="N17" s="12">
+        <f>IF(OR(M17="",J17=""),"",M17*J17)</f>
         <v/>
       </c>
     </row>
@@ -1867,16 +1983,21 @@
       <c r="G18" s="11" t="n"/>
       <c r="H18" s="11" t="n"/>
       <c r="I18" s="11" t="n"/>
-      <c r="J18" s="10">
+      <c r="J18" s="11" t="n"/>
+      <c r="K18" s="10">
         <f>IF(E18="","",IF(D18="日",(E18+F18)/2*G18,(E18+F18)/2)*$C$1)</f>
         <v/>
       </c>
-      <c r="K18" s="10">
-        <f>IF(OR(J18="",H18=""),"",J18*H18)</f>
-        <v/>
-      </c>
-      <c r="L18" s="12">
-        <f>IF(OR(J18="",I18=""),"",J18*I18)</f>
+      <c r="L18" s="10">
+        <f>IF(OR(K18="",H18=""),"",K18*H18)</f>
+        <v/>
+      </c>
+      <c r="M18" s="10">
+        <f>IF(OR(K18="",I18=""),"",K18*I18)</f>
+        <v/>
+      </c>
+      <c r="N18" s="12">
+        <f>IF(OR(M18="",J18=""),"",M18*J18)</f>
         <v/>
       </c>
     </row>
@@ -1890,16 +2011,21 @@
       <c r="G19" s="11" t="n"/>
       <c r="H19" s="11" t="n"/>
       <c r="I19" s="11" t="n"/>
-      <c r="J19" s="10">
+      <c r="J19" s="11" t="n"/>
+      <c r="K19" s="10">
         <f>IF(E19="","",IF(D19="日",(E19+F19)/2*G19,(E19+F19)/2)*$C$1)</f>
         <v/>
       </c>
-      <c r="K19" s="10">
-        <f>IF(OR(J19="",H19=""),"",J19*H19)</f>
-        <v/>
-      </c>
-      <c r="L19" s="12">
-        <f>IF(OR(J19="",I19=""),"",J19*I19)</f>
+      <c r="L19" s="10">
+        <f>IF(OR(K19="",H19=""),"",K19*H19)</f>
+        <v/>
+      </c>
+      <c r="M19" s="10">
+        <f>IF(OR(K19="",I19=""),"",K19*I19)</f>
+        <v/>
+      </c>
+      <c r="N19" s="12">
+        <f>IF(OR(M19="",J19=""),"",M19*J19)</f>
         <v/>
       </c>
     </row>
@@ -1913,16 +2039,21 @@
       <c r="G20" s="11" t="n"/>
       <c r="H20" s="11" t="n"/>
       <c r="I20" s="11" t="n"/>
-      <c r="J20" s="10">
+      <c r="J20" s="11" t="n"/>
+      <c r="K20" s="10">
         <f>IF(E20="","",IF(D20="日",(E20+F20)/2*G20,(E20+F20)/2)*$C$1)</f>
         <v/>
       </c>
-      <c r="K20" s="10">
-        <f>IF(OR(J20="",H20=""),"",J20*H20)</f>
-        <v/>
-      </c>
-      <c r="L20" s="12">
-        <f>IF(OR(J20="",I20=""),"",J20*I20)</f>
+      <c r="L20" s="10">
+        <f>IF(OR(K20="",H20=""),"",K20*H20)</f>
+        <v/>
+      </c>
+      <c r="M20" s="10">
+        <f>IF(OR(K20="",I20=""),"",K20*I20)</f>
+        <v/>
+      </c>
+      <c r="N20" s="12">
+        <f>IF(OR(M20="",J20=""),"",M20*J20)</f>
         <v/>
       </c>
     </row>
@@ -1936,16 +2067,21 @@
       <c r="G21" s="11" t="n"/>
       <c r="H21" s="11" t="n"/>
       <c r="I21" s="11" t="n"/>
-      <c r="J21" s="10">
+      <c r="J21" s="11" t="n"/>
+      <c r="K21" s="10">
         <f>IF(E21="","",IF(D21="日",(E21+F21)/2*G21,(E21+F21)/2)*$C$1)</f>
         <v/>
       </c>
-      <c r="K21" s="10">
-        <f>IF(OR(J21="",H21=""),"",J21*H21)</f>
-        <v/>
-      </c>
-      <c r="L21" s="12">
-        <f>IF(OR(J21="",I21=""),"",J21*I21)</f>
+      <c r="L21" s="10">
+        <f>IF(OR(K21="",H21=""),"",K21*H21)</f>
+        <v/>
+      </c>
+      <c r="M21" s="10">
+        <f>IF(OR(K21="",I21=""),"",K21*I21)</f>
+        <v/>
+      </c>
+      <c r="N21" s="12">
+        <f>IF(OR(M21="",J21=""),"",M21*J21)</f>
         <v/>
       </c>
     </row>
@@ -1959,16 +2095,21 @@
       <c r="G22" s="11" t="n"/>
       <c r="H22" s="11" t="n"/>
       <c r="I22" s="11" t="n"/>
-      <c r="J22" s="10">
+      <c r="J22" s="11" t="n"/>
+      <c r="K22" s="10">
         <f>IF(E22="","",IF(D22="日",(E22+F22)/2*G22,(E22+F22)/2)*$C$1)</f>
         <v/>
       </c>
-      <c r="K22" s="10">
-        <f>IF(OR(J22="",H22=""),"",J22*H22)</f>
-        <v/>
-      </c>
-      <c r="L22" s="12">
-        <f>IF(OR(J22="",I22=""),"",J22*I22)</f>
+      <c r="L22" s="10">
+        <f>IF(OR(K22="",H22=""),"",K22*H22)</f>
+        <v/>
+      </c>
+      <c r="M22" s="10">
+        <f>IF(OR(K22="",I22=""),"",K22*I22)</f>
+        <v/>
+      </c>
+      <c r="N22" s="12">
+        <f>IF(OR(M22="",J22=""),"",M22*J22)</f>
         <v/>
       </c>
     </row>
@@ -1982,16 +2123,21 @@
       <c r="G23" s="11" t="n"/>
       <c r="H23" s="11" t="n"/>
       <c r="I23" s="11" t="n"/>
-      <c r="J23" s="10">
+      <c r="J23" s="11" t="n"/>
+      <c r="K23" s="10">
         <f>IF(E23="","",IF(D23="日",(E23+F23)/2*G23,(E23+F23)/2)*$C$1)</f>
         <v/>
       </c>
-      <c r="K23" s="10">
-        <f>IF(OR(J23="",H23=""),"",J23*H23)</f>
-        <v/>
-      </c>
-      <c r="L23" s="12">
-        <f>IF(OR(J23="",I23=""),"",J23*I23)</f>
+      <c r="L23" s="10">
+        <f>IF(OR(K23="",H23=""),"",K23*H23)</f>
+        <v/>
+      </c>
+      <c r="M23" s="10">
+        <f>IF(OR(K23="",I23=""),"",K23*I23)</f>
+        <v/>
+      </c>
+      <c r="N23" s="12">
+        <f>IF(OR(M23="",J23=""),"",M23*J23)</f>
         <v/>
       </c>
     </row>
@@ -2005,16 +2151,21 @@
       <c r="G24" s="11" t="n"/>
       <c r="H24" s="11" t="n"/>
       <c r="I24" s="11" t="n"/>
-      <c r="J24" s="10">
+      <c r="J24" s="11" t="n"/>
+      <c r="K24" s="10">
         <f>IF(E24="","",IF(D24="日",(E24+F24)/2*G24,(E24+F24)/2)*$C$1)</f>
         <v/>
       </c>
-      <c r="K24" s="10">
-        <f>IF(OR(J24="",H24=""),"",J24*H24)</f>
-        <v/>
-      </c>
-      <c r="L24" s="12">
-        <f>IF(OR(J24="",I24=""),"",J24*I24)</f>
+      <c r="L24" s="10">
+        <f>IF(OR(K24="",H24=""),"",K24*H24)</f>
+        <v/>
+      </c>
+      <c r="M24" s="10">
+        <f>IF(OR(K24="",I24=""),"",K24*I24)</f>
+        <v/>
+      </c>
+      <c r="N24" s="12">
+        <f>IF(OR(M24="",J24=""),"",M24*J24)</f>
         <v/>
       </c>
     </row>
@@ -2028,16 +2179,21 @@
       <c r="G25" s="11" t="n"/>
       <c r="H25" s="11" t="n"/>
       <c r="I25" s="11" t="n"/>
-      <c r="J25" s="10">
+      <c r="J25" s="11" t="n"/>
+      <c r="K25" s="10">
         <f>IF(E25="","",IF(D25="日",(E25+F25)/2*G25,(E25+F25)/2)*$C$1)</f>
         <v/>
       </c>
-      <c r="K25" s="10">
-        <f>IF(OR(J25="",H25=""),"",J25*H25)</f>
-        <v/>
-      </c>
-      <c r="L25" s="12">
-        <f>IF(OR(J25="",I25=""),"",J25*I25)</f>
+      <c r="L25" s="10">
+        <f>IF(OR(K25="",H25=""),"",K25*H25)</f>
+        <v/>
+      </c>
+      <c r="M25" s="10">
+        <f>IF(OR(K25="",I25=""),"",K25*I25)</f>
+        <v/>
+      </c>
+      <c r="N25" s="12">
+        <f>IF(OR(M25="",J25=""),"",M25*J25)</f>
         <v/>
       </c>
     </row>
@@ -2051,16 +2207,21 @@
       <c r="G26" s="11" t="n"/>
       <c r="H26" s="11" t="n"/>
       <c r="I26" s="11" t="n"/>
-      <c r="J26" s="10">
+      <c r="J26" s="11" t="n"/>
+      <c r="K26" s="10">
         <f>IF(E26="","",IF(D26="日",(E26+F26)/2*G26,(E26+F26)/2)*$C$1)</f>
         <v/>
       </c>
-      <c r="K26" s="10">
-        <f>IF(OR(J26="",H26=""),"",J26*H26)</f>
-        <v/>
-      </c>
-      <c r="L26" s="12">
-        <f>IF(OR(J26="",I26=""),"",J26*I26)</f>
+      <c r="L26" s="10">
+        <f>IF(OR(K26="",H26=""),"",K26*H26)</f>
+        <v/>
+      </c>
+      <c r="M26" s="10">
+        <f>IF(OR(K26="",I26=""),"",K26*I26)</f>
+        <v/>
+      </c>
+      <c r="N26" s="12">
+        <f>IF(OR(M26="",J26=""),"",M26*J26)</f>
         <v/>
       </c>
     </row>
@@ -2074,16 +2235,21 @@
       <c r="G27" s="11" t="n"/>
       <c r="H27" s="11" t="n"/>
       <c r="I27" s="11" t="n"/>
-      <c r="J27" s="10">
+      <c r="J27" s="11" t="n"/>
+      <c r="K27" s="10">
         <f>IF(E27="","",IF(D27="日",(E27+F27)/2*G27,(E27+F27)/2)*$C$1)</f>
         <v/>
       </c>
-      <c r="K27" s="10">
-        <f>IF(OR(J27="",H27=""),"",J27*H27)</f>
-        <v/>
-      </c>
-      <c r="L27" s="12">
-        <f>IF(OR(J27="",I27=""),"",J27*I27)</f>
+      <c r="L27" s="10">
+        <f>IF(OR(K27="",H27=""),"",K27*H27)</f>
+        <v/>
+      </c>
+      <c r="M27" s="10">
+        <f>IF(OR(K27="",I27=""),"",K27*I27)</f>
+        <v/>
+      </c>
+      <c r="N27" s="12">
+        <f>IF(OR(M27="",J27=""),"",M27*J27)</f>
         <v/>
       </c>
     </row>
@@ -2097,16 +2263,21 @@
       <c r="G28" s="11" t="n"/>
       <c r="H28" s="11" t="n"/>
       <c r="I28" s="11" t="n"/>
-      <c r="J28" s="10">
+      <c r="J28" s="11" t="n"/>
+      <c r="K28" s="10">
         <f>IF(E28="","",IF(D28="日",(E28+F28)/2*G28,(E28+F28)/2)*$C$1)</f>
         <v/>
       </c>
-      <c r="K28" s="10">
-        <f>IF(OR(J28="",H28=""),"",J28*H28)</f>
-        <v/>
-      </c>
-      <c r="L28" s="12">
-        <f>IF(OR(J28="",I28=""),"",J28*I28)</f>
+      <c r="L28" s="10">
+        <f>IF(OR(K28="",H28=""),"",K28*H28)</f>
+        <v/>
+      </c>
+      <c r="M28" s="10">
+        <f>IF(OR(K28="",I28=""),"",K28*I28)</f>
+        <v/>
+      </c>
+      <c r="N28" s="12">
+        <f>IF(OR(M28="",J28=""),"",M28*J28)</f>
         <v/>
       </c>
     </row>
@@ -2120,16 +2291,21 @@
       <c r="G29" s="11" t="n"/>
       <c r="H29" s="11" t="n"/>
       <c r="I29" s="11" t="n"/>
-      <c r="J29" s="10">
+      <c r="J29" s="11" t="n"/>
+      <c r="K29" s="10">
         <f>IF(E29="","",IF(D29="日",(E29+F29)/2*G29,(E29+F29)/2)*$C$1)</f>
         <v/>
       </c>
-      <c r="K29" s="10">
-        <f>IF(OR(J29="",H29=""),"",J29*H29)</f>
-        <v/>
-      </c>
-      <c r="L29" s="12">
-        <f>IF(OR(J29="",I29=""),"",J29*I29)</f>
+      <c r="L29" s="10">
+        <f>IF(OR(K29="",H29=""),"",K29*H29)</f>
+        <v/>
+      </c>
+      <c r="M29" s="10">
+        <f>IF(OR(K29="",I29=""),"",K29*I29)</f>
+        <v/>
+      </c>
+      <c r="N29" s="12">
+        <f>IF(OR(M29="",J29=""),"",M29*J29)</f>
         <v/>
       </c>
     </row>
@@ -2143,16 +2319,21 @@
       <c r="G30" s="11" t="n"/>
       <c r="H30" s="11" t="n"/>
       <c r="I30" s="11" t="n"/>
-      <c r="J30" s="10">
+      <c r="J30" s="11" t="n"/>
+      <c r="K30" s="10">
         <f>IF(E30="","",IF(D30="日",(E30+F30)/2*G30,(E30+F30)/2)*$C$1)</f>
         <v/>
       </c>
-      <c r="K30" s="10">
-        <f>IF(OR(J30="",H30=""),"",J30*H30)</f>
-        <v/>
-      </c>
-      <c r="L30" s="12">
-        <f>IF(OR(J30="",I30=""),"",J30*I30)</f>
+      <c r="L30" s="10">
+        <f>IF(OR(K30="",H30=""),"",K30*H30)</f>
+        <v/>
+      </c>
+      <c r="M30" s="10">
+        <f>IF(OR(K30="",I30=""),"",K30*I30)</f>
+        <v/>
+      </c>
+      <c r="N30" s="12">
+        <f>IF(OR(M30="",J30=""),"",M30*J30)</f>
         <v/>
       </c>
     </row>
@@ -2166,16 +2347,21 @@
       <c r="G31" s="11" t="n"/>
       <c r="H31" s="11" t="n"/>
       <c r="I31" s="11" t="n"/>
-      <c r="J31" s="10">
+      <c r="J31" s="11" t="n"/>
+      <c r="K31" s="10">
         <f>IF(E31="","",IF(D31="日",(E31+F31)/2*G31,(E31+F31)/2)*$C$1)</f>
         <v/>
       </c>
-      <c r="K31" s="10">
-        <f>IF(OR(J31="",H31=""),"",J31*H31)</f>
-        <v/>
-      </c>
-      <c r="L31" s="12">
-        <f>IF(OR(J31="",I31=""),"",J31*I31)</f>
+      <c r="L31" s="10">
+        <f>IF(OR(K31="",H31=""),"",K31*H31)</f>
+        <v/>
+      </c>
+      <c r="M31" s="10">
+        <f>IF(OR(K31="",I31=""),"",K31*I31)</f>
+        <v/>
+      </c>
+      <c r="N31" s="12">
+        <f>IF(OR(M31="",J31=""),"",M31*J31)</f>
         <v/>
       </c>
     </row>
@@ -2189,16 +2375,21 @@
       <c r="G32" s="11" t="n"/>
       <c r="H32" s="11" t="n"/>
       <c r="I32" s="11" t="n"/>
-      <c r="J32" s="10">
+      <c r="J32" s="11" t="n"/>
+      <c r="K32" s="10">
         <f>IF(E32="","",IF(D32="日",(E32+F32)/2*G32,(E32+F32)/2)*$C$1)</f>
         <v/>
       </c>
-      <c r="K32" s="10">
-        <f>IF(OR(J32="",H32=""),"",J32*H32)</f>
-        <v/>
-      </c>
-      <c r="L32" s="12">
-        <f>IF(OR(J32="",I32=""),"",J32*I32)</f>
+      <c r="L32" s="10">
+        <f>IF(OR(K32="",H32=""),"",K32*H32)</f>
+        <v/>
+      </c>
+      <c r="M32" s="10">
+        <f>IF(OR(K32="",I32=""),"",K32*I32)</f>
+        <v/>
+      </c>
+      <c r="N32" s="12">
+        <f>IF(OR(M32="",J32=""),"",M32*J32)</f>
         <v/>
       </c>
     </row>
@@ -2212,16 +2403,21 @@
       <c r="G33" s="11" t="n"/>
       <c r="H33" s="11" t="n"/>
       <c r="I33" s="11" t="n"/>
-      <c r="J33" s="10">
+      <c r="J33" s="11" t="n"/>
+      <c r="K33" s="10">
         <f>IF(E33="","",IF(D33="日",(E33+F33)/2*G33,(E33+F33)/2)*$C$1)</f>
         <v/>
       </c>
-      <c r="K33" s="10">
-        <f>IF(OR(J33="",H33=""),"",J33*H33)</f>
-        <v/>
-      </c>
-      <c r="L33" s="12">
-        <f>IF(OR(J33="",I33=""),"",J33*I33)</f>
+      <c r="L33" s="10">
+        <f>IF(OR(K33="",H33=""),"",K33*H33)</f>
+        <v/>
+      </c>
+      <c r="M33" s="10">
+        <f>IF(OR(K33="",I33=""),"",K33*I33)</f>
+        <v/>
+      </c>
+      <c r="N33" s="12">
+        <f>IF(OR(M33="",J33=""),"",M33*J33)</f>
         <v/>
       </c>
     </row>
@@ -2235,16 +2431,21 @@
       <c r="G34" s="11" t="n"/>
       <c r="H34" s="11" t="n"/>
       <c r="I34" s="11" t="n"/>
-      <c r="J34" s="10">
+      <c r="J34" s="11" t="n"/>
+      <c r="K34" s="10">
         <f>IF(E34="","",IF(D34="日",(E34+F34)/2*G34,(E34+F34)/2)*$C$1)</f>
         <v/>
       </c>
-      <c r="K34" s="10">
-        <f>IF(OR(J34="",H34=""),"",J34*H34)</f>
-        <v/>
-      </c>
-      <c r="L34" s="12">
-        <f>IF(OR(J34="",I34=""),"",J34*I34)</f>
+      <c r="L34" s="10">
+        <f>IF(OR(K34="",H34=""),"",K34*H34)</f>
+        <v/>
+      </c>
+      <c r="M34" s="10">
+        <f>IF(OR(K34="",I34=""),"",K34*I34)</f>
+        <v/>
+      </c>
+      <c r="N34" s="12">
+        <f>IF(OR(M34="",J34=""),"",M34*J34)</f>
         <v/>
       </c>
     </row>
@@ -2258,16 +2459,21 @@
       <c r="G35" s="11" t="n"/>
       <c r="H35" s="11" t="n"/>
       <c r="I35" s="11" t="n"/>
-      <c r="J35" s="10">
+      <c r="J35" s="11" t="n"/>
+      <c r="K35" s="10">
         <f>IF(E35="","",IF(D35="日",(E35+F35)/2*G35,(E35+F35)/2)*$C$1)</f>
         <v/>
       </c>
-      <c r="K35" s="10">
-        <f>IF(OR(J35="",H35=""),"",J35*H35)</f>
-        <v/>
-      </c>
-      <c r="L35" s="12">
-        <f>IF(OR(J35="",I35=""),"",J35*I35)</f>
+      <c r="L35" s="10">
+        <f>IF(OR(K35="",H35=""),"",K35*H35)</f>
+        <v/>
+      </c>
+      <c r="M35" s="10">
+        <f>IF(OR(K35="",I35=""),"",K35*I35)</f>
+        <v/>
+      </c>
+      <c r="N35" s="12">
+        <f>IF(OR(M35="",J35=""),"",M35*J35)</f>
         <v/>
       </c>
     </row>
@@ -2281,16 +2487,21 @@
       <c r="G36" s="11" t="n"/>
       <c r="H36" s="11" t="n"/>
       <c r="I36" s="11" t="n"/>
-      <c r="J36" s="10">
+      <c r="J36" s="11" t="n"/>
+      <c r="K36" s="10">
         <f>IF(E36="","",IF(D36="日",(E36+F36)/2*G36,(E36+F36)/2)*$C$1)</f>
         <v/>
       </c>
-      <c r="K36" s="10">
-        <f>IF(OR(J36="",H36=""),"",J36*H36)</f>
-        <v/>
-      </c>
-      <c r="L36" s="12">
-        <f>IF(OR(J36="",I36=""),"",J36*I36)</f>
+      <c r="L36" s="10">
+        <f>IF(OR(K36="",H36=""),"",K36*H36)</f>
+        <v/>
+      </c>
+      <c r="M36" s="10">
+        <f>IF(OR(K36="",I36=""),"",K36*I36)</f>
+        <v/>
+      </c>
+      <c r="N36" s="12">
+        <f>IF(OR(M36="",J36=""),"",M36*J36)</f>
         <v/>
       </c>
     </row>
@@ -2304,16 +2515,21 @@
       <c r="G37" s="11" t="n"/>
       <c r="H37" s="11" t="n"/>
       <c r="I37" s="11" t="n"/>
-      <c r="J37" s="10">
+      <c r="J37" s="11" t="n"/>
+      <c r="K37" s="10">
         <f>IF(E37="","",IF(D37="日",(E37+F37)/2*G37,(E37+F37)/2)*$C$1)</f>
         <v/>
       </c>
-      <c r="K37" s="10">
-        <f>IF(OR(J37="",H37=""),"",J37*H37)</f>
-        <v/>
-      </c>
-      <c r="L37" s="12">
-        <f>IF(OR(J37="",I37=""),"",J37*I37)</f>
+      <c r="L37" s="10">
+        <f>IF(OR(K37="",H37=""),"",K37*H37)</f>
+        <v/>
+      </c>
+      <c r="M37" s="10">
+        <f>IF(OR(K37="",I37=""),"",K37*I37)</f>
+        <v/>
+      </c>
+      <c r="N37" s="12">
+        <f>IF(OR(M37="",J37=""),"",M37*J37)</f>
         <v/>
       </c>
     </row>
@@ -2327,16 +2543,21 @@
       <c r="G38" s="11" t="n"/>
       <c r="H38" s="11" t="n"/>
       <c r="I38" s="11" t="n"/>
-      <c r="J38" s="10">
+      <c r="J38" s="11" t="n"/>
+      <c r="K38" s="10">
         <f>IF(E38="","",IF(D38="日",(E38+F38)/2*G38,(E38+F38)/2)*$C$1)</f>
         <v/>
       </c>
-      <c r="K38" s="10">
-        <f>IF(OR(J38="",H38=""),"",J38*H38)</f>
-        <v/>
-      </c>
-      <c r="L38" s="12">
-        <f>IF(OR(J38="",I38=""),"",J38*I38)</f>
+      <c r="L38" s="10">
+        <f>IF(OR(K38="",H38=""),"",K38*H38)</f>
+        <v/>
+      </c>
+      <c r="M38" s="10">
+        <f>IF(OR(K38="",I38=""),"",K38*I38)</f>
+        <v/>
+      </c>
+      <c r="N38" s="12">
+        <f>IF(OR(M38="",J38=""),"",M38*J38)</f>
         <v/>
       </c>
     </row>
@@ -2350,16 +2571,21 @@
       <c r="G39" s="11" t="n"/>
       <c r="H39" s="11" t="n"/>
       <c r="I39" s="11" t="n"/>
-      <c r="J39" s="10">
+      <c r="J39" s="11" t="n"/>
+      <c r="K39" s="10">
         <f>IF(E39="","",IF(D39="日",(E39+F39)/2*G39,(E39+F39)/2)*$C$1)</f>
         <v/>
       </c>
-      <c r="K39" s="10">
-        <f>IF(OR(J39="",H39=""),"",J39*H39)</f>
-        <v/>
-      </c>
-      <c r="L39" s="12">
-        <f>IF(OR(J39="",I39=""),"",J39*I39)</f>
+      <c r="L39" s="10">
+        <f>IF(OR(K39="",H39=""),"",K39*H39)</f>
+        <v/>
+      </c>
+      <c r="M39" s="10">
+        <f>IF(OR(K39="",I39=""),"",K39*I39)</f>
+        <v/>
+      </c>
+      <c r="N39" s="12">
+        <f>IF(OR(M39="",J39=""),"",M39*J39)</f>
         <v/>
       </c>
     </row>
@@ -2373,16 +2599,21 @@
       <c r="G40" s="11" t="n"/>
       <c r="H40" s="11" t="n"/>
       <c r="I40" s="11" t="n"/>
-      <c r="J40" s="10">
+      <c r="J40" s="11" t="n"/>
+      <c r="K40" s="10">
         <f>IF(E40="","",IF(D40="日",(E40+F40)/2*G40,(E40+F40)/2)*$C$1)</f>
         <v/>
       </c>
-      <c r="K40" s="10">
-        <f>IF(OR(J40="",H40=""),"",J40*H40)</f>
-        <v/>
-      </c>
-      <c r="L40" s="12">
-        <f>IF(OR(J40="",I40=""),"",J40*I40)</f>
+      <c r="L40" s="10">
+        <f>IF(OR(K40="",H40=""),"",K40*H40)</f>
+        <v/>
+      </c>
+      <c r="M40" s="10">
+        <f>IF(OR(K40="",I40=""),"",K40*I40)</f>
+        <v/>
+      </c>
+      <c r="N40" s="12">
+        <f>IF(OR(M40="",J40=""),"",M40*J40)</f>
         <v/>
       </c>
     </row>
@@ -2396,16 +2627,21 @@
       <c r="G41" s="11" t="n"/>
       <c r="H41" s="11" t="n"/>
       <c r="I41" s="11" t="n"/>
-      <c r="J41" s="10">
+      <c r="J41" s="11" t="n"/>
+      <c r="K41" s="10">
         <f>IF(E41="","",IF(D41="日",(E41+F41)/2*G41,(E41+F41)/2)*$C$1)</f>
         <v/>
       </c>
-      <c r="K41" s="10">
-        <f>IF(OR(J41="",H41=""),"",J41*H41)</f>
-        <v/>
-      </c>
-      <c r="L41" s="12">
-        <f>IF(OR(J41="",I41=""),"",J41*I41)</f>
+      <c r="L41" s="10">
+        <f>IF(OR(K41="",H41=""),"",K41*H41)</f>
+        <v/>
+      </c>
+      <c r="M41" s="10">
+        <f>IF(OR(K41="",I41=""),"",K41*I41)</f>
+        <v/>
+      </c>
+      <c r="N41" s="12">
+        <f>IF(OR(M41="",J41=""),"",M41*J41)</f>
         <v/>
       </c>
     </row>
@@ -2419,16 +2655,21 @@
       <c r="G42" s="11" t="n"/>
       <c r="H42" s="11" t="n"/>
       <c r="I42" s="11" t="n"/>
-      <c r="J42" s="10">
+      <c r="J42" s="11" t="n"/>
+      <c r="K42" s="10">
         <f>IF(E42="","",IF(D42="日",(E42+F42)/2*G42,(E42+F42)/2)*$C$1)</f>
         <v/>
       </c>
-      <c r="K42" s="10">
-        <f>IF(OR(J42="",H42=""),"",J42*H42)</f>
-        <v/>
-      </c>
-      <c r="L42" s="12">
-        <f>IF(OR(J42="",I42=""),"",J42*I42)</f>
+      <c r="L42" s="10">
+        <f>IF(OR(K42="",H42=""),"",K42*H42)</f>
+        <v/>
+      </c>
+      <c r="M42" s="10">
+        <f>IF(OR(K42="",I42=""),"",K42*I42)</f>
+        <v/>
+      </c>
+      <c r="N42" s="12">
+        <f>IF(OR(M42="",J42=""),"",M42*J42)</f>
         <v/>
       </c>
     </row>
@@ -2442,16 +2683,21 @@
       <c r="G43" s="11" t="n"/>
       <c r="H43" s="11" t="n"/>
       <c r="I43" s="11" t="n"/>
-      <c r="J43" s="10">
+      <c r="J43" s="11" t="n"/>
+      <c r="K43" s="10">
         <f>IF(E43="","",IF(D43="日",(E43+F43)/2*G43,(E43+F43)/2)*$C$1)</f>
         <v/>
       </c>
-      <c r="K43" s="10">
-        <f>IF(OR(J43="",H43=""),"",J43*H43)</f>
-        <v/>
-      </c>
-      <c r="L43" s="12">
-        <f>IF(OR(J43="",I43=""),"",J43*I43)</f>
+      <c r="L43" s="10">
+        <f>IF(OR(K43="",H43=""),"",K43*H43)</f>
+        <v/>
+      </c>
+      <c r="M43" s="10">
+        <f>IF(OR(K43="",I43=""),"",K43*I43)</f>
+        <v/>
+      </c>
+      <c r="N43" s="12">
+        <f>IF(OR(M43="",J43=""),"",M43*J43)</f>
         <v/>
       </c>
     </row>

--- a/waste-calculator/waste_calculator_template.xlsx
+++ b/waste-calculator/waste_calculator_template.xlsx
@@ -569,7 +569,7 @@
     <row r="11">
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>・ラボ名（案件名）：案件ごとに分かる名前を入力（複数案件を1シートに並べてOK）</t>
+          <t>・案件名：案件ごとに分かる名前を入力（複数案件を1シートに並べてOK）</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>ラボ名（案件名）</t>
+          <t>案件名</t>
         </is>
       </c>
       <c r="B3" s="8" t="inlineStr">
@@ -704,7 +704,7 @@
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>新宿区新規ラボ（laidback cafeの例）</t>
+          <t>新宿区の新規案件（laidback cafeの例）</t>
         </is>
       </c>
       <c r="B4" s="9" t="inlineStr">
@@ -729,7 +729,7 @@
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>新宿区新規ラボ（laidback cafeの例）</t>
+          <t>新宿区の新規案件（laidback cafeの例）</t>
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr">
@@ -754,7 +754,7 @@
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>新宿区新規ラボ（laidback cafeの例）</t>
+          <t>新宿区の新規案件（laidback cafeの例）</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
@@ -779,7 +779,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>新宿区新規ラボ（laidback cafeの例）</t>
+          <t>新宿区の新規案件（laidback cafeの例）</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
@@ -804,7 +804,7 @@
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>新宿区新規ラボ（laidback cafeの例）</t>
+          <t>新宿区の新規案件（laidback cafeの例）</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
@@ -829,7 +829,7 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>新宿区新規ラボ（laidback cafeの例）</t>
+          <t>新宿区の新規案件（laidback cafeの例）</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
@@ -854,7 +854,7 @@
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>中野区の現ラボの例</t>
+          <t>中野区の現行案件の例</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
@@ -879,7 +879,7 @@
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>中野区の現ラボの例</t>
+          <t>中野区の現行案件の例</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">
@@ -1306,7 +1306,7 @@
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>ラボ名（案件名）</t>
+          <t>案件名</t>
         </is>
       </c>
       <c r="B3" s="8" t="inlineStr">
@@ -1378,7 +1378,7 @@
     <row r="4">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>新宿区新規ラボ（laidback cafeの例）</t>
+          <t>新宿区の新規案件（laidback cafeの例）</t>
         </is>
       </c>
       <c r="B4" s="9" t="inlineStr">
@@ -1434,7 +1434,7 @@
     <row r="5">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>新宿区新規ラボ（laidback cafeの例）</t>
+          <t>新宿区の新規案件（laidback cafeの例）</t>
         </is>
       </c>
       <c r="B5" s="9" t="inlineStr">
@@ -1488,7 +1488,7 @@
     <row r="6">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>新宿区新規ラボ（laidback cafeの例）</t>
+          <t>新宿区の新規案件（laidback cafeの例）</t>
         </is>
       </c>
       <c r="B6" s="9" t="inlineStr">
@@ -1540,7 +1540,7 @@
     <row r="7">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>新宿区新規ラボ（laidback cafeの例）</t>
+          <t>新宿区の新規案件（laidback cafeの例）</t>
         </is>
       </c>
       <c r="B7" s="9" t="inlineStr">
@@ -1592,7 +1592,7 @@
     <row r="8">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>新宿区新規ラボ（laidback cafeの例）</t>
+          <t>新宿区の新規案件（laidback cafeの例）</t>
         </is>
       </c>
       <c r="B8" s="9" t="inlineStr">
@@ -1644,7 +1644,7 @@
     <row r="9">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>新宿区新規ラボ（laidback cafeの例）</t>
+          <t>新宿区の新規案件（laidback cafeの例）</t>
         </is>
       </c>
       <c r="B9" s="9" t="inlineStr">
@@ -1696,7 +1696,7 @@
     <row r="10">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>中野区の現ラボの例</t>
+          <t>中野区の現行案件の例</t>
         </is>
       </c>
       <c r="B10" s="9" t="inlineStr">
@@ -1752,7 +1752,7 @@
     <row r="11">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>中野区の現ラボの例</t>
+          <t>中野区の現行案件の例</t>
         </is>
       </c>
       <c r="B11" s="9" t="inlineStr">

--- a/waste-calculator/waste_calculator_template.xlsx
+++ b/waste-calculator/waste_calculator_template.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B20"/>
+  <dimension ref="B2:B22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -590,45 +590,59 @@
     <row r="14">
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>・（詳細入力のみ）重量(kg/個)：料金計算のもとになる重量。45L≈5kg・70L≈8kgの実測値をもとにした目安を仮入力していますが、必要に応じて修正してください（段ボールは1枚≈0.3kgが目安）。</t>
+          <t>・数量min／数量max：「1〜2袋」のように幅がある場合は両方入力。「2袋」のように1つだけの場合は数量maxを空欄にすればOK（数量minの値だけで計算されます）。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="4" t="inlineStr">
         <is>
+          <t>・（詳細入力のみ）重量(kg/個)：料金計算のもとになる重量。45L≈5kg・70L≈8kgの実測値をもとにした目安を仮入力していますが、必要に応じて修正してください（段ボールは1枚≈0.3kgが目安）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="4" t="inlineStr">
+        <is>
           <t>・（詳細入力のみ）単価(円/kg)：1kgあたりの料金。可燃40円・不燃100円・段ボール35円を仮入力済み（実際の契約単価に合わせて修正してください）</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="B16" s="4" t="inlineStr"/>
-    </row>
     <row r="17">
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B17" s="4" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>③ 前提</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="4" t="inlineStr">
-        <is>
-          <t>1ヶ月あたりの週数は各シートのC1セルで設定（既定値 4.35週 ＝ 365日 ÷ 12ヶ月 ÷ 7日）。</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>数量が明記されていない項目（例:「不燃物 週2日」のみで数量記載なし）は 1回1袋 と仮定しています。実数が分かり次第、数量欄を修正してください。</t>
+          <t>1ヶ月あたりの週数は各シートのC1セルで設定（既定値 4.35週 ＝ 365日 ÷ 12ヶ月 ÷ 7日）。</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="4" t="inlineStr">
         <is>
+          <t>数量が明記されていない項目（例:「不燃物 週2日」のみで数量記載なし）は 1回1袋 と仮定しています。実数が分かり次第、数量欄を修正してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="4" t="inlineStr">
+        <is>
           <t>概算料金＝月間量×重量(kg/個)×単価(円/kg)で計算しています。重量が未入力の項目は料金計算から除外されます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>初回手数料（詳細入力シートC2セル、既定 ¥3,000）は新規契約の案件ごとに一律で加算する費用です。ご提示金額＝その案件の月間概算料金の合計＋初回手数料、として手動で合算してください。</t>
         </is>
       </c>
     </row>
@@ -722,7 +736,7 @@
         <v>7</v>
       </c>
       <c r="F4" s="10">
-        <f>IF(C4="","",(C4+D4)/2*E4*$C$1)</f>
+        <f>IF(C4="","",IF(D4="",C4,(C4+D4)/2)*E4*$C$1)</f>
         <v/>
       </c>
     </row>
@@ -747,7 +761,7 @@
         <v>7</v>
       </c>
       <c r="F5" s="10">
-        <f>IF(C5="","",(C5+D5)/2*E5*$C$1)</f>
+        <f>IF(C5="","",IF(D5="",C5,(C5+D5)/2)*E5*$C$1)</f>
         <v/>
       </c>
     </row>
@@ -772,7 +786,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="10">
-        <f>IF(C6="","",(C6+D6)/2*E6*$C$1)</f>
+        <f>IF(C6="","",IF(D6="",C6,(C6+D6)/2)*E6*$C$1)</f>
         <v/>
       </c>
     </row>
@@ -797,7 +811,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="10">
-        <f>IF(C7="","",(C7+D7)/2*E7*$C$1)</f>
+        <f>IF(C7="","",IF(D7="",C7,(C7+D7)/2)*E7*$C$1)</f>
         <v/>
       </c>
     </row>
@@ -822,7 +836,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="10">
-        <f>IF(C8="","",(C8+D8)/2*E8*$C$1)</f>
+        <f>IF(C8="","",IF(D8="",C8,(C8+D8)/2)*E8*$C$1)</f>
         <v/>
       </c>
     </row>
@@ -847,7 +861,7 @@
         <v>1</v>
       </c>
       <c r="F9" s="10">
-        <f>IF(C9="","",(C9+D9)/2*E9*$C$1)</f>
+        <f>IF(C9="","",IF(D9="",C9,(C9+D9)/2)*E9*$C$1)</f>
         <v/>
       </c>
     </row>
@@ -872,7 +886,7 @@
         <v>5</v>
       </c>
       <c r="F10" s="10">
-        <f>IF(C10="","",(C10+D10)/2*E10*$C$1)</f>
+        <f>IF(C10="","",IF(D10="",C10,(C10+D10)/2)*E10*$C$1)</f>
         <v/>
       </c>
     </row>
@@ -897,7 +911,7 @@
         <v>2</v>
       </c>
       <c r="F11" s="10">
-        <f>IF(C11="","",(C11+D11)/2*E11*$C$1)</f>
+        <f>IF(C11="","",IF(D11="",C11,(C11+D11)/2)*E11*$C$1)</f>
         <v/>
       </c>
     </row>
@@ -908,7 +922,7 @@
       <c r="D12" s="11" t="n"/>
       <c r="E12" s="11" t="n"/>
       <c r="F12" s="10">
-        <f>IF(C12="","",(C12+D12)/2*E12*$C$1)</f>
+        <f>IF(C12="","",IF(D12="",C12,(C12+D12)/2)*E12*$C$1)</f>
         <v/>
       </c>
     </row>
@@ -919,7 +933,7 @@
       <c r="D13" s="11" t="n"/>
       <c r="E13" s="11" t="n"/>
       <c r="F13" s="10">
-        <f>IF(C13="","",(C13+D13)/2*E13*$C$1)</f>
+        <f>IF(C13="","",IF(D13="",C13,(C13+D13)/2)*E13*$C$1)</f>
         <v/>
       </c>
     </row>
@@ -930,7 +944,7 @@
       <c r="D14" s="11" t="n"/>
       <c r="E14" s="11" t="n"/>
       <c r="F14" s="10">
-        <f>IF(C14="","",(C14+D14)/2*E14*$C$1)</f>
+        <f>IF(C14="","",IF(D14="",C14,(C14+D14)/2)*E14*$C$1)</f>
         <v/>
       </c>
     </row>
@@ -941,7 +955,7 @@
       <c r="D15" s="11" t="n"/>
       <c r="E15" s="11" t="n"/>
       <c r="F15" s="10">
-        <f>IF(C15="","",(C15+D15)/2*E15*$C$1)</f>
+        <f>IF(C15="","",IF(D15="",C15,(C15+D15)/2)*E15*$C$1)</f>
         <v/>
       </c>
     </row>
@@ -952,7 +966,7 @@
       <c r="D16" s="11" t="n"/>
       <c r="E16" s="11" t="n"/>
       <c r="F16" s="10">
-        <f>IF(C16="","",(C16+D16)/2*E16*$C$1)</f>
+        <f>IF(C16="","",IF(D16="",C16,(C16+D16)/2)*E16*$C$1)</f>
         <v/>
       </c>
     </row>
@@ -963,7 +977,7 @@
       <c r="D17" s="11" t="n"/>
       <c r="E17" s="11" t="n"/>
       <c r="F17" s="10">
-        <f>IF(C17="","",(C17+D17)/2*E17*$C$1)</f>
+        <f>IF(C17="","",IF(D17="",C17,(C17+D17)/2)*E17*$C$1)</f>
         <v/>
       </c>
     </row>
@@ -974,7 +988,7 @@
       <c r="D18" s="11" t="n"/>
       <c r="E18" s="11" t="n"/>
       <c r="F18" s="10">
-        <f>IF(C18="","",(C18+D18)/2*E18*$C$1)</f>
+        <f>IF(C18="","",IF(D18="",C18,(C18+D18)/2)*E18*$C$1)</f>
         <v/>
       </c>
     </row>
@@ -985,7 +999,7 @@
       <c r="D19" s="11" t="n"/>
       <c r="E19" s="11" t="n"/>
       <c r="F19" s="10">
-        <f>IF(C19="","",(C19+D19)/2*E19*$C$1)</f>
+        <f>IF(C19="","",IF(D19="",C19,(C19+D19)/2)*E19*$C$1)</f>
         <v/>
       </c>
     </row>
@@ -996,7 +1010,7 @@
       <c r="D20" s="11" t="n"/>
       <c r="E20" s="11" t="n"/>
       <c r="F20" s="10">
-        <f>IF(C20="","",(C20+D20)/2*E20*$C$1)</f>
+        <f>IF(C20="","",IF(D20="",C20,(C20+D20)/2)*E20*$C$1)</f>
         <v/>
       </c>
     </row>
@@ -1007,7 +1021,7 @@
       <c r="D21" s="11" t="n"/>
       <c r="E21" s="11" t="n"/>
       <c r="F21" s="10">
-        <f>IF(C21="","",(C21+D21)/2*E21*$C$1)</f>
+        <f>IF(C21="","",IF(D21="",C21,(C21+D21)/2)*E21*$C$1)</f>
         <v/>
       </c>
     </row>
@@ -1018,7 +1032,7 @@
       <c r="D22" s="11" t="n"/>
       <c r="E22" s="11" t="n"/>
       <c r="F22" s="10">
-        <f>IF(C22="","",(C22+D22)/2*E22*$C$1)</f>
+        <f>IF(C22="","",IF(D22="",C22,(C22+D22)/2)*E22*$C$1)</f>
         <v/>
       </c>
     </row>
@@ -1029,7 +1043,7 @@
       <c r="D23" s="11" t="n"/>
       <c r="E23" s="11" t="n"/>
       <c r="F23" s="10">
-        <f>IF(C23="","",(C23+D23)/2*E23*$C$1)</f>
+        <f>IF(C23="","",IF(D23="",C23,(C23+D23)/2)*E23*$C$1)</f>
         <v/>
       </c>
     </row>
@@ -1040,7 +1054,7 @@
       <c r="D24" s="11" t="n"/>
       <c r="E24" s="11" t="n"/>
       <c r="F24" s="10">
-        <f>IF(C24="","",(C24+D24)/2*E24*$C$1)</f>
+        <f>IF(C24="","",IF(D24="",C24,(C24+D24)/2)*E24*$C$1)</f>
         <v/>
       </c>
     </row>
@@ -1051,7 +1065,7 @@
       <c r="D25" s="11" t="n"/>
       <c r="E25" s="11" t="n"/>
       <c r="F25" s="10">
-        <f>IF(C25="","",(C25+D25)/2*E25*$C$1)</f>
+        <f>IF(C25="","",IF(D25="",C25,(C25+D25)/2)*E25*$C$1)</f>
         <v/>
       </c>
     </row>
@@ -1062,7 +1076,7 @@
       <c r="D26" s="11" t="n"/>
       <c r="E26" s="11" t="n"/>
       <c r="F26" s="10">
-        <f>IF(C26="","",(C26+D26)/2*E26*$C$1)</f>
+        <f>IF(C26="","",IF(D26="",C26,(C26+D26)/2)*E26*$C$1)</f>
         <v/>
       </c>
     </row>
@@ -1073,7 +1087,7 @@
       <c r="D27" s="11" t="n"/>
       <c r="E27" s="11" t="n"/>
       <c r="F27" s="10">
-        <f>IF(C27="","",(C27+D27)/2*E27*$C$1)</f>
+        <f>IF(C27="","",IF(D27="",C27,(C27+D27)/2)*E27*$C$1)</f>
         <v/>
       </c>
     </row>
@@ -1084,7 +1098,7 @@
       <c r="D28" s="11" t="n"/>
       <c r="E28" s="11" t="n"/>
       <c r="F28" s="10">
-        <f>IF(C28="","",(C28+D28)/2*E28*$C$1)</f>
+        <f>IF(C28="","",IF(D28="",C28,(C28+D28)/2)*E28*$C$1)</f>
         <v/>
       </c>
     </row>
@@ -1095,7 +1109,7 @@
       <c r="D29" s="11" t="n"/>
       <c r="E29" s="11" t="n"/>
       <c r="F29" s="10">
-        <f>IF(C29="","",(C29+D29)/2*E29*$C$1)</f>
+        <f>IF(C29="","",IF(D29="",C29,(C29+D29)/2)*E29*$C$1)</f>
         <v/>
       </c>
     </row>
@@ -1106,7 +1120,7 @@
       <c r="D30" s="11" t="n"/>
       <c r="E30" s="11" t="n"/>
       <c r="F30" s="10">
-        <f>IF(C30="","",(C30+D30)/2*E30*$C$1)</f>
+        <f>IF(C30="","",IF(D30="",C30,(C30+D30)/2)*E30*$C$1)</f>
         <v/>
       </c>
     </row>
@@ -1117,7 +1131,7 @@
       <c r="D31" s="11" t="n"/>
       <c r="E31" s="11" t="n"/>
       <c r="F31" s="10">
-        <f>IF(C31="","",(C31+D31)/2*E31*$C$1)</f>
+        <f>IF(C31="","",IF(D31="",C31,(C31+D31)/2)*E31*$C$1)</f>
         <v/>
       </c>
     </row>
@@ -1128,7 +1142,7 @@
       <c r="D32" s="11" t="n"/>
       <c r="E32" s="11" t="n"/>
       <c r="F32" s="10">
-        <f>IF(C32="","",(C32+D32)/2*E32*$C$1)</f>
+        <f>IF(C32="","",IF(D32="",C32,(C32+D32)/2)*E32*$C$1)</f>
         <v/>
       </c>
     </row>
@@ -1139,7 +1153,7 @@
       <c r="D33" s="11" t="n"/>
       <c r="E33" s="11" t="n"/>
       <c r="F33" s="10">
-        <f>IF(C33="","",(C33+D33)/2*E33*$C$1)</f>
+        <f>IF(C33="","",IF(D33="",C33,(C33+D33)/2)*E33*$C$1)</f>
         <v/>
       </c>
     </row>
@@ -1150,7 +1164,7 @@
       <c r="D34" s="11" t="n"/>
       <c r="E34" s="11" t="n"/>
       <c r="F34" s="10">
-        <f>IF(C34="","",(C34+D34)/2*E34*$C$1)</f>
+        <f>IF(C34="","",IF(D34="",C34,(C34+D34)/2)*E34*$C$1)</f>
         <v/>
       </c>
     </row>
@@ -1161,7 +1175,7 @@
       <c r="D35" s="11" t="n"/>
       <c r="E35" s="11" t="n"/>
       <c r="F35" s="10">
-        <f>IF(C35="","",(C35+D35)/2*E35*$C$1)</f>
+        <f>IF(C35="","",IF(D35="",C35,(C35+D35)/2)*E35*$C$1)</f>
         <v/>
       </c>
     </row>
@@ -1172,7 +1186,7 @@
       <c r="D36" s="11" t="n"/>
       <c r="E36" s="11" t="n"/>
       <c r="F36" s="10">
-        <f>IF(C36="","",(C36+D36)/2*E36*$C$1)</f>
+        <f>IF(C36="","",IF(D36="",C36,(C36+D36)/2)*E36*$C$1)</f>
         <v/>
       </c>
     </row>
@@ -1183,7 +1197,7 @@
       <c r="D37" s="11" t="n"/>
       <c r="E37" s="11" t="n"/>
       <c r="F37" s="10">
-        <f>IF(C37="","",(C37+D37)/2*E37*$C$1)</f>
+        <f>IF(C37="","",IF(D37="",C37,(C37+D37)/2)*E37*$C$1)</f>
         <v/>
       </c>
     </row>
@@ -1194,7 +1208,7 @@
       <c r="D38" s="11" t="n"/>
       <c r="E38" s="11" t="n"/>
       <c r="F38" s="10">
-        <f>IF(C38="","",(C38+D38)/2*E38*$C$1)</f>
+        <f>IF(C38="","",IF(D38="",C38,(C38+D38)/2)*E38*$C$1)</f>
         <v/>
       </c>
     </row>
@@ -1205,7 +1219,7 @@
       <c r="D39" s="11" t="n"/>
       <c r="E39" s="11" t="n"/>
       <c r="F39" s="10">
-        <f>IF(C39="","",(C39+D39)/2*E39*$C$1)</f>
+        <f>IF(C39="","",IF(D39="",C39,(C39+D39)/2)*E39*$C$1)</f>
         <v/>
       </c>
     </row>
@@ -1216,7 +1230,7 @@
       <c r="D40" s="11" t="n"/>
       <c r="E40" s="11" t="n"/>
       <c r="F40" s="10">
-        <f>IF(C40="","",(C40+D40)/2*E40*$C$1)</f>
+        <f>IF(C40="","",IF(D40="",C40,(C40+D40)/2)*E40*$C$1)</f>
         <v/>
       </c>
     </row>
@@ -1227,7 +1241,7 @@
       <c r="D41" s="11" t="n"/>
       <c r="E41" s="11" t="n"/>
       <c r="F41" s="10">
-        <f>IF(C41="","",(C41+D41)/2*E41*$C$1)</f>
+        <f>IF(C41="","",IF(D41="",C41,(C41+D41)/2)*E41*$C$1)</f>
         <v/>
       </c>
     </row>
@@ -1238,7 +1252,7 @@
       <c r="D42" s="11" t="n"/>
       <c r="E42" s="11" t="n"/>
       <c r="F42" s="10">
-        <f>IF(C42="","",(C42+D42)/2*E42*$C$1)</f>
+        <f>IF(C42="","",IF(D42="",C42,(C42+D42)/2)*E42*$C$1)</f>
         <v/>
       </c>
     </row>
@@ -1249,7 +1263,7 @@
       <c r="D43" s="11" t="n"/>
       <c r="E43" s="11" t="n"/>
       <c r="F43" s="10">
-        <f>IF(C43="","",(C43+D43)/2*E43*$C$1)</f>
+        <f>IF(C43="","",IF(D43="",C43,(C43+D43)/2)*E43*$C$1)</f>
         <v/>
       </c>
     </row>
@@ -1303,6 +1317,21 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>初回手数料(円)</t>
+        </is>
+      </c>
+      <c r="C2" s="6" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D2" s="7" t="inlineStr">
+        <is>
+          <t>※新規契約時に案件ごと一律で加算。ご提示金額＝月間概算料金の合計＋この金額（手動で合算してください）。</t>
+        </is>
+      </c>
+    </row>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="8" t="inlineStr">
         <is>
@@ -1415,7 +1444,7 @@
         <v>40</v>
       </c>
       <c r="K4" s="10">
-        <f>IF(E4="","",IF(D4="日",(E4+F4)/2*G4,(E4+F4)/2)*$C$1)</f>
+        <f>IF(E4="","",IF(D4="日",IF(F4="",E4,(E4+F4)/2)*G4,IF(F4="",E4,(E4+F4)/2))*$C$1)</f>
         <v/>
       </c>
       <c r="L4" s="10">
@@ -1469,7 +1498,7 @@
       </c>
       <c r="J5" s="9" t="inlineStr"/>
       <c r="K5" s="10">
-        <f>IF(E5="","",IF(D5="日",(E5+F5)/2*G5,(E5+F5)/2)*$C$1)</f>
+        <f>IF(E5="","",IF(D5="日",IF(F5="",E5,(E5+F5)/2)*G5,IF(F5="",E5,(E5+F5)/2))*$C$1)</f>
         <v/>
       </c>
       <c r="L5" s="10">
@@ -1521,7 +1550,7 @@
       </c>
       <c r="J6" s="9" t="inlineStr"/>
       <c r="K6" s="10">
-        <f>IF(E6="","",IF(D6="日",(E6+F6)/2*G6,(E6+F6)/2)*$C$1)</f>
+        <f>IF(E6="","",IF(D6="日",IF(F6="",E6,(E6+F6)/2)*G6,IF(F6="",E6,(E6+F6)/2))*$C$1)</f>
         <v/>
       </c>
       <c r="L6" s="10">
@@ -1573,7 +1602,7 @@
       </c>
       <c r="J7" s="9" t="inlineStr"/>
       <c r="K7" s="10">
-        <f>IF(E7="","",IF(D7="日",(E7+F7)/2*G7,(E7+F7)/2)*$C$1)</f>
+        <f>IF(E7="","",IF(D7="日",IF(F7="",E7,(E7+F7)/2)*G7,IF(F7="",E7,(E7+F7)/2))*$C$1)</f>
         <v/>
       </c>
       <c r="L7" s="10">
@@ -1625,7 +1654,7 @@
       </c>
       <c r="J8" s="9" t="inlineStr"/>
       <c r="K8" s="10">
-        <f>IF(E8="","",IF(D8="日",(E8+F8)/2*G8,(E8+F8)/2)*$C$1)</f>
+        <f>IF(E8="","",IF(D8="日",IF(F8="",E8,(E8+F8)/2)*G8,IF(F8="",E8,(E8+F8)/2))*$C$1)</f>
         <v/>
       </c>
       <c r="L8" s="10">
@@ -1677,7 +1706,7 @@
         <v>35</v>
       </c>
       <c r="K9" s="10">
-        <f>IF(E9="","",IF(D9="日",(E9+F9)/2*G9,(E9+F9)/2)*$C$1)</f>
+        <f>IF(E9="","",IF(D9="日",IF(F9="",E9,(E9+F9)/2)*G9,IF(F9="",E9,(E9+F9)/2))*$C$1)</f>
         <v/>
       </c>
       <c r="L9" s="10">
@@ -1733,7 +1762,7 @@
         <v>40</v>
       </c>
       <c r="K10" s="10">
-        <f>IF(E10="","",IF(D10="日",(E10+F10)/2*G10,(E10+F10)/2)*$C$1)</f>
+        <f>IF(E10="","",IF(D10="日",IF(F10="",E10,(E10+F10)/2)*G10,IF(F10="",E10,(E10+F10)/2))*$C$1)</f>
         <v/>
       </c>
       <c r="L10" s="10">
@@ -1789,7 +1818,7 @@
         <v>100</v>
       </c>
       <c r="K11" s="10">
-        <f>IF(E11="","",IF(D11="日",(E11+F11)/2*G11,(E11+F11)/2)*$C$1)</f>
+        <f>IF(E11="","",IF(D11="日",IF(F11="",E11,(E11+F11)/2)*G11,IF(F11="",E11,(E11+F11)/2))*$C$1)</f>
         <v/>
       </c>
       <c r="L11" s="10">
@@ -1817,7 +1846,7 @@
       <c r="I12" s="11" t="n"/>
       <c r="J12" s="11" t="n"/>
       <c r="K12" s="10">
-        <f>IF(E12="","",IF(D12="日",(E12+F12)/2*G12,(E12+F12)/2)*$C$1)</f>
+        <f>IF(E12="","",IF(D12="日",IF(F12="",E12,(E12+F12)/2)*G12,IF(F12="",E12,(E12+F12)/2))*$C$1)</f>
         <v/>
       </c>
       <c r="L12" s="10">
@@ -1845,7 +1874,7 @@
       <c r="I13" s="11" t="n"/>
       <c r="J13" s="11" t="n"/>
       <c r="K13" s="10">
-        <f>IF(E13="","",IF(D13="日",(E13+F13)/2*G13,(E13+F13)/2)*$C$1)</f>
+        <f>IF(E13="","",IF(D13="日",IF(F13="",E13,(E13+F13)/2)*G13,IF(F13="",E13,(E13+F13)/2))*$C$1)</f>
         <v/>
       </c>
       <c r="L13" s="10">
@@ -1873,7 +1902,7 @@
       <c r="I14" s="11" t="n"/>
       <c r="J14" s="11" t="n"/>
       <c r="K14" s="10">
-        <f>IF(E14="","",IF(D14="日",(E14+F14)/2*G14,(E14+F14)/2)*$C$1)</f>
+        <f>IF(E14="","",IF(D14="日",IF(F14="",E14,(E14+F14)/2)*G14,IF(F14="",E14,(E14+F14)/2))*$C$1)</f>
         <v/>
       </c>
       <c r="L14" s="10">
@@ -1901,7 +1930,7 @@
       <c r="I15" s="11" t="n"/>
       <c r="J15" s="11" t="n"/>
       <c r="K15" s="10">
-        <f>IF(E15="","",IF(D15="日",(E15+F15)/2*G15,(E15+F15)/2)*$C$1)</f>
+        <f>IF(E15="","",IF(D15="日",IF(F15="",E15,(E15+F15)/2)*G15,IF(F15="",E15,(E15+F15)/2))*$C$1)</f>
         <v/>
       </c>
       <c r="L15" s="10">
@@ -1929,7 +1958,7 @@
       <c r="I16" s="11" t="n"/>
       <c r="J16" s="11" t="n"/>
       <c r="K16" s="10">
-        <f>IF(E16="","",IF(D16="日",(E16+F16)/2*G16,(E16+F16)/2)*$C$1)</f>
+        <f>IF(E16="","",IF(D16="日",IF(F16="",E16,(E16+F16)/2)*G16,IF(F16="",E16,(E16+F16)/2))*$C$1)</f>
         <v/>
       </c>
       <c r="L16" s="10">
@@ -1957,7 +1986,7 @@
       <c r="I17" s="11" t="n"/>
       <c r="J17" s="11" t="n"/>
       <c r="K17" s="10">
-        <f>IF(E17="","",IF(D17="日",(E17+F17)/2*G17,(E17+F17)/2)*$C$1)</f>
+        <f>IF(E17="","",IF(D17="日",IF(F17="",E17,(E17+F17)/2)*G17,IF(F17="",E17,(E17+F17)/2))*$C$1)</f>
         <v/>
       </c>
       <c r="L17" s="10">
@@ -1985,7 +2014,7 @@
       <c r="I18" s="11" t="n"/>
       <c r="J18" s="11" t="n"/>
       <c r="K18" s="10">
-        <f>IF(E18="","",IF(D18="日",(E18+F18)/2*G18,(E18+F18)/2)*$C$1)</f>
+        <f>IF(E18="","",IF(D18="日",IF(F18="",E18,(E18+F18)/2)*G18,IF(F18="",E18,(E18+F18)/2))*$C$1)</f>
         <v/>
       </c>
       <c r="L18" s="10">
@@ -2013,7 +2042,7 @@
       <c r="I19" s="11" t="n"/>
       <c r="J19" s="11" t="n"/>
       <c r="K19" s="10">
-        <f>IF(E19="","",IF(D19="日",(E19+F19)/2*G19,(E19+F19)/2)*$C$1)</f>
+        <f>IF(E19="","",IF(D19="日",IF(F19="",E19,(E19+F19)/2)*G19,IF(F19="",E19,(E19+F19)/2))*$C$1)</f>
         <v/>
       </c>
       <c r="L19" s="10">
@@ -2041,7 +2070,7 @@
       <c r="I20" s="11" t="n"/>
       <c r="J20" s="11" t="n"/>
       <c r="K20" s="10">
-        <f>IF(E20="","",IF(D20="日",(E20+F20)/2*G20,(E20+F20)/2)*$C$1)</f>
+        <f>IF(E20="","",IF(D20="日",IF(F20="",E20,(E20+F20)/2)*G20,IF(F20="",E20,(E20+F20)/2))*$C$1)</f>
         <v/>
       </c>
       <c r="L20" s="10">
@@ -2069,7 +2098,7 @@
       <c r="I21" s="11" t="n"/>
       <c r="J21" s="11" t="n"/>
       <c r="K21" s="10">
-        <f>IF(E21="","",IF(D21="日",(E21+F21)/2*G21,(E21+F21)/2)*$C$1)</f>
+        <f>IF(E21="","",IF(D21="日",IF(F21="",E21,(E21+F21)/2)*G21,IF(F21="",E21,(E21+F21)/2))*$C$1)</f>
         <v/>
       </c>
       <c r="L21" s="10">
@@ -2097,7 +2126,7 @@
       <c r="I22" s="11" t="n"/>
       <c r="J22" s="11" t="n"/>
       <c r="K22" s="10">
-        <f>IF(E22="","",IF(D22="日",(E22+F22)/2*G22,(E22+F22)/2)*$C$1)</f>
+        <f>IF(E22="","",IF(D22="日",IF(F22="",E22,(E22+F22)/2)*G22,IF(F22="",E22,(E22+F22)/2))*$C$1)</f>
         <v/>
       </c>
       <c r="L22" s="10">
@@ -2125,7 +2154,7 @@
       <c r="I23" s="11" t="n"/>
       <c r="J23" s="11" t="n"/>
       <c r="K23" s="10">
-        <f>IF(E23="","",IF(D23="日",(E23+F23)/2*G23,(E23+F23)/2)*$C$1)</f>
+        <f>IF(E23="","",IF(D23="日",IF(F23="",E23,(E23+F23)/2)*G23,IF(F23="",E23,(E23+F23)/2))*$C$1)</f>
         <v/>
       </c>
       <c r="L23" s="10">
@@ -2153,7 +2182,7 @@
       <c r="I24" s="11" t="n"/>
       <c r="J24" s="11" t="n"/>
       <c r="K24" s="10">
-        <f>IF(E24="","",IF(D24="日",(E24+F24)/2*G24,(E24+F24)/2)*$C$1)</f>
+        <f>IF(E24="","",IF(D24="日",IF(F24="",E24,(E24+F24)/2)*G24,IF(F24="",E24,(E24+F24)/2))*$C$1)</f>
         <v/>
       </c>
       <c r="L24" s="10">
@@ -2181,7 +2210,7 @@
       <c r="I25" s="11" t="n"/>
       <c r="J25" s="11" t="n"/>
       <c r="K25" s="10">
-        <f>IF(E25="","",IF(D25="日",(E25+F25)/2*G25,(E25+F25)/2)*$C$1)</f>
+        <f>IF(E25="","",IF(D25="日",IF(F25="",E25,(E25+F25)/2)*G25,IF(F25="",E25,(E25+F25)/2))*$C$1)</f>
         <v/>
       </c>
       <c r="L25" s="10">
@@ -2209,7 +2238,7 @@
       <c r="I26" s="11" t="n"/>
       <c r="J26" s="11" t="n"/>
       <c r="K26" s="10">
-        <f>IF(E26="","",IF(D26="日",(E26+F26)/2*G26,(E26+F26)/2)*$C$1)</f>
+        <f>IF(E26="","",IF(D26="日",IF(F26="",E26,(E26+F26)/2)*G26,IF(F26="",E26,(E26+F26)/2))*$C$1)</f>
         <v/>
       </c>
       <c r="L26" s="10">
@@ -2237,7 +2266,7 @@
       <c r="I27" s="11" t="n"/>
       <c r="J27" s="11" t="n"/>
       <c r="K27" s="10">
-        <f>IF(E27="","",IF(D27="日",(E27+F27)/2*G27,(E27+F27)/2)*$C$1)</f>
+        <f>IF(E27="","",IF(D27="日",IF(F27="",E27,(E27+F27)/2)*G27,IF(F27="",E27,(E27+F27)/2))*$C$1)</f>
         <v/>
       </c>
       <c r="L27" s="10">
@@ -2265,7 +2294,7 @@
       <c r="I28" s="11" t="n"/>
       <c r="J28" s="11" t="n"/>
       <c r="K28" s="10">
-        <f>IF(E28="","",IF(D28="日",(E28+F28)/2*G28,(E28+F28)/2)*$C$1)</f>
+        <f>IF(E28="","",IF(D28="日",IF(F28="",E28,(E28+F28)/2)*G28,IF(F28="",E28,(E28+F28)/2))*$C$1)</f>
         <v/>
       </c>
       <c r="L28" s="10">
@@ -2293,7 +2322,7 @@
       <c r="I29" s="11" t="n"/>
       <c r="J29" s="11" t="n"/>
       <c r="K29" s="10">
-        <f>IF(E29="","",IF(D29="日",(E29+F29)/2*G29,(E29+F29)/2)*$C$1)</f>
+        <f>IF(E29="","",IF(D29="日",IF(F29="",E29,(E29+F29)/2)*G29,IF(F29="",E29,(E29+F29)/2))*$C$1)</f>
         <v/>
       </c>
       <c r="L29" s="10">
@@ -2321,7 +2350,7 @@
       <c r="I30" s="11" t="n"/>
       <c r="J30" s="11" t="n"/>
       <c r="K30" s="10">
-        <f>IF(E30="","",IF(D30="日",(E30+F30)/2*G30,(E30+F30)/2)*$C$1)</f>
+        <f>IF(E30="","",IF(D30="日",IF(F30="",E30,(E30+F30)/2)*G30,IF(F30="",E30,(E30+F30)/2))*$C$1)</f>
         <v/>
       </c>
       <c r="L30" s="10">
@@ -2349,7 +2378,7 @@
       <c r="I31" s="11" t="n"/>
       <c r="J31" s="11" t="n"/>
       <c r="K31" s="10">
-        <f>IF(E31="","",IF(D31="日",(E31+F31)/2*G31,(E31+F31)/2)*$C$1)</f>
+        <f>IF(E31="","",IF(D31="日",IF(F31="",E31,(E31+F31)/2)*G31,IF(F31="",E31,(E31+F31)/2))*$C$1)</f>
         <v/>
       </c>
       <c r="L31" s="10">
@@ -2377,7 +2406,7 @@
       <c r="I32" s="11" t="n"/>
       <c r="J32" s="11" t="n"/>
       <c r="K32" s="10">
-        <f>IF(E32="","",IF(D32="日",(E32+F32)/2*G32,(E32+F32)/2)*$C$1)</f>
+        <f>IF(E32="","",IF(D32="日",IF(F32="",E32,(E32+F32)/2)*G32,IF(F32="",E32,(E32+F32)/2))*$C$1)</f>
         <v/>
       </c>
       <c r="L32" s="10">
@@ -2405,7 +2434,7 @@
       <c r="I33" s="11" t="n"/>
       <c r="J33" s="11" t="n"/>
       <c r="K33" s="10">
-        <f>IF(E33="","",IF(D33="日",(E33+F33)/2*G33,(E33+F33)/2)*$C$1)</f>
+        <f>IF(E33="","",IF(D33="日",IF(F33="",E33,(E33+F33)/2)*G33,IF(F33="",E33,(E33+F33)/2))*$C$1)</f>
         <v/>
       </c>
       <c r="L33" s="10">
@@ -2433,7 +2462,7 @@
       <c r="I34" s="11" t="n"/>
       <c r="J34" s="11" t="n"/>
       <c r="K34" s="10">
-        <f>IF(E34="","",IF(D34="日",(E34+F34)/2*G34,(E34+F34)/2)*$C$1)</f>
+        <f>IF(E34="","",IF(D34="日",IF(F34="",E34,(E34+F34)/2)*G34,IF(F34="",E34,(E34+F34)/2))*$C$1)</f>
         <v/>
       </c>
       <c r="L34" s="10">
@@ -2461,7 +2490,7 @@
       <c r="I35" s="11" t="n"/>
       <c r="J35" s="11" t="n"/>
       <c r="K35" s="10">
-        <f>IF(E35="","",IF(D35="日",(E35+F35)/2*G35,(E35+F35)/2)*$C$1)</f>
+        <f>IF(E35="","",IF(D35="日",IF(F35="",E35,(E35+F35)/2)*G35,IF(F35="",E35,(E35+F35)/2))*$C$1)</f>
         <v/>
       </c>
       <c r="L35" s="10">
@@ -2489,7 +2518,7 @@
       <c r="I36" s="11" t="n"/>
       <c r="J36" s="11" t="n"/>
       <c r="K36" s="10">
-        <f>IF(E36="","",IF(D36="日",(E36+F36)/2*G36,(E36+F36)/2)*$C$1)</f>
+        <f>IF(E36="","",IF(D36="日",IF(F36="",E36,(E36+F36)/2)*G36,IF(F36="",E36,(E36+F36)/2))*$C$1)</f>
         <v/>
       </c>
       <c r="L36" s="10">
@@ -2517,7 +2546,7 @@
       <c r="I37" s="11" t="n"/>
       <c r="J37" s="11" t="n"/>
       <c r="K37" s="10">
-        <f>IF(E37="","",IF(D37="日",(E37+F37)/2*G37,(E37+F37)/2)*$C$1)</f>
+        <f>IF(E37="","",IF(D37="日",IF(F37="",E37,(E37+F37)/2)*G37,IF(F37="",E37,(E37+F37)/2))*$C$1)</f>
         <v/>
       </c>
       <c r="L37" s="10">
@@ -2545,7 +2574,7 @@
       <c r="I38" s="11" t="n"/>
       <c r="J38" s="11" t="n"/>
       <c r="K38" s="10">
-        <f>IF(E38="","",IF(D38="日",(E38+F38)/2*G38,(E38+F38)/2)*$C$1)</f>
+        <f>IF(E38="","",IF(D38="日",IF(F38="",E38,(E38+F38)/2)*G38,IF(F38="",E38,(E38+F38)/2))*$C$1)</f>
         <v/>
       </c>
       <c r="L38" s="10">
@@ -2573,7 +2602,7 @@
       <c r="I39" s="11" t="n"/>
       <c r="J39" s="11" t="n"/>
       <c r="K39" s="10">
-        <f>IF(E39="","",IF(D39="日",(E39+F39)/2*G39,(E39+F39)/2)*$C$1)</f>
+        <f>IF(E39="","",IF(D39="日",IF(F39="",E39,(E39+F39)/2)*G39,IF(F39="",E39,(E39+F39)/2))*$C$1)</f>
         <v/>
       </c>
       <c r="L39" s="10">
@@ -2601,7 +2630,7 @@
       <c r="I40" s="11" t="n"/>
       <c r="J40" s="11" t="n"/>
       <c r="K40" s="10">
-        <f>IF(E40="","",IF(D40="日",(E40+F40)/2*G40,(E40+F40)/2)*$C$1)</f>
+        <f>IF(E40="","",IF(D40="日",IF(F40="",E40,(E40+F40)/2)*G40,IF(F40="",E40,(E40+F40)/2))*$C$1)</f>
         <v/>
       </c>
       <c r="L40" s="10">
@@ -2629,7 +2658,7 @@
       <c r="I41" s="11" t="n"/>
       <c r="J41" s="11" t="n"/>
       <c r="K41" s="10">
-        <f>IF(E41="","",IF(D41="日",(E41+F41)/2*G41,(E41+F41)/2)*$C$1)</f>
+        <f>IF(E41="","",IF(D41="日",IF(F41="",E41,(E41+F41)/2)*G41,IF(F41="",E41,(E41+F41)/2))*$C$1)</f>
         <v/>
       </c>
       <c r="L41" s="10">
@@ -2657,7 +2686,7 @@
       <c r="I42" s="11" t="n"/>
       <c r="J42" s="11" t="n"/>
       <c r="K42" s="10">
-        <f>IF(E42="","",IF(D42="日",(E42+F42)/2*G42,(E42+F42)/2)*$C$1)</f>
+        <f>IF(E42="","",IF(D42="日",IF(F42="",E42,(E42+F42)/2)*G42,IF(F42="",E42,(E42+F42)/2))*$C$1)</f>
         <v/>
       </c>
       <c r="L42" s="10">
@@ -2685,7 +2714,7 @@
       <c r="I43" s="11" t="n"/>
       <c r="J43" s="11" t="n"/>
       <c r="K43" s="10">
-        <f>IF(E43="","",IF(D43="日",(E43+F43)/2*G43,(E43+F43)/2)*$C$1)</f>
+        <f>IF(E43="","",IF(D43="日",IF(F43="",E43,(E43+F43)/2)*G43,IF(F43="",E43,(E43+F43)/2))*$C$1)</f>
         <v/>
       </c>
       <c r="L43" s="10">

--- a/waste-calculator/waste_calculator_template.xlsx
+++ b/waste-calculator/waste_calculator_template.xlsx
@@ -507,7 +507,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B22"/>
+  <dimension ref="B2:B23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -590,57 +590,64 @@
     <row r="14">
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>・数量min／数量max：「1〜2袋」のように幅がある場合は両方入力。「2袋」のように1つだけの場合は数量maxを空欄にすればOK（数量minの値だけで計算されます）。</t>
+          <t>・（詳細入力のみ）頻度パターンに「月」を選ぶと、数量min欄をそのまま月間量として使えます。見積りが「月56袋」のように確定している場合はこちらが便利です。</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>・（詳細入力のみ）重量(kg/個)：料金計算のもとになる重量。45L≈5kg・70L≈8kgの実測値をもとにした目安を仮入力していますが、必要に応じて修正してください（段ボールは1枚≈0.3kgが目安）。</t>
+          <t>・数量min／数量max：「1〜2袋」のように幅がある場合は両方入力。「2袋」のように1つだけの場合は数量maxを空欄にすればOK（数量minの値だけで計算されます）。</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="4" t="inlineStr">
         <is>
+          <t>・（詳細入力のみ）重量(kg/個)：料金計算のもとになる重量。45L≈5kg・70L≈8kgの実測値をもとにした目安を仮入力していますが、必ず実際の見積り値に合わせて修正してください（段ボールは1枚≈1kgが目安、可燃・不燃でも実際は異なることがあります）。</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="4" t="inlineStr">
+        <is>
           <t>・（詳細入力のみ）単価(円/kg)：1kgあたりの料金。可燃40円・不燃100円・段ボール35円を仮入力済み（実際の契約単価に合わせて修正してください）</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" s="4" t="inlineStr"/>
-    </row>
     <row r="18">
-      <c r="B18" s="3" t="inlineStr">
+      <c r="B18" s="4" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>③ 前提</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="4" t="inlineStr">
-        <is>
-          <t>1ヶ月あたりの週数は各シートのC1セルで設定（既定値 4.35週 ＝ 365日 ÷ 12ヶ月 ÷ 7日）。</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>数量が明記されていない項目（例:「不燃物 週2日」のみで数量記載なし）は 1回1袋 と仮定しています。実数が分かり次第、数量欄を修正してください。</t>
+          <t>1ヶ月あたりの週数は各シートのC1セルで設定（既定値 4.35週 ＝ 365日 ÷ 12ヶ月 ÷ 7日）。</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>概算料金＝月間量×重量(kg/個)×単価(円/kg)で計算しています。重量が未入力の項目は料金計算から除外されます。</t>
+          <t>数量が明記されていない項目（例:「不燃物 週2日」のみで数量記載なし）は 1回1袋 と仮定しています。実数が分かり次第、数量欄を修正してください。</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="B22" s="4" t="inlineStr">
+        <is>
+          <t>概算料金＝月間量×重量(kg/個)×単価(円/kg)で計算しています。重量が未入力の項目は料金計算から除外されます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="4" t="inlineStr">
         <is>
           <t>初回手数料（詳細入力シートC2セル、既定 ¥3,000）は新規契約の案件ごとに一律で加算する費用です。ご提示金額＝その案件の月間概算料金の合計＋初回手数料、として手動で合算してください。</t>
         </is>
@@ -1350,17 +1357,17 @@
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>頻度パターン(日/週)</t>
+          <t>頻度パターン(日/週/月)</t>
         </is>
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
-          <t>数量min(1回あたり)</t>
+          <t>数量min(1回あたり/月あたり)</t>
         </is>
       </c>
       <c r="F3" s="8" t="inlineStr">
         <is>
-          <t>数量max(1回あたり)</t>
+          <t>数量max(1回あたり/月あたり)</t>
         </is>
       </c>
       <c r="G3" s="8" t="inlineStr">
@@ -1444,7 +1451,7 @@
         <v>40</v>
       </c>
       <c r="K4" s="10">
-        <f>IF(E4="","",IF(D4="日",IF(F4="",E4,(E4+F4)/2)*G4,IF(F4="",E4,(E4+F4)/2))*$C$1)</f>
+        <f>IF(E4="","",IF(D4="日",IF(F4="",E4,(E4+F4)/2)*G4,IF(D4="月",E4,IF(F4="",E4,(E4+F4)/2)))*IF(D4="月",1,$C$1))</f>
         <v/>
       </c>
       <c r="L4" s="10">
@@ -1498,7 +1505,7 @@
       </c>
       <c r="J5" s="9" t="inlineStr"/>
       <c r="K5" s="10">
-        <f>IF(E5="","",IF(D5="日",IF(F5="",E5,(E5+F5)/2)*G5,IF(F5="",E5,(E5+F5)/2))*$C$1)</f>
+        <f>IF(E5="","",IF(D5="日",IF(F5="",E5,(E5+F5)/2)*G5,IF(D5="月",E5,IF(F5="",E5,(E5+F5)/2)))*IF(D5="月",1,$C$1))</f>
         <v/>
       </c>
       <c r="L5" s="10">
@@ -1550,7 +1557,7 @@
       </c>
       <c r="J6" s="9" t="inlineStr"/>
       <c r="K6" s="10">
-        <f>IF(E6="","",IF(D6="日",IF(F6="",E6,(E6+F6)/2)*G6,IF(F6="",E6,(E6+F6)/2))*$C$1)</f>
+        <f>IF(E6="","",IF(D6="日",IF(F6="",E6,(E6+F6)/2)*G6,IF(D6="月",E6,IF(F6="",E6,(E6+F6)/2)))*IF(D6="月",1,$C$1))</f>
         <v/>
       </c>
       <c r="L6" s="10">
@@ -1602,7 +1609,7 @@
       </c>
       <c r="J7" s="9" t="inlineStr"/>
       <c r="K7" s="10">
-        <f>IF(E7="","",IF(D7="日",IF(F7="",E7,(E7+F7)/2)*G7,IF(F7="",E7,(E7+F7)/2))*$C$1)</f>
+        <f>IF(E7="","",IF(D7="日",IF(F7="",E7,(E7+F7)/2)*G7,IF(D7="月",E7,IF(F7="",E7,(E7+F7)/2)))*IF(D7="月",1,$C$1))</f>
         <v/>
       </c>
       <c r="L7" s="10">
@@ -1654,7 +1661,7 @@
       </c>
       <c r="J8" s="9" t="inlineStr"/>
       <c r="K8" s="10">
-        <f>IF(E8="","",IF(D8="日",IF(F8="",E8,(E8+F8)/2)*G8,IF(F8="",E8,(E8+F8)/2))*$C$1)</f>
+        <f>IF(E8="","",IF(D8="日",IF(F8="",E8,(E8+F8)/2)*G8,IF(D8="月",E8,IF(F8="",E8,(E8+F8)/2)))*IF(D8="月",1,$C$1))</f>
         <v/>
       </c>
       <c r="L8" s="10">
@@ -1700,13 +1707,13 @@
       <c r="G9" s="9" t="inlineStr"/>
       <c r="H9" s="9" t="inlineStr"/>
       <c r="I9" s="9" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="J9" s="9" t="n">
         <v>35</v>
       </c>
       <c r="K9" s="10">
-        <f>IF(E9="","",IF(D9="日",IF(F9="",E9,(E9+F9)/2)*G9,IF(F9="",E9,(E9+F9)/2))*$C$1)</f>
+        <f>IF(E9="","",IF(D9="日",IF(F9="",E9,(E9+F9)/2)*G9,IF(D9="月",E9,IF(F9="",E9,(E9+F9)/2)))*IF(D9="月",1,$C$1))</f>
         <v/>
       </c>
       <c r="L9" s="10">
@@ -1762,7 +1769,7 @@
         <v>40</v>
       </c>
       <c r="K10" s="10">
-        <f>IF(E10="","",IF(D10="日",IF(F10="",E10,(E10+F10)/2)*G10,IF(F10="",E10,(E10+F10)/2))*$C$1)</f>
+        <f>IF(E10="","",IF(D10="日",IF(F10="",E10,(E10+F10)/2)*G10,IF(D10="月",E10,IF(F10="",E10,(E10+F10)/2)))*IF(D10="月",1,$C$1))</f>
         <v/>
       </c>
       <c r="L10" s="10">
@@ -1818,7 +1825,7 @@
         <v>100</v>
       </c>
       <c r="K11" s="10">
-        <f>IF(E11="","",IF(D11="日",IF(F11="",E11,(E11+F11)/2)*G11,IF(F11="",E11,(E11+F11)/2))*$C$1)</f>
+        <f>IF(E11="","",IF(D11="日",IF(F11="",E11,(E11+F11)/2)*G11,IF(D11="月",E11,IF(F11="",E11,(E11+F11)/2)))*IF(D11="月",1,$C$1))</f>
         <v/>
       </c>
       <c r="L11" s="10">
@@ -1835,18 +1842,40 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="n"/>
-      <c r="B12" s="11" t="n"/>
-      <c r="C12" s="11" t="n"/>
-      <c r="D12" s="11" t="n"/>
-      <c r="E12" s="11" t="n"/>
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>確定見積りの例（月あたり直接入力）</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>可燃ごみ</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>袋</t>
+        </is>
+      </c>
+      <c r="D12" s="9" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="E12" s="9" t="n">
+        <v>56</v>
+      </c>
       <c r="F12" s="11" t="n"/>
       <c r="G12" s="11" t="n"/>
       <c r="H12" s="11" t="n"/>
-      <c r="I12" s="11" t="n"/>
-      <c r="J12" s="11" t="n"/>
+      <c r="I12" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="J12" s="9" t="n">
+        <v>40</v>
+      </c>
       <c r="K12" s="10">
-        <f>IF(E12="","",IF(D12="日",IF(F12="",E12,(E12+F12)/2)*G12,IF(F12="",E12,(E12+F12)/2))*$C$1)</f>
+        <f>IF(E12="","",IF(D12="日",IF(F12="",E12,(E12+F12)/2)*G12,IF(D12="月",E12,IF(F12="",E12,(E12+F12)/2)))*IF(D12="月",1,$C$1))</f>
         <v/>
       </c>
       <c r="L12" s="10">
@@ -1863,18 +1892,40 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="11" t="n"/>
-      <c r="B13" s="11" t="n"/>
-      <c r="C13" s="11" t="n"/>
-      <c r="D13" s="11" t="n"/>
-      <c r="E13" s="11" t="n"/>
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>確定見積りの例（月あたり直接入力）</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="inlineStr">
+        <is>
+          <t>不燃ごみ</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>袋</t>
+        </is>
+      </c>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>16</v>
+      </c>
       <c r="F13" s="11" t="n"/>
       <c r="G13" s="11" t="n"/>
       <c r="H13" s="11" t="n"/>
-      <c r="I13" s="11" t="n"/>
-      <c r="J13" s="11" t="n"/>
+      <c r="I13" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="J13" s="9" t="n">
+        <v>100</v>
+      </c>
       <c r="K13" s="10">
-        <f>IF(E13="","",IF(D13="日",IF(F13="",E13,(E13+F13)/2)*G13,IF(F13="",E13,(E13+F13)/2))*$C$1)</f>
+        <f>IF(E13="","",IF(D13="日",IF(F13="",E13,(E13+F13)/2)*G13,IF(D13="月",E13,IF(F13="",E13,(E13+F13)/2)))*IF(D13="月",1,$C$1))</f>
         <v/>
       </c>
       <c r="L13" s="10">
@@ -1891,18 +1942,40 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="11" t="n"/>
-      <c r="B14" s="11" t="n"/>
-      <c r="C14" s="11" t="n"/>
-      <c r="D14" s="11" t="n"/>
-      <c r="E14" s="11" t="n"/>
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>確定見積りの例（月あたり直接入力）</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>段ボール</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
+        <is>
+          <t>枚</t>
+        </is>
+      </c>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>月</t>
+        </is>
+      </c>
+      <c r="E14" s="9" t="n">
+        <v>20</v>
+      </c>
       <c r="F14" s="11" t="n"/>
       <c r="G14" s="11" t="n"/>
       <c r="H14" s="11" t="n"/>
-      <c r="I14" s="11" t="n"/>
-      <c r="J14" s="11" t="n"/>
+      <c r="I14" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" s="9" t="n">
+        <v>35</v>
+      </c>
       <c r="K14" s="10">
-        <f>IF(E14="","",IF(D14="日",IF(F14="",E14,(E14+F14)/2)*G14,IF(F14="",E14,(E14+F14)/2))*$C$1)</f>
+        <f>IF(E14="","",IF(D14="日",IF(F14="",E14,(E14+F14)/2)*G14,IF(D14="月",E14,IF(F14="",E14,(E14+F14)/2)))*IF(D14="月",1,$C$1))</f>
         <v/>
       </c>
       <c r="L14" s="10">
@@ -1930,7 +2003,7 @@
       <c r="I15" s="11" t="n"/>
       <c r="J15" s="11" t="n"/>
       <c r="K15" s="10">
-        <f>IF(E15="","",IF(D15="日",IF(F15="",E15,(E15+F15)/2)*G15,IF(F15="",E15,(E15+F15)/2))*$C$1)</f>
+        <f>IF(E15="","",IF(D15="日",IF(F15="",E15,(E15+F15)/2)*G15,IF(D15="月",E15,IF(F15="",E15,(E15+F15)/2)))*IF(D15="月",1,$C$1))</f>
         <v/>
       </c>
       <c r="L15" s="10">
@@ -1958,7 +2031,7 @@
       <c r="I16" s="11" t="n"/>
       <c r="J16" s="11" t="n"/>
       <c r="K16" s="10">
-        <f>IF(E16="","",IF(D16="日",IF(F16="",E16,(E16+F16)/2)*G16,IF(F16="",E16,(E16+F16)/2))*$C$1)</f>
+        <f>IF(E16="","",IF(D16="日",IF(F16="",E16,(E16+F16)/2)*G16,IF(D16="月",E16,IF(F16="",E16,(E16+F16)/2)))*IF(D16="月",1,$C$1))</f>
         <v/>
       </c>
       <c r="L16" s="10">
@@ -1986,7 +2059,7 @@
       <c r="I17" s="11" t="n"/>
       <c r="J17" s="11" t="n"/>
       <c r="K17" s="10">
-        <f>IF(E17="","",IF(D17="日",IF(F17="",E17,(E17+F17)/2)*G17,IF(F17="",E17,(E17+F17)/2))*$C$1)</f>
+        <f>IF(E17="","",IF(D17="日",IF(F17="",E17,(E17+F17)/2)*G17,IF(D17="月",E17,IF(F17="",E17,(E17+F17)/2)))*IF(D17="月",1,$C$1))</f>
         <v/>
       </c>
       <c r="L17" s="10">
@@ -2014,7 +2087,7 @@
       <c r="I18" s="11" t="n"/>
       <c r="J18" s="11" t="n"/>
       <c r="K18" s="10">
-        <f>IF(E18="","",IF(D18="日",IF(F18="",E18,(E18+F18)/2)*G18,IF(F18="",E18,(E18+F18)/2))*$C$1)</f>
+        <f>IF(E18="","",IF(D18="日",IF(F18="",E18,(E18+F18)/2)*G18,IF(D18="月",E18,IF(F18="",E18,(E18+F18)/2)))*IF(D18="月",1,$C$1))</f>
         <v/>
       </c>
       <c r="L18" s="10">
@@ -2042,7 +2115,7 @@
       <c r="I19" s="11" t="n"/>
       <c r="J19" s="11" t="n"/>
       <c r="K19" s="10">
-        <f>IF(E19="","",IF(D19="日",IF(F19="",E19,(E19+F19)/2)*G19,IF(F19="",E19,(E19+F19)/2))*$C$1)</f>
+        <f>IF(E19="","",IF(D19="日",IF(F19="",E19,(E19+F19)/2)*G19,IF(D19="月",E19,IF(F19="",E19,(E19+F19)/2)))*IF(D19="月",1,$C$1))</f>
         <v/>
       </c>
       <c r="L19" s="10">
@@ -2070,7 +2143,7 @@
       <c r="I20" s="11" t="n"/>
       <c r="J20" s="11" t="n"/>
       <c r="K20" s="10">
-        <f>IF(E20="","",IF(D20="日",IF(F20="",E20,(E20+F20)/2)*G20,IF(F20="",E20,(E20+F20)/2))*$C$1)</f>
+        <f>IF(E20="","",IF(D20="日",IF(F20="",E20,(E20+F20)/2)*G20,IF(D20="月",E20,IF(F20="",E20,(E20+F20)/2)))*IF(D20="月",1,$C$1))</f>
         <v/>
       </c>
       <c r="L20" s="10">
@@ -2098,7 +2171,7 @@
       <c r="I21" s="11" t="n"/>
       <c r="J21" s="11" t="n"/>
       <c r="K21" s="10">
-        <f>IF(E21="","",IF(D21="日",IF(F21="",E21,(E21+F21)/2)*G21,IF(F21="",E21,(E21+F21)/2))*$C$1)</f>
+        <f>IF(E21="","",IF(D21="日",IF(F21="",E21,(E21+F21)/2)*G21,IF(D21="月",E21,IF(F21="",E21,(E21+F21)/2)))*IF(D21="月",1,$C$1))</f>
         <v/>
       </c>
       <c r="L21" s="10">
@@ -2126,7 +2199,7 @@
       <c r="I22" s="11" t="n"/>
       <c r="J22" s="11" t="n"/>
       <c r="K22" s="10">
-        <f>IF(E22="","",IF(D22="日",IF(F22="",E22,(E22+F22)/2)*G22,IF(F22="",E22,(E22+F22)/2))*$C$1)</f>
+        <f>IF(E22="","",IF(D22="日",IF(F22="",E22,(E22+F22)/2)*G22,IF(D22="月",E22,IF(F22="",E22,(E22+F22)/2)))*IF(D22="月",1,$C$1))</f>
         <v/>
       </c>
       <c r="L22" s="10">
@@ -2154,7 +2227,7 @@
       <c r="I23" s="11" t="n"/>
       <c r="J23" s="11" t="n"/>
       <c r="K23" s="10">
-        <f>IF(E23="","",IF(D23="日",IF(F23="",E23,(E23+F23)/2)*G23,IF(F23="",E23,(E23+F23)/2))*$C$1)</f>
+        <f>IF(E23="","",IF(D23="日",IF(F23="",E23,(E23+F23)/2)*G23,IF(D23="月",E23,IF(F23="",E23,(E23+F23)/2)))*IF(D23="月",1,$C$1))</f>
         <v/>
       </c>
       <c r="L23" s="10">
@@ -2182,7 +2255,7 @@
       <c r="I24" s="11" t="n"/>
       <c r="J24" s="11" t="n"/>
       <c r="K24" s="10">
-        <f>IF(E24="","",IF(D24="日",IF(F24="",E24,(E24+F24)/2)*G24,IF(F24="",E24,(E24+F24)/2))*$C$1)</f>
+        <f>IF(E24="","",IF(D24="日",IF(F24="",E24,(E24+F24)/2)*G24,IF(D24="月",E24,IF(F24="",E24,(E24+F24)/2)))*IF(D24="月",1,$C$1))</f>
         <v/>
       </c>
       <c r="L24" s="10">
@@ -2210,7 +2283,7 @@
       <c r="I25" s="11" t="n"/>
       <c r="J25" s="11" t="n"/>
       <c r="K25" s="10">
-        <f>IF(E25="","",IF(D25="日",IF(F25="",E25,(E25+F25)/2)*G25,IF(F25="",E25,(E25+F25)/2))*$C$1)</f>
+        <f>IF(E25="","",IF(D25="日",IF(F25="",E25,(E25+F25)/2)*G25,IF(D25="月",E25,IF(F25="",E25,(E25+F25)/2)))*IF(D25="月",1,$C$1))</f>
         <v/>
       </c>
       <c r="L25" s="10">
@@ -2238,7 +2311,7 @@
       <c r="I26" s="11" t="n"/>
       <c r="J26" s="11" t="n"/>
       <c r="K26" s="10">
-        <f>IF(E26="","",IF(D26="日",IF(F26="",E26,(E26+F26)/2)*G26,IF(F26="",E26,(E26+F26)/2))*$C$1)</f>
+        <f>IF(E26="","",IF(D26="日",IF(F26="",E26,(E26+F26)/2)*G26,IF(D26="月",E26,IF(F26="",E26,(E26+F26)/2)))*IF(D26="月",1,$C$1))</f>
         <v/>
       </c>
       <c r="L26" s="10">
@@ -2266,7 +2339,7 @@
       <c r="I27" s="11" t="n"/>
       <c r="J27" s="11" t="n"/>
       <c r="K27" s="10">
-        <f>IF(E27="","",IF(D27="日",IF(F27="",E27,(E27+F27)/2)*G27,IF(F27="",E27,(E27+F27)/2))*$C$1)</f>
+        <f>IF(E27="","",IF(D27="日",IF(F27="",E27,(E27+F27)/2)*G27,IF(D27="月",E27,IF(F27="",E27,(E27+F27)/2)))*IF(D27="月",1,$C$1))</f>
         <v/>
       </c>
       <c r="L27" s="10">
@@ -2294,7 +2367,7 @@
       <c r="I28" s="11" t="n"/>
       <c r="J28" s="11" t="n"/>
       <c r="K28" s="10">
-        <f>IF(E28="","",IF(D28="日",IF(F28="",E28,(E28+F28)/2)*G28,IF(F28="",E28,(E28+F28)/2))*$C$1)</f>
+        <f>IF(E28="","",IF(D28="日",IF(F28="",E28,(E28+F28)/2)*G28,IF(D28="月",E28,IF(F28="",E28,(E28+F28)/2)))*IF(D28="月",1,$C$1))</f>
         <v/>
       </c>
       <c r="L28" s="10">
@@ -2322,7 +2395,7 @@
       <c r="I29" s="11" t="n"/>
       <c r="J29" s="11" t="n"/>
       <c r="K29" s="10">
-        <f>IF(E29="","",IF(D29="日",IF(F29="",E29,(E29+F29)/2)*G29,IF(F29="",E29,(E29+F29)/2))*$C$1)</f>
+        <f>IF(E29="","",IF(D29="日",IF(F29="",E29,(E29+F29)/2)*G29,IF(D29="月",E29,IF(F29="",E29,(E29+F29)/2)))*IF(D29="月",1,$C$1))</f>
         <v/>
       </c>
       <c r="L29" s="10">
@@ -2350,7 +2423,7 @@
       <c r="I30" s="11" t="n"/>
       <c r="J30" s="11" t="n"/>
       <c r="K30" s="10">
-        <f>IF(E30="","",IF(D30="日",IF(F30="",E30,(E30+F30)/2)*G30,IF(F30="",E30,(E30+F30)/2))*$C$1)</f>
+        <f>IF(E30="","",IF(D30="日",IF(F30="",E30,(E30+F30)/2)*G30,IF(D30="月",E30,IF(F30="",E30,(E30+F30)/2)))*IF(D30="月",1,$C$1))</f>
         <v/>
       </c>
       <c r="L30" s="10">
@@ -2378,7 +2451,7 @@
       <c r="I31" s="11" t="n"/>
       <c r="J31" s="11" t="n"/>
       <c r="K31" s="10">
-        <f>IF(E31="","",IF(D31="日",IF(F31="",E31,(E31+F31)/2)*G31,IF(F31="",E31,(E31+F31)/2))*$C$1)</f>
+        <f>IF(E31="","",IF(D31="日",IF(F31="",E31,(E31+F31)/2)*G31,IF(D31="月",E31,IF(F31="",E31,(E31+F31)/2)))*IF(D31="月",1,$C$1))</f>
         <v/>
       </c>
       <c r="L31" s="10">
@@ -2406,7 +2479,7 @@
       <c r="I32" s="11" t="n"/>
       <c r="J32" s="11" t="n"/>
       <c r="K32" s="10">
-        <f>IF(E32="","",IF(D32="日",IF(F32="",E32,(E32+F32)/2)*G32,IF(F32="",E32,(E32+F32)/2))*$C$1)</f>
+        <f>IF(E32="","",IF(D32="日",IF(F32="",E32,(E32+F32)/2)*G32,IF(D32="月",E32,IF(F32="",E32,(E32+F32)/2)))*IF(D32="月",1,$C$1))</f>
         <v/>
       </c>
       <c r="L32" s="10">
@@ -2434,7 +2507,7 @@
       <c r="I33" s="11" t="n"/>
       <c r="J33" s="11" t="n"/>
       <c r="K33" s="10">
-        <f>IF(E33="","",IF(D33="日",IF(F33="",E33,(E33+F33)/2)*G33,IF(F33="",E33,(E33+F33)/2))*$C$1)</f>
+        <f>IF(E33="","",IF(D33="日",IF(F33="",E33,(E33+F33)/2)*G33,IF(D33="月",E33,IF(F33="",E33,(E33+F33)/2)))*IF(D33="月",1,$C$1))</f>
         <v/>
       </c>
       <c r="L33" s="10">
@@ -2462,7 +2535,7 @@
       <c r="I34" s="11" t="n"/>
       <c r="J34" s="11" t="n"/>
       <c r="K34" s="10">
-        <f>IF(E34="","",IF(D34="日",IF(F34="",E34,(E34+F34)/2)*G34,IF(F34="",E34,(E34+F34)/2))*$C$1)</f>
+        <f>IF(E34="","",IF(D34="日",IF(F34="",E34,(E34+F34)/2)*G34,IF(D34="月",E34,IF(F34="",E34,(E34+F34)/2)))*IF(D34="月",1,$C$1))</f>
         <v/>
       </c>
       <c r="L34" s="10">
@@ -2490,7 +2563,7 @@
       <c r="I35" s="11" t="n"/>
       <c r="J35" s="11" t="n"/>
       <c r="K35" s="10">
-        <f>IF(E35="","",IF(D35="日",IF(F35="",E35,(E35+F35)/2)*G35,IF(F35="",E35,(E35+F35)/2))*$C$1)</f>
+        <f>IF(E35="","",IF(D35="日",IF(F35="",E35,(E35+F35)/2)*G35,IF(D35="月",E35,IF(F35="",E35,(E35+F35)/2)))*IF(D35="月",1,$C$1))</f>
         <v/>
       </c>
       <c r="L35" s="10">
@@ -2518,7 +2591,7 @@
       <c r="I36" s="11" t="n"/>
       <c r="J36" s="11" t="n"/>
       <c r="K36" s="10">
-        <f>IF(E36="","",IF(D36="日",IF(F36="",E36,(E36+F36)/2)*G36,IF(F36="",E36,(E36+F36)/2))*$C$1)</f>
+        <f>IF(E36="","",IF(D36="日",IF(F36="",E36,(E36+F36)/2)*G36,IF(D36="月",E36,IF(F36="",E36,(E36+F36)/2)))*IF(D36="月",1,$C$1))</f>
         <v/>
       </c>
       <c r="L36" s="10">
@@ -2546,7 +2619,7 @@
       <c r="I37" s="11" t="n"/>
       <c r="J37" s="11" t="n"/>
       <c r="K37" s="10">
-        <f>IF(E37="","",IF(D37="日",IF(F37="",E37,(E37+F37)/2)*G37,IF(F37="",E37,(E37+F37)/2))*$C$1)</f>
+        <f>IF(E37="","",IF(D37="日",IF(F37="",E37,(E37+F37)/2)*G37,IF(D37="月",E37,IF(F37="",E37,(E37+F37)/2)))*IF(D37="月",1,$C$1))</f>
         <v/>
       </c>
       <c r="L37" s="10">
@@ -2574,7 +2647,7 @@
       <c r="I38" s="11" t="n"/>
       <c r="J38" s="11" t="n"/>
       <c r="K38" s="10">
-        <f>IF(E38="","",IF(D38="日",IF(F38="",E38,(E38+F38)/2)*G38,IF(F38="",E38,(E38+F38)/2))*$C$1)</f>
+        <f>IF(E38="","",IF(D38="日",IF(F38="",E38,(E38+F38)/2)*G38,IF(D38="月",E38,IF(F38="",E38,(E38+F38)/2)))*IF(D38="月",1,$C$1))</f>
         <v/>
       </c>
       <c r="L38" s="10">
@@ -2602,7 +2675,7 @@
       <c r="I39" s="11" t="n"/>
       <c r="J39" s="11" t="n"/>
       <c r="K39" s="10">
-        <f>IF(E39="","",IF(D39="日",IF(F39="",E39,(E39+F39)/2)*G39,IF(F39="",E39,(E39+F39)/2))*$C$1)</f>
+        <f>IF(E39="","",IF(D39="日",IF(F39="",E39,(E39+F39)/2)*G39,IF(D39="月",E39,IF(F39="",E39,(E39+F39)/2)))*IF(D39="月",1,$C$1))</f>
         <v/>
       </c>
       <c r="L39" s="10">
@@ -2630,7 +2703,7 @@
       <c r="I40" s="11" t="n"/>
       <c r="J40" s="11" t="n"/>
       <c r="K40" s="10">
-        <f>IF(E40="","",IF(D40="日",IF(F40="",E40,(E40+F40)/2)*G40,IF(F40="",E40,(E40+F40)/2))*$C$1)</f>
+        <f>IF(E40="","",IF(D40="日",IF(F40="",E40,(E40+F40)/2)*G40,IF(D40="月",E40,IF(F40="",E40,(E40+F40)/2)))*IF(D40="月",1,$C$1))</f>
         <v/>
       </c>
       <c r="L40" s="10">
@@ -2658,7 +2731,7 @@
       <c r="I41" s="11" t="n"/>
       <c r="J41" s="11" t="n"/>
       <c r="K41" s="10">
-        <f>IF(E41="","",IF(D41="日",IF(F41="",E41,(E41+F41)/2)*G41,IF(F41="",E41,(E41+F41)/2))*$C$1)</f>
+        <f>IF(E41="","",IF(D41="日",IF(F41="",E41,(E41+F41)/2)*G41,IF(D41="月",E41,IF(F41="",E41,(E41+F41)/2)))*IF(D41="月",1,$C$1))</f>
         <v/>
       </c>
       <c r="L41" s="10">
@@ -2686,7 +2759,7 @@
       <c r="I42" s="11" t="n"/>
       <c r="J42" s="11" t="n"/>
       <c r="K42" s="10">
-        <f>IF(E42="","",IF(D42="日",IF(F42="",E42,(E42+F42)/2)*G42,IF(F42="",E42,(E42+F42)/2))*$C$1)</f>
+        <f>IF(E42="","",IF(D42="日",IF(F42="",E42,(E42+F42)/2)*G42,IF(D42="月",E42,IF(F42="",E42,(E42+F42)/2)))*IF(D42="月",1,$C$1))</f>
         <v/>
       </c>
       <c r="L42" s="10">
@@ -2714,7 +2787,7 @@
       <c r="I43" s="11" t="n"/>
       <c r="J43" s="11" t="n"/>
       <c r="K43" s="10">
-        <f>IF(E43="","",IF(D43="日",IF(F43="",E43,(E43+F43)/2)*G43,IF(F43="",E43,(E43+F43)/2))*$C$1)</f>
+        <f>IF(E43="","",IF(D43="日",IF(F43="",E43,(E43+F43)/2)*G43,IF(D43="月",E43,IF(F43="",E43,(E43+F43)/2)))*IF(D43="月",1,$C$1))</f>
         <v/>
       </c>
       <c r="L43" s="10">
@@ -2739,7 +2812,7 @@
       <formula1>"袋,枚"</formula1>
     </dataValidation>
     <dataValidation sqref="D4:D43" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>"日,週"</formula1>
+      <formula1>"日,週,月"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
